--- a/data/lseg_excel/BOK26.xlsx
+++ b/data/lseg_excel/BOK26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C551"/>
+  <dimension ref="A1:C553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>59.79</v>
+        <v>60.26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>59.88</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>59.3</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -502,13 +502,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>60.09</v>
+        <v>59.88</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>59.08</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>57.76</v>
+        <v>60.09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>57.47</v>
+        <v>59.08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -562,13 +562,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>57.91</v>
+        <v>57.76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>57.5</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>57.74</v>
+        <v>57.91</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>57.17</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>55.84</v>
+        <v>57.74</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -637,13 +637,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>56.17</v>
+        <v>57.17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -652,13 +652,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>56.18</v>
+        <v>55.84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -667,13 +667,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>55.03</v>
+        <v>56.17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -682,13 +682,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>53.74</v>
+        <v>56.18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -697,13 +697,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>54.06</v>
+        <v>55.03</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -712,13 +712,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>54.58</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>54.85</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -742,13 +742,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>54.95</v>
+        <v>54.58</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>54.42</v>
+        <v>54.85</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -772,13 +772,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>54.52</v>
+        <v>54.95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>54.33</v>
+        <v>54.42</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -802,13 +802,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>54.54</v>
+        <v>54.52</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>53.11</v>
+        <v>54.33</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>53.15</v>
+        <v>54.54</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -847,13 +847,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>53.47</v>
+        <v>53.11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>51.5</v>
+        <v>53.15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -877,13 +877,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>51.69</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -892,13 +892,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>50.77</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>50.2</v>
+        <v>51.69</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -922,13 +922,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>49.97</v>
+        <v>50.77</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -937,13 +937,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>49.84</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -952,13 +952,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>49.95</v>
+        <v>49.97</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>50.41</v>
+        <v>49.84</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>49.83</v>
+        <v>49.95</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>49.09</v>
+        <v>50.41</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>49.94</v>
+        <v>49.83</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1027,13 +1027,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>49.8</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1042,13 +1042,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>49.73</v>
+        <v>49.94</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>50</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>49.28</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>49.58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1102,13 +1102,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>48.92</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>49.1</v>
+        <v>49.58</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>49.53</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1147,13 +1147,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>49.4</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1162,13 +1162,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>50.45</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>51.03</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>51.68</v>
+        <v>50.45</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1207,13 +1207,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>51.96</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1222,13 +1222,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>51.88</v>
+        <v>51.68</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1237,13 +1237,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>52.04</v>
+        <v>51.96</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>52.54</v>
+        <v>51.88</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>52.63</v>
+        <v>52.04</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1288,7 +1288,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>53.51</v>
+        <v>52.63</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>53.16</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>52.84</v>
+        <v>53.51</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1342,13 +1342,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>51.89</v>
+        <v>53.16</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1357,13 +1357,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>51.51</v>
+        <v>52.84</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1372,13 +1372,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>51.41</v>
+        <v>51.89</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>51.47</v>
+        <v>51.51</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1402,13 +1402,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>51.83</v>
+        <v>51.41</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>52.3</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>53.35</v>
+        <v>51.83</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1447,13 +1447,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>52.36</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1462,13 +1462,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>51.46</v>
+        <v>53.35</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1477,13 +1477,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>51.56</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>51.9</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>52.33</v>
+        <v>51.56</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1522,13 +1522,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1537,13 +1537,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>50.9</v>
+        <v>52.33</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1552,13 +1552,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>50.56</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1567,13 +1567,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>50.88</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1582,13 +1582,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>50.76</v>
+        <v>50.56</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>51.08</v>
+        <v>50.88</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1612,13 +1612,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>50</v>
+        <v>50.76</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1627,13 +1627,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>50.88</v>
+        <v>51.08</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1642,13 +1642,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>51.34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1657,13 +1657,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>51.46</v>
+        <v>50.88</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1672,13 +1672,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>51.93</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1687,13 +1687,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>51.4</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1708,7 +1708,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1717,13 +1717,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>51.21</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>51.72</v>
+        <v>51.93</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1747,13 +1747,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>52.32</v>
+        <v>51.21</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1762,13 +1762,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>52.09</v>
+        <v>51.72</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1777,13 +1777,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>51.84</v>
+        <v>52.32</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1792,13 +1792,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>51.73</v>
+        <v>52.09</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1807,13 +1807,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>51.47</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -1822,13 +1822,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>51.47</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>50.86</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1852,13 +1852,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>51.84</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1867,13 +1867,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>52.41</v>
+        <v>50.86</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -1882,13 +1882,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>51.89</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1897,13 +1897,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>51.33</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>51.02</v>
+        <v>51.89</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -1927,13 +1927,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>51.38</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -1942,13 +1942,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>51.34</v>
+        <v>51.02</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -1957,13 +1957,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>50.46</v>
+        <v>51.38</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>50.74</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -1987,13 +1987,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>51.27</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2002,13 +2002,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>51.34</v>
+        <v>50.74</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>50.92</v>
+        <v>51.27</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2032,13 +2032,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>50.93</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2047,13 +2047,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>50.7</v>
+        <v>50.92</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2062,13 +2062,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>51.5</v>
+        <v>50.93</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>52.03</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2092,13 +2092,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>52.59</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2107,13 +2107,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>53.81</v>
+        <v>52.03</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2122,13 +2122,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>52.98</v>
+        <v>52.59</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2137,13 +2137,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>52.98</v>
+        <v>53.81</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2152,13 +2152,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>52.41</v>
+        <v>52.98</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2167,13 +2167,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>51.85</v>
+        <v>52.98</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2182,13 +2182,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>51.41</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2197,13 +2197,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>52.36</v>
+        <v>51.85</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2212,13 +2212,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>52.02</v>
+        <v>51.41</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2227,13 +2227,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>52.63</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2242,13 +2242,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>52.54</v>
+        <v>52.02</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2257,13 +2257,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>53.3</v>
+        <v>52.63</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2272,13 +2272,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>52.79</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>53.07</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2302,13 +2302,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>53.82</v>
+        <v>52.79</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2317,13 +2317,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>53.93</v>
+        <v>53.07</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2332,13 +2332,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>55.12</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>55.41</v>
+        <v>53.93</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2362,13 +2362,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>54.01</v>
+        <v>55.12</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>51.87</v>
+        <v>55.41</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -2392,13 +2392,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>52.23</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -2407,13 +2407,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>53.59</v>
+        <v>51.87</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -2422,13 +2422,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>53.31</v>
+        <v>52.23</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -2437,13 +2437,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>52.27</v>
+        <v>53.59</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -2452,13 +2452,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>53.3</v>
+        <v>53.31</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -2467,13 +2467,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>53</v>
+        <v>52.27</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -2482,13 +2482,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>52.87</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -2497,13 +2497,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>52.46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -2512,13 +2512,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>53.33</v>
+        <v>52.87</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -2527,13 +2527,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>53.53</v>
+        <v>52.46</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>53.25</v>
+        <v>53.33</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -2557,13 +2557,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>53.87</v>
+        <v>53.53</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -2572,13 +2572,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>53.61</v>
+        <v>53.25</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -2587,13 +2587,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>54.32</v>
+        <v>53.87</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -2602,13 +2602,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>55.55</v>
+        <v>53.61</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>56.24</v>
+        <v>54.32</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -2632,13 +2632,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>55.61</v>
+        <v>55.55</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>55.47</v>
+        <v>56.24</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -2662,13 +2662,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>55.8</v>
+        <v>55.61</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -2677,13 +2677,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>55.34</v>
+        <v>55.47</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -2692,13 +2692,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>54.93</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -2707,13 +2707,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>55.29</v>
+        <v>55.34</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -2722,13 +2722,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>55.02</v>
+        <v>54.93</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -2737,13 +2737,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>55.59</v>
+        <v>55.29</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -2752,13 +2752,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>54.31</v>
+        <v>55.02</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -2767,13 +2767,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>54.1</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -2782,13 +2782,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>53.8</v>
+        <v>54.31</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -2797,13 +2797,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>53.47</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -2812,13 +2812,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>53.38</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -2827,13 +2827,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>53.17</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -2842,13 +2842,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>53.82</v>
+        <v>53.38</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -2857,13 +2857,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>53.64</v>
+        <v>53.17</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -2872,13 +2872,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>54.46</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>54.77</v>
+        <v>53.64</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -2902,13 +2902,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>53.48</v>
+        <v>54.46</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>52.62</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -2932,13 +2932,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>52.52</v>
+        <v>53.48</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -2947,13 +2947,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>52.86</v>
+        <v>52.62</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -2962,13 +2962,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>52.43</v>
+        <v>52.52</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -2977,13 +2977,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>52.69</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -2992,13 +2992,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>53.79</v>
+        <v>52.43</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3007,13 +3007,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>55.04</v>
+        <v>52.69</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3022,13 +3022,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>55.23</v>
+        <v>53.79</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -3037,13 +3037,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>55.16</v>
+        <v>55.04</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -3052,13 +3052,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>55.1</v>
+        <v>55.23</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>51.65</v>
+        <v>55.16</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -3082,13 +3082,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>48.65</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3097,13 +3097,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>48.94</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -3112,13 +3112,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>48.82</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -3127,13 +3127,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>48.46</v>
+        <v>48.94</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -3142,13 +3142,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>48.62</v>
+        <v>48.82</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -3157,13 +3157,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>47.95</v>
+        <v>48.46</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -3172,13 +3172,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>47.8</v>
+        <v>48.62</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -3187,13 +3187,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>47.85</v>
+        <v>47.95</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -3202,13 +3202,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>47.49</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -3217,13 +3217,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>47.78</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -3232,13 +3232,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>49.05</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -3247,13 +3247,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>49.41</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -3262,13 +3262,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>50.03</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>49.88</v>
+        <v>49.41</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -3292,13 +3292,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>49.73</v>
+        <v>50.03</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -3307,13 +3307,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>50.23</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -3322,13 +3322,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>49.88</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -3337,13 +3337,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>49.78</v>
+        <v>50.23</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -3352,13 +3352,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>49.2</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -3367,13 +3367,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>48.9</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -3382,13 +3382,13 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>51.9</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>51.46</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -3412,13 +3412,13 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>50.03</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -3427,13 +3427,13 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>48.66</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -3442,13 +3442,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>48.38</v>
+        <v>50.03</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -3457,13 +3457,13 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>47.52</v>
+        <v>48.66</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -3472,13 +3472,13 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>48.22</v>
+        <v>48.38</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -3487,13 +3487,13 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>48.33</v>
+        <v>47.52</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -3502,13 +3502,13 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>48.82</v>
+        <v>48.22</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>48.95</v>
+        <v>48.33</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -3532,13 +3532,13 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>48.22</v>
+        <v>48.82</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -3547,13 +3547,13 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>48.75</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -3562,13 +3562,13 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>49.78</v>
+        <v>48.22</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -3577,13 +3577,13 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>49.23</v>
+        <v>48.75</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -3592,13 +3592,13 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>49.17</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -3607,13 +3607,13 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>47.85</v>
+        <v>49.23</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -3622,13 +3622,13 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>47.78</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -3637,13 +3637,13 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>47.83</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -3652,13 +3652,13 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>47.91</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>47.73</v>
+        <v>47.83</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -3682,13 +3682,13 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>47.54</v>
+        <v>47.91</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -3697,13 +3697,13 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>46.72</v>
+        <v>47.73</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -3712,13 +3712,13 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>47.16</v>
+        <v>47.54</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -3727,13 +3727,13 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>46.15</v>
+        <v>46.72</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -3742,13 +3742,13 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>46.11</v>
+        <v>47.16</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -3757,13 +3757,13 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>44.82</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -3772,13 +3772,13 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>45.02</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -3787,13 +3787,13 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>45.96</v>
+        <v>44.82</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>47.35</v>
+        <v>45.02</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -3817,13 +3817,13 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>48.65</v>
+        <v>45.96</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -3832,13 +3832,13 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>47.87</v>
+        <v>47.35</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -3847,13 +3847,13 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>46</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -3862,13 +3862,13 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>46.11</v>
+        <v>47.87</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -3877,13 +3877,13 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>45.42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -3892,13 +3892,13 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>44.2</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -3907,13 +3907,13 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>43.82</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -3922,13 +3922,13 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>43.48</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -3937,13 +3937,13 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>43.28</v>
+        <v>43.82</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -3952,13 +3952,13 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>43.7</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -3967,13 +3967,13 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>43.32</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -3982,13 +3982,13 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>43.28</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -3997,13 +3997,13 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>42.9</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -4012,13 +4012,13 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>42.51</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -4027,13 +4027,13 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>42.36</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -4042,13 +4042,13 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>42.65</v>
+        <v>42.51</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -4057,13 +4057,13 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>42.85</v>
+        <v>42.36</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -4072,13 +4072,13 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>43.04</v>
+        <v>42.65</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -4087,13 +4087,13 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>43.92</v>
+        <v>42.85</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -4102,13 +4102,13 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>43.52</v>
+        <v>43.04</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -4117,13 +4117,13 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>43.37</v>
+        <v>43.92</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -4132,13 +4132,13 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>43.24</v>
+        <v>43.52</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -4147,13 +4147,13 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>43.99</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -4162,13 +4162,13 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>44.52</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -4177,13 +4177,13 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>45.66</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -4192,13 +4192,13 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>45.78</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -4207,13 +4207,13 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>46.1</v>
+        <v>45.66</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -4222,13 +4222,13 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>46.42</v>
+        <v>45.78</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -4237,13 +4237,13 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>47.21</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -4252,13 +4252,13 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>47.44</v>
+        <v>46.42</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -4267,13 +4267,13 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>46.5</v>
+        <v>47.21</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -4282,13 +4282,13 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>47.21</v>
+        <v>47.44</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -4297,13 +4297,13 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>46.08</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -4312,13 +4312,13 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>46.21</v>
+        <v>47.21</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -4327,13 +4327,13 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>45.72</v>
+        <v>46.08</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>46.29</v>
+        <v>46.21</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -4357,13 +4357,13 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>45.9</v>
+        <v>45.72</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -4372,13 +4372,13 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>46.05</v>
+        <v>46.29</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -4387,13 +4387,13 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>45.73</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -4402,13 +4402,13 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>45.31</v>
+        <v>46.05</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -4417,13 +4417,13 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>45.75</v>
+        <v>45.73</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -4432,13 +4432,13 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>46.37</v>
+        <v>45.31</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -4447,13 +4447,13 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>45.77</v>
+        <v>45.75</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -4462,13 +4462,13 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>45.1</v>
+        <v>46.37</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -4477,13 +4477,13 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>44.97</v>
+        <v>45.77</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -4492,13 +4492,13 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>45.11</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -4507,13 +4507,13 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>44.88</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -4522,13 +4522,13 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>45.06</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -4537,13 +4537,13 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>44.73</v>
+        <v>44.88</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -4552,13 +4552,13 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>44.3</v>
+        <v>45.06</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -4567,13 +4567,13 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>45.15</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -4582,13 +4582,13 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>45.27</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -4597,13 +4597,13 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>45.03</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -4612,13 +4612,13 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>45.99</v>
+        <v>45.27</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -4627,13 +4627,13 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>46.22</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -4642,13 +4642,13 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>46.06</v>
+        <v>45.99</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -4657,13 +4657,13 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>45.62</v>
+        <v>46.22</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -4672,13 +4672,13 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>43.48</v>
+        <v>46.06</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -4687,13 +4687,13 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>42.45</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -4702,13 +4702,13 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>42.17</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>41.34</v>
+        <v>42.45</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -4732,13 +4732,13 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>40.87</v>
+        <v>42.17</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -4747,13 +4747,13 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>41.09</v>
+        <v>41.34</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -4762,13 +4762,13 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>41.32</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -4777,13 +4777,13 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>41.19</v>
+        <v>41.09</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -4792,13 +4792,13 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>40.94</v>
+        <v>41.32</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -4807,13 +4807,13 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>40.94</v>
+        <v>41.19</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2024-12-24</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -4822,13 +4822,13 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>41.38</v>
+        <v>40.94</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -4837,13 +4837,13 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>41.62</v>
+        <v>40.94</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -4852,13 +4852,13 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>40.87</v>
+        <v>41.38</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -4867,13 +4867,13 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>41.15</v>
+        <v>41.62</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -4882,13 +4882,13 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>40.92</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -4897,13 +4897,13 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>41.73</v>
+        <v>41.15</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -4912,13 +4912,13 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>42.72</v>
+        <v>40.92</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -4927,13 +4927,13 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>43.49</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -4942,13 +4942,13 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>43.53</v>
+        <v>42.72</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -4957,13 +4957,13 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>43.26</v>
+        <v>43.49</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -4972,13 +4972,13 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>43.46</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -4987,13 +4987,13 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>43.52</v>
+        <v>43.26</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>43.58</v>
+        <v>43.46</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -5017,13 +5017,13 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>42.89</v>
+        <v>43.52</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>42.12</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -5047,13 +5047,13 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>42.67</v>
+        <v>42.89</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>42.3</v>
+        <v>42.12</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -5077,13 +5077,13 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>42.39</v>
+        <v>42.67</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -5092,13 +5092,13 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>41.84</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -5107,13 +5107,13 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>43.17</v>
+        <v>42.39</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -5122,13 +5122,13 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>42.27</v>
+        <v>41.84</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -5137,13 +5137,13 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>42.78</v>
+        <v>43.17</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -5152,13 +5152,13 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>43.09</v>
+        <v>42.27</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -5167,13 +5167,13 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>43.95</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -5182,13 +5182,13 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>44.91</v>
+        <v>43.09</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -5197,13 +5197,13 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>45.32</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -5212,13 +5212,13 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>45.24</v>
+        <v>44.91</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -5227,13 +5227,13 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>44.48</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -5242,13 +5242,13 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>45.38</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -5257,13 +5257,13 @@
         </is>
       </c>
       <c r="C322" t="n">
-        <v>46.24</v>
+        <v>44.48</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -5272,13 +5272,13 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>47.78</v>
+        <v>45.38</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -5287,13 +5287,13 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>48.04</v>
+        <v>46.24</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -5302,13 +5302,13 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>47.49</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -5317,13 +5317,13 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>45.65</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>45.01</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -5347,13 +5347,13 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>45.36</v>
+        <v>45.65</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>45.49</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -5377,13 +5377,13 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>44.54</v>
+        <v>45.36</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -5392,13 +5392,13 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>43.62</v>
+        <v>45.49</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -5407,13 +5407,13 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>42.78</v>
+        <v>44.54</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -5422,13 +5422,13 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>42.73</v>
+        <v>43.62</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -5437,13 +5437,13 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>43.65</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -5452,13 +5452,13 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>43.48</v>
+        <v>42.73</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -5467,13 +5467,13 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>42.77</v>
+        <v>43.65</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -5482,13 +5482,13 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>42.86</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -5497,13 +5497,13 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>41.8</v>
+        <v>42.77</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -5512,13 +5512,13 @@
         </is>
       </c>
       <c r="C339" t="n">
-        <v>41.24</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -5527,13 +5527,13 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>41.92</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -5542,13 +5542,13 @@
         </is>
       </c>
       <c r="C341" t="n">
-        <v>41.59</v>
+        <v>41.24</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -5557,13 +5557,13 @@
         </is>
       </c>
       <c r="C342" t="n">
-        <v>42.03</v>
+        <v>41.92</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -5572,13 +5572,13 @@
         </is>
       </c>
       <c r="C343" t="n">
-        <v>42.03</v>
+        <v>41.59</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -5587,13 +5587,13 @@
         </is>
       </c>
       <c r="C344" t="n">
-        <v>43.28</v>
+        <v>42.03</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -5602,13 +5602,13 @@
         </is>
       </c>
       <c r="C345" t="n">
-        <v>43.74</v>
+        <v>42.03</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -5617,13 +5617,13 @@
         </is>
       </c>
       <c r="C346" t="n">
-        <v>43.16</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>43.22</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -5647,13 +5647,13 @@
         </is>
       </c>
       <c r="C348" t="n">
-        <v>44.73</v>
+        <v>43.16</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -5662,13 +5662,13 @@
         </is>
       </c>
       <c r="C349" t="n">
-        <v>44.08</v>
+        <v>43.22</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -5677,13 +5677,13 @@
         </is>
       </c>
       <c r="C350" t="n">
-        <v>44.43</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -5692,13 +5692,13 @@
         </is>
       </c>
       <c r="C351" t="n">
-        <v>43.57</v>
+        <v>44.08</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -5707,13 +5707,13 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>43.08</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -5722,13 +5722,13 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>43.05</v>
+        <v>43.57</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -5737,13 +5737,13 @@
         </is>
       </c>
       <c r="C354" t="n">
-        <v>42.78</v>
+        <v>43.08</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -5752,13 +5752,13 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>43.53</v>
+        <v>43.05</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -5767,13 +5767,13 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>43.71</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -5782,13 +5782,13 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>43.14</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>42.09</v>
+        <v>43.71</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>41.73</v>
+        <v>43.14</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -5827,13 +5827,13 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>41.43</v>
+        <v>42.09</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -5842,13 +5842,13 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>41.17</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -5857,13 +5857,13 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>40.69</v>
+        <v>41.43</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -5872,13 +5872,13 @@
         </is>
       </c>
       <c r="C363" t="n">
-        <v>40.11</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -5887,13 +5887,13 @@
         </is>
       </c>
       <c r="C364" t="n">
-        <v>40.12</v>
+        <v>40.69</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -5902,13 +5902,13 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>40.75</v>
+        <v>40.11</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -5917,13 +5917,13 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>40.39</v>
+        <v>40.12</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -5932,13 +5932,13 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>40.6</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -5947,13 +5947,13 @@
         </is>
       </c>
       <c r="C368" t="n">
-        <v>41.29</v>
+        <v>40.39</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -5962,13 +5962,13 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>40.49</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -5977,13 +5977,13 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>41.62</v>
+        <v>41.29</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -5992,13 +5992,13 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>40.98</v>
+        <v>40.49</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -6007,13 +6007,13 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>41.5</v>
+        <v>41.62</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -6022,13 +6022,13 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>42.26</v>
+        <v>40.98</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -6037,13 +6037,13 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>42.24</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -6052,13 +6052,13 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>41.21</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -6067,13 +6067,13 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>40.93</v>
+        <v>42.24</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -6082,13 +6082,13 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>40.83</v>
+        <v>41.21</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -6097,13 +6097,13 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>40.51</v>
+        <v>40.93</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -6112,13 +6112,13 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>39.52</v>
+        <v>40.83</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -6127,13 +6127,13 @@
         </is>
       </c>
       <c r="C380" t="n">
-        <v>40.05</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -6142,13 +6142,13 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>39.68</v>
+        <v>39.52</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -6157,13 +6157,13 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>39.76</v>
+        <v>40.05</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -6172,13 +6172,13 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>39.55</v>
+        <v>39.68</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -6187,13 +6187,13 @@
         </is>
       </c>
       <c r="C384" t="n">
-        <v>39.29</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -6202,13 +6202,13 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>39.58</v>
+        <v>39.55</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -6217,13 +6217,13 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>39.89</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -6232,13 +6232,13 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>40.84</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -6247,13 +6247,13 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>40.75</v>
+        <v>39.89</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -6262,13 +6262,13 @@
         </is>
       </c>
       <c r="C389" t="n">
-        <v>40.68</v>
+        <v>40.84</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -6277,13 +6277,13 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>40.51</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -6292,13 +6292,13 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>40.16</v>
+        <v>40.68</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -6307,13 +6307,13 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>40.25</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -6322,13 +6322,13 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>40.91</v>
+        <v>40.16</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -6337,13 +6337,13 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>41.18</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -6352,13 +6352,13 @@
         </is>
       </c>
       <c r="C395" t="n">
-        <v>41.72</v>
+        <v>40.91</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -6367,13 +6367,13 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>41.2</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -6382,13 +6382,13 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>41.67</v>
+        <v>41.72</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -6397,13 +6397,13 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>41.34</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -6412,13 +6412,13 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>42.82</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -6427,13 +6427,13 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>42.57</v>
+        <v>41.34</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -6442,13 +6442,13 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>43.28</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -6457,13 +6457,13 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>42.86</v>
+        <v>42.57</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -6472,13 +6472,13 @@
         </is>
       </c>
       <c r="C403" t="n">
-        <v>41.96</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -6487,13 +6487,13 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>42.63</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -6502,13 +6502,13 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>42.6</v>
+        <v>41.96</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -6517,13 +6517,13 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>43.39</v>
+        <v>42.63</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -6532,13 +6532,13 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>43.49</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>44.6</v>
+        <v>43.39</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -6562,13 +6562,13 @@
         </is>
       </c>
       <c r="C409" t="n">
-        <v>45.01</v>
+        <v>43.49</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -6577,13 +6577,13 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>44.73</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -6592,13 +6592,13 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>45.87</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -6607,13 +6607,13 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>46.97</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -6622,13 +6622,13 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>47.02</v>
+        <v>45.87</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -6637,13 +6637,13 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>46.75</v>
+        <v>46.97</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -6652,13 +6652,13 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>45.79</v>
+        <v>47.02</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -6667,13 +6667,13 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>44.84</v>
+        <v>46.75</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -6682,13 +6682,13 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>43.13</v>
+        <v>45.79</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -6697,13 +6697,13 @@
         </is>
       </c>
       <c r="C418" t="n">
-        <v>42.97</v>
+        <v>44.84</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -6712,13 +6712,13 @@
         </is>
       </c>
       <c r="C419" t="n">
-        <v>43.37</v>
+        <v>43.13</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -6727,13 +6727,13 @@
         </is>
       </c>
       <c r="C420" t="n">
-        <v>42.71</v>
+        <v>42.97</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -6742,13 +6742,13 @@
         </is>
       </c>
       <c r="C421" t="n">
-        <v>43.35</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -6757,13 +6757,13 @@
         </is>
       </c>
       <c r="C422" t="n">
-        <v>43.58</v>
+        <v>42.71</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -6772,13 +6772,13 @@
         </is>
       </c>
       <c r="C423" t="n">
-        <v>43.59</v>
+        <v>43.35</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -6787,13 +6787,13 @@
         </is>
       </c>
       <c r="C424" t="n">
-        <v>44.01</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -6802,13 +6802,13 @@
         </is>
       </c>
       <c r="C425" t="n">
-        <v>43.56</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -6817,13 +6817,13 @@
         </is>
       </c>
       <c r="C426" t="n">
-        <v>43.53</v>
+        <v>44.01</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -6832,13 +6832,13 @@
         </is>
       </c>
       <c r="C427" t="n">
-        <v>43.76</v>
+        <v>43.56</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="C428" t="n">
-        <v>43.87</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -6868,7 +6868,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -6877,13 +6877,13 @@
         </is>
       </c>
       <c r="C430" t="n">
-        <v>43.98</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -6892,13 +6892,13 @@
         </is>
       </c>
       <c r="C431" t="n">
-        <v>44.29</v>
+        <v>43.76</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -6907,13 +6907,13 @@
         </is>
       </c>
       <c r="C432" t="n">
-        <v>44.83</v>
+        <v>43.98</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -6922,13 +6922,13 @@
         </is>
       </c>
       <c r="C433" t="n">
-        <v>43.88</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -6937,13 +6937,13 @@
         </is>
       </c>
       <c r="C434" t="n">
-        <v>44.2</v>
+        <v>44.83</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -6952,13 +6952,13 @@
         </is>
       </c>
       <c r="C435" t="n">
-        <v>44.63</v>
+        <v>43.88</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -6967,13 +6967,13 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>45.81</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -6982,13 +6982,13 @@
         </is>
       </c>
       <c r="C437" t="n">
-        <v>45.93</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -6997,13 +6997,13 @@
         </is>
       </c>
       <c r="C438" t="n">
-        <v>46.11</v>
+        <v>45.81</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -7012,13 +7012,13 @@
         </is>
       </c>
       <c r="C439" t="n">
-        <v>45.74</v>
+        <v>45.93</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -7027,13 +7027,13 @@
         </is>
       </c>
       <c r="C440" t="n">
-        <v>45.32</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -7042,13 +7042,13 @@
         </is>
       </c>
       <c r="C441" t="n">
-        <v>45.96</v>
+        <v>45.74</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -7057,13 +7057,13 @@
         </is>
       </c>
       <c r="C442" t="n">
-        <v>46.2</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -7072,13 +7072,13 @@
         </is>
       </c>
       <c r="C443" t="n">
-        <v>46.37</v>
+        <v>45.96</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -7087,13 +7087,13 @@
         </is>
       </c>
       <c r="C444" t="n">
-        <v>46.6</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -7102,13 +7102,13 @@
         </is>
       </c>
       <c r="C445" t="n">
-        <v>45.89</v>
+        <v>46.37</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -7117,13 +7117,13 @@
         </is>
       </c>
       <c r="C446" t="n">
-        <v>45.45</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -7132,13 +7132,13 @@
         </is>
       </c>
       <c r="C447" t="n">
-        <v>44.82</v>
+        <v>45.89</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -7147,13 +7147,13 @@
         </is>
       </c>
       <c r="C448" t="n">
-        <v>44.7</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -7162,13 +7162,13 @@
         </is>
       </c>
       <c r="C449" t="n">
-        <v>46.01</v>
+        <v>44.82</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -7177,13 +7177,13 @@
         </is>
       </c>
       <c r="C450" t="n">
-        <v>45.24</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -7192,13 +7192,13 @@
         </is>
       </c>
       <c r="C451" t="n">
-        <v>44.2</v>
+        <v>46.01</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="C452" t="n">
-        <v>44.8</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -7222,13 +7222,13 @@
         </is>
       </c>
       <c r="C453" t="n">
-        <v>45.29</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -7237,13 +7237,13 @@
         </is>
       </c>
       <c r="C454" t="n">
-        <v>44.66</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="C455" t="n">
-        <v>44.34</v>
+        <v>45.29</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -7267,13 +7267,13 @@
         </is>
       </c>
       <c r="C456" t="n">
-        <v>44.43</v>
+        <v>44.66</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -7282,13 +7282,13 @@
         </is>
       </c>
       <c r="C457" t="n">
-        <v>44.49</v>
+        <v>44.34</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -7297,13 +7297,13 @@
         </is>
       </c>
       <c r="C458" t="n">
-        <v>44.32</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -7312,13 +7312,13 @@
         </is>
       </c>
       <c r="C459" t="n">
-        <v>45.01</v>
+        <v>44.49</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -7327,13 +7327,13 @@
         </is>
       </c>
       <c r="C460" t="n">
-        <v>45.94</v>
+        <v>44.32</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -7342,13 +7342,13 @@
         </is>
       </c>
       <c r="C461" t="n">
-        <v>45.67</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -7357,13 +7357,13 @@
         </is>
       </c>
       <c r="C462" t="n">
-        <v>45.58</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -7372,13 +7372,13 @@
         </is>
       </c>
       <c r="C463" t="n">
-        <v>45.95</v>
+        <v>45.67</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -7387,13 +7387,13 @@
         </is>
       </c>
       <c r="C464" t="n">
-        <v>45.8</v>
+        <v>45.58</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -7402,13 +7402,13 @@
         </is>
       </c>
       <c r="C465" t="n">
-        <v>45.14</v>
+        <v>45.95</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -7417,13 +7417,13 @@
         </is>
       </c>
       <c r="C466" t="n">
-        <v>44.97</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -7432,13 +7432,13 @@
         </is>
       </c>
       <c r="C467" t="n">
-        <v>45.19</v>
+        <v>45.14</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -7447,13 +7447,13 @@
         </is>
       </c>
       <c r="C468" t="n">
-        <v>45.34</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="C469" t="n">
-        <v>45.6</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -7477,13 +7477,13 @@
         </is>
       </c>
       <c r="C470" t="n">
-        <v>45.97</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -7492,13 +7492,13 @@
         </is>
       </c>
       <c r="C471" t="n">
-        <v>45.91</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -7507,13 +7507,13 @@
         </is>
       </c>
       <c r="C472" t="n">
-        <v>46.95</v>
+        <v>45.97</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -7522,13 +7522,13 @@
         </is>
       </c>
       <c r="C473" t="n">
-        <v>46.91</v>
+        <v>45.91</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -7537,13 +7537,13 @@
         </is>
       </c>
       <c r="C474" t="n">
-        <v>47.23</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -7552,13 +7552,13 @@
         </is>
       </c>
       <c r="C475" t="n">
-        <v>47.84</v>
+        <v>46.91</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -7567,13 +7567,13 @@
         </is>
       </c>
       <c r="C476" t="n">
-        <v>47.38</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -7582,13 +7582,13 @@
         </is>
       </c>
       <c r="C477" t="n">
-        <v>48</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -7597,13 +7597,13 @@
         </is>
       </c>
       <c r="C478" t="n">
-        <v>47.67</v>
+        <v>47.38</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -7612,13 +7612,13 @@
         </is>
       </c>
       <c r="C479" t="n">
-        <v>47.12</v>
+        <v>48</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -7627,13 +7627,13 @@
         </is>
       </c>
       <c r="C480" t="n">
-        <v>47.14</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -7642,13 +7642,13 @@
         </is>
       </c>
       <c r="C481" t="n">
-        <v>46.67</v>
+        <v>47.12</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -7657,13 +7657,13 @@
         </is>
       </c>
       <c r="C482" t="n">
-        <v>47.46</v>
+        <v>47.14</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -7672,13 +7672,13 @@
         </is>
       </c>
       <c r="C483" t="n">
-        <v>47.71</v>
+        <v>46.67</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -7687,13 +7687,13 @@
         </is>
       </c>
       <c r="C484" t="n">
-        <v>46.65</v>
+        <v>47.46</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -7702,13 +7702,13 @@
         </is>
       </c>
       <c r="C485" t="n">
-        <v>47.72</v>
+        <v>47.71</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -7717,13 +7717,13 @@
         </is>
       </c>
       <c r="C486" t="n">
-        <v>47.89</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -7732,13 +7732,13 @@
         </is>
       </c>
       <c r="C487" t="n">
-        <v>47.23</v>
+        <v>47.72</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -7747,13 +7747,13 @@
         </is>
       </c>
       <c r="C488" t="n">
-        <v>47.63</v>
+        <v>47.89</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -7762,13 +7762,13 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>48.16</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -7777,13 +7777,13 @@
         </is>
       </c>
       <c r="C490" t="n">
-        <v>47.08</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -7792,13 +7792,13 @@
         </is>
       </c>
       <c r="C491" t="n">
-        <v>47.34</v>
+        <v>48.16</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="C492" t="n">
-        <v>46.61</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -7822,13 +7822,13 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>45.84</v>
+        <v>47.34</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -7837,13 +7837,13 @@
         </is>
       </c>
       <c r="C494" t="n">
-        <v>45.28</v>
+        <v>46.61</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -7852,13 +7852,13 @@
         </is>
       </c>
       <c r="C495" t="n">
-        <v>45.23</v>
+        <v>45.84</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -7867,13 +7867,13 @@
         </is>
       </c>
       <c r="C496" t="n">
-        <v>44.51</v>
+        <v>45.28</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -7882,13 +7882,13 @@
         </is>
       </c>
       <c r="C497" t="n">
-        <v>44.37</v>
+        <v>45.23</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -7897,13 +7897,13 @@
         </is>
       </c>
       <c r="C498" t="n">
-        <v>44.55</v>
+        <v>44.51</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -7912,13 +7912,13 @@
         </is>
       </c>
       <c r="C499" t="n">
-        <v>44.45</v>
+        <v>44.37</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -7927,13 +7927,13 @@
         </is>
       </c>
       <c r="C500" t="n">
-        <v>44.56</v>
+        <v>44.55</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -7942,13 +7942,13 @@
         </is>
       </c>
       <c r="C501" t="n">
-        <v>44.63</v>
+        <v>44.45</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -7957,13 +7957,13 @@
         </is>
       </c>
       <c r="C502" t="n">
-        <v>44.69</v>
+        <v>44.56</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>2024-02-26</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -7972,13 +7972,13 @@
         </is>
       </c>
       <c r="C503" t="n">
-        <v>44.2</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -7987,13 +7987,13 @@
         </is>
       </c>
       <c r="C504" t="n">
-        <v>43.78</v>
+        <v>44.69</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -8002,13 +8002,13 @@
         </is>
       </c>
       <c r="C505" t="n">
-        <v>43.99</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -8017,13 +8017,13 @@
         </is>
       </c>
       <c r="C506" t="n">
-        <v>44</v>
+        <v>43.78</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-22</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -8032,13 +8032,13 @@
         </is>
       </c>
       <c r="C507" t="n">
-        <v>44.35</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -8047,13 +8047,13 @@
         </is>
       </c>
       <c r="C508" t="n">
-        <v>44.52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -8062,13 +8062,13 @@
         </is>
       </c>
       <c r="C509" t="n">
-        <v>44.68</v>
+        <v>44.35</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -8077,13 +8077,13 @@
         </is>
       </c>
       <c r="C510" t="n">
-        <v>45.07</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -8092,13 +8092,13 @@
         </is>
       </c>
       <c r="C511" t="n">
-        <v>45.62</v>
+        <v>44.68</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -8107,13 +8107,13 @@
         </is>
       </c>
       <c r="C512" t="n">
-        <v>45.33</v>
+        <v>45.07</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -8122,13 +8122,13 @@
         </is>
       </c>
       <c r="C513" t="n">
-        <v>45.64</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -8137,13 +8137,13 @@
         </is>
       </c>
       <c r="C514" t="n">
-        <v>45.59</v>
+        <v>45.33</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-09</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -8152,13 +8152,13 @@
         </is>
       </c>
       <c r="C515" t="n">
-        <v>44.61</v>
+        <v>45.64</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -8167,13 +8167,13 @@
         </is>
       </c>
       <c r="C516" t="n">
-        <v>44.2</v>
+        <v>45.59</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -8182,13 +8182,13 @@
         </is>
       </c>
       <c r="C517" t="n">
-        <v>43.73</v>
+        <v>44.61</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -8197,13 +8197,13 @@
         </is>
       </c>
       <c r="C518" t="n">
-        <v>43.66</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -8212,13 +8212,13 @@
         </is>
       </c>
       <c r="C519" t="n">
-        <v>44.07</v>
+        <v>43.73</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -8227,13 +8227,13 @@
         </is>
       </c>
       <c r="C520" t="n">
-        <v>44.66</v>
+        <v>43.66</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -8242,13 +8242,13 @@
         </is>
       </c>
       <c r="C521" t="n">
-        <v>44.75</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -8257,13 +8257,13 @@
         </is>
       </c>
       <c r="C522" t="n">
-        <v>44.73</v>
+        <v>44.66</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024-01-30</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -8272,13 +8272,13 @@
         </is>
       </c>
       <c r="C523" t="n">
-        <v>45.37</v>
+        <v>44.75</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="C524" t="n">
-        <v>45.34</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -8302,13 +8302,13 @@
         </is>
       </c>
       <c r="C525" t="n">
-        <v>45.57</v>
+        <v>45.37</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>2024-01-23</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -8317,13 +8317,13 @@
         </is>
       </c>
       <c r="C526" t="n">
-        <v>45.97</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -8332,13 +8332,13 @@
         </is>
       </c>
       <c r="C527" t="n">
-        <v>45.94</v>
+        <v>45.57</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>2024-01-19</t>
+          <t>2024-01-23</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -8347,13 +8347,13 @@
         </is>
       </c>
       <c r="C528" t="n">
-        <v>45.19</v>
+        <v>45.97</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-22</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -8362,13 +8362,13 @@
         </is>
       </c>
       <c r="C529" t="n">
-        <v>45.44</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="C530" t="n">
-        <v>45.42</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -8392,13 +8392,13 @@
         </is>
       </c>
       <c r="C531" t="n">
-        <v>45.42</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -8407,13 +8407,13 @@
         </is>
       </c>
       <c r="C532" t="n">
-        <v>46.13</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>2024-01-11</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -8422,13 +8422,13 @@
         </is>
       </c>
       <c r="C533" t="n">
-        <v>46.6</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -8437,13 +8437,13 @@
         </is>
       </c>
       <c r="C534" t="n">
-        <v>46.28</v>
+        <v>46.13</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -8452,13 +8452,13 @@
         </is>
       </c>
       <c r="C535" t="n">
-        <v>46.63</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>2024-01-08</t>
+          <t>2024-01-10</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -8467,13 +8467,13 @@
         </is>
       </c>
       <c r="C536" t="n">
-        <v>45.95</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -8482,13 +8482,13 @@
         </is>
       </c>
       <c r="C537" t="n">
-        <v>45.99</v>
+        <v>46.63</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>2024-01-04</t>
+          <t>2024-01-08</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -8497,13 +8497,13 @@
         </is>
       </c>
       <c r="C538" t="n">
-        <v>46.36</v>
+        <v>45.95</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>2024-01-03</t>
+          <t>2024-01-05</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -8512,13 +8512,13 @@
         </is>
       </c>
       <c r="C539" t="n">
-        <v>46.7</v>
+        <v>45.99</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-01-04</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -8527,13 +8527,13 @@
         </is>
       </c>
       <c r="C540" t="n">
-        <v>46.66</v>
+        <v>46.36</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>2023-12-29</t>
+          <t>2024-01-03</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -8542,13 +8542,13 @@
         </is>
       </c>
       <c r="C541" t="n">
-        <v>46.4</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>2023-12-28</t>
+          <t>2024-01-02</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -8557,13 +8557,13 @@
         </is>
       </c>
       <c r="C542" t="n">
-        <v>46.26</v>
+        <v>46.66</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>2023-12-27</t>
+          <t>2023-12-29</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -8572,13 +8572,13 @@
         </is>
       </c>
       <c r="C543" t="n">
-        <v>46.98</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>2023-12-26</t>
+          <t>2023-12-28</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -8587,13 +8587,13 @@
         </is>
       </c>
       <c r="C544" t="n">
-        <v>47.03</v>
+        <v>46.26</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2023-12-27</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -8602,13 +8602,13 @@
         </is>
       </c>
       <c r="C545" t="n">
-        <v>47.28</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2023-12-26</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -8617,13 +8617,13 @@
         </is>
       </c>
       <c r="C546" t="n">
-        <v>47.36</v>
+        <v>47.03</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2023-12-22</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="C547" t="n">
-        <v>48.24</v>
+        <v>47.28</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -8647,13 +8647,13 @@
         </is>
       </c>
       <c r="C548" t="n">
-        <v>48.29</v>
+        <v>47.36</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -8662,13 +8662,13 @@
         </is>
       </c>
       <c r="C549" t="n">
-        <v>48.22</v>
+        <v>48.24</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -8677,21 +8677,51 @@
         </is>
       </c>
       <c r="C550" t="n">
-        <v>47.59</v>
+        <v>48.29</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C551" t="n">
+        <v>48.22</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2023-12-15</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C552" t="n">
+        <v>47.59</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
           <t>2023-12-14</t>
         </is>
       </c>
-      <c r="B551" t="inlineStr">
-        <is>
-          <t>BOK26</t>
-        </is>
-      </c>
-      <c r="C551" t="n">
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C553" t="n">
         <v>47.31</v>
       </c>
     </row>

--- a/data/lseg_excel/BOK26.xlsx
+++ b/data/lseg_excel/BOK26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C553"/>
+  <dimension ref="A1:C567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>60.26</v>
+        <v>65.64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>60.67</v>
+        <v>65.97</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>60.5</v>
+        <v>63.94</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -502,13 +502,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>59.88</v>
+        <v>67.44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>59.3</v>
+        <v>67.42</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>60.09</v>
+        <v>67.16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>59.08</v>
+        <v>65.62</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -562,13 +562,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>57.76</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>57.47</v>
+        <v>66.58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>57.91</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>57.5</v>
+        <v>63.59</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>57.74</v>
+        <v>62.82</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -637,13 +637,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>57.17</v>
+        <v>62.74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -652,13 +652,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>55.84</v>
+        <v>61.85</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -667,13 +667,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>56.17</v>
+        <v>61.76</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -682,13 +682,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>56.18</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -697,13 +697,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>55.03</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -712,13 +712,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>53.74</v>
+        <v>59.88</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>54.06</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -742,13 +742,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>54.58</v>
+        <v>60.09</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>54.85</v>
+        <v>59.08</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -772,13 +772,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>54.95</v>
+        <v>57.76</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>54.42</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -802,13 +802,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>54.52</v>
+        <v>57.91</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>54.33</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>54.54</v>
+        <v>57.74</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -847,13 +847,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>53.11</v>
+        <v>57.17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>53.15</v>
+        <v>55.84</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -877,13 +877,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>53.47</v>
+        <v>56.17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -892,13 +892,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>51.5</v>
+        <v>56.18</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>51.69</v>
+        <v>55.03</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -922,13 +922,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>50.77</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -937,13 +937,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>50.2</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -952,13 +952,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>49.97</v>
+        <v>54.58</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>49.84</v>
+        <v>54.85</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>49.95</v>
+        <v>54.95</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>50.41</v>
+        <v>54.42</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>49.83</v>
+        <v>54.52</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1027,13 +1027,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>49.09</v>
+        <v>54.33</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1042,13 +1042,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>49.94</v>
+        <v>54.54</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>49.8</v>
+        <v>53.11</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>49.73</v>
+        <v>53.15</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>50</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1102,13 +1102,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>49.28</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>49.58</v>
+        <v>51.69</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>48.92</v>
+        <v>50.77</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1147,13 +1147,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>49.1</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1162,13 +1162,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>49.53</v>
+        <v>49.97</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>49.4</v>
+        <v>49.84</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>50.45</v>
+        <v>49.95</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1207,13 +1207,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>51.03</v>
+        <v>50.41</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1222,13 +1222,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>51.68</v>
+        <v>49.83</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1237,13 +1237,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>51.96</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>51.88</v>
+        <v>49.94</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>52.04</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1282,13 +1282,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>52.54</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>52.54</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>53.51</v>
+        <v>49.58</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1342,13 +1342,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>53.16</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1357,13 +1357,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>52.84</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1372,13 +1372,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>51.89</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>51.51</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1402,13 +1402,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>51.41</v>
+        <v>50.45</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>51.47</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>51.83</v>
+        <v>51.68</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1447,13 +1447,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>52.3</v>
+        <v>51.96</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1462,13 +1462,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>53.35</v>
+        <v>51.88</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1477,13 +1477,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>52.36</v>
+        <v>52.04</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>51.46</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>51.56</v>
+        <v>52.63</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1522,13 +1522,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>51.9</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1537,13 +1537,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>52.33</v>
+        <v>53.51</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1552,13 +1552,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>51.8</v>
+        <v>53.16</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1567,13 +1567,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>50.9</v>
+        <v>52.84</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1582,13 +1582,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>50.56</v>
+        <v>51.89</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>50.88</v>
+        <v>51.51</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1612,13 +1612,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>50.76</v>
+        <v>51.41</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1627,13 +1627,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>51.08</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1642,13 +1642,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>50</v>
+        <v>51.83</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1657,13 +1657,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>50.88</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1672,13 +1672,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>51.34</v>
+        <v>53.35</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1687,13 +1687,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>51.46</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1702,13 +1702,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>51.93</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1717,13 +1717,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>51.4</v>
+        <v>51.56</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>51.93</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1747,13 +1747,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>51.21</v>
+        <v>52.33</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1762,13 +1762,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>51.72</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1777,13 +1777,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>52.32</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1792,13 +1792,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>52.09</v>
+        <v>50.56</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1807,13 +1807,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>51.84</v>
+        <v>50.88</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -1822,13 +1822,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>51.73</v>
+        <v>50.76</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>51.47</v>
+        <v>51.08</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1852,13 +1852,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>51.47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1867,13 +1867,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>50.86</v>
+        <v>50.88</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -1882,13 +1882,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>51.84</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1897,13 +1897,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>52.41</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>51.89</v>
+        <v>51.93</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -1927,13 +1927,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>51.33</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -1942,13 +1942,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>51.02</v>
+        <v>51.93</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -1957,13 +1957,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>51.38</v>
+        <v>51.21</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>51.34</v>
+        <v>51.72</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -1987,13 +1987,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>50.46</v>
+        <v>52.32</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2002,13 +2002,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>50.74</v>
+        <v>52.09</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>51.27</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2032,13 +2032,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>51.34</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2047,13 +2047,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>50.92</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2062,13 +2062,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>50.93</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>50.7</v>
+        <v>50.86</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2092,13 +2092,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>51.5</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2107,13 +2107,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>52.03</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2122,13 +2122,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>52.59</v>
+        <v>51.89</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2137,13 +2137,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>53.81</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2152,13 +2152,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>52.98</v>
+        <v>51.02</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2167,13 +2167,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>52.98</v>
+        <v>51.38</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2182,13 +2182,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>52.41</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2197,13 +2197,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>51.85</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2212,13 +2212,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>51.41</v>
+        <v>50.74</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2227,13 +2227,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>52.36</v>
+        <v>51.27</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2242,13 +2242,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>52.02</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2257,13 +2257,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>52.63</v>
+        <v>50.92</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2272,13 +2272,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>52.54</v>
+        <v>50.93</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>53.3</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2302,13 +2302,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>52.79</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2317,13 +2317,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>53.07</v>
+        <v>52.03</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2332,13 +2332,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>53.82</v>
+        <v>52.59</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>53.93</v>
+        <v>53.81</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2362,13 +2362,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>55.12</v>
+        <v>52.98</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>55.41</v>
+        <v>52.98</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -2392,13 +2392,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>54.01</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -2407,13 +2407,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>51.87</v>
+        <v>51.85</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -2422,13 +2422,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>52.23</v>
+        <v>51.41</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -2437,13 +2437,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>53.59</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -2452,13 +2452,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>53.31</v>
+        <v>52.02</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -2467,13 +2467,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>52.27</v>
+        <v>52.63</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -2482,13 +2482,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>53.3</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -2497,13 +2497,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>53</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -2512,13 +2512,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>52.87</v>
+        <v>52.79</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -2527,13 +2527,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>52.46</v>
+        <v>53.07</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>53.33</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -2557,13 +2557,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>53.53</v>
+        <v>53.93</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -2572,13 +2572,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>53.25</v>
+        <v>55.12</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -2587,13 +2587,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>53.87</v>
+        <v>55.41</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -2602,13 +2602,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>53.61</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>54.32</v>
+        <v>51.87</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -2632,13 +2632,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>55.55</v>
+        <v>52.23</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>56.24</v>
+        <v>53.59</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -2662,13 +2662,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>55.61</v>
+        <v>53.31</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -2677,13 +2677,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>55.47</v>
+        <v>52.27</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -2692,13 +2692,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>55.8</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -2707,13 +2707,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>55.34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -2722,13 +2722,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>54.93</v>
+        <v>52.87</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -2737,13 +2737,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>55.29</v>
+        <v>52.46</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -2752,13 +2752,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>55.02</v>
+        <v>53.33</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -2767,13 +2767,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>55.59</v>
+        <v>53.53</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -2782,13 +2782,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>54.31</v>
+        <v>53.25</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -2797,13 +2797,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>54.1</v>
+        <v>53.87</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -2812,13 +2812,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>53.8</v>
+        <v>53.61</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -2827,13 +2827,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>53.47</v>
+        <v>54.32</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -2842,13 +2842,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>53.38</v>
+        <v>55.55</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -2857,13 +2857,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>53.17</v>
+        <v>56.24</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -2872,13 +2872,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>53.82</v>
+        <v>55.61</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>53.64</v>
+        <v>55.47</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -2902,13 +2902,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>54.46</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>54.77</v>
+        <v>55.34</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -2932,13 +2932,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>53.48</v>
+        <v>54.93</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -2947,13 +2947,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>52.62</v>
+        <v>55.29</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -2962,13 +2962,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>52.52</v>
+        <v>55.02</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -2977,13 +2977,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>52.86</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -2992,13 +2992,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>52.43</v>
+        <v>54.31</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3007,13 +3007,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>52.69</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3022,13 +3022,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>53.79</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -3037,13 +3037,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>55.04</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -3052,13 +3052,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>55.23</v>
+        <v>53.38</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>55.16</v>
+        <v>53.17</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -3082,13 +3082,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>55.1</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3097,13 +3097,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>51.65</v>
+        <v>53.64</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -3112,13 +3112,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>48.65</v>
+        <v>54.46</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -3127,13 +3127,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>48.94</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -3142,13 +3142,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>48.82</v>
+        <v>53.48</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -3157,13 +3157,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>48.46</v>
+        <v>52.62</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -3172,13 +3172,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>48.62</v>
+        <v>52.52</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -3187,13 +3187,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>47.95</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -3202,13 +3202,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>47.8</v>
+        <v>52.43</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -3217,13 +3217,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>47.85</v>
+        <v>52.69</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -3232,13 +3232,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>47.49</v>
+        <v>53.79</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -3247,13 +3247,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>47.78</v>
+        <v>55.04</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -3262,13 +3262,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>49.05</v>
+        <v>55.23</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>49.41</v>
+        <v>55.16</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -3292,13 +3292,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>50.03</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -3307,13 +3307,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>49.88</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -3322,13 +3322,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>49.73</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -3337,13 +3337,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>50.23</v>
+        <v>48.94</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -3352,13 +3352,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>49.88</v>
+        <v>48.82</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -3367,13 +3367,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>49.78</v>
+        <v>48.46</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -3382,13 +3382,13 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>49.2</v>
+        <v>48.62</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>48.9</v>
+        <v>47.95</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -3412,13 +3412,13 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>51.9</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -3427,13 +3427,13 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>51.46</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -3442,13 +3442,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>50.03</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -3457,13 +3457,13 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>48.66</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -3472,13 +3472,13 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>48.38</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -3487,13 +3487,13 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>47.52</v>
+        <v>49.41</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -3502,13 +3502,13 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>48.22</v>
+        <v>50.03</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>48.33</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -3532,13 +3532,13 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>48.82</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -3547,13 +3547,13 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>48.95</v>
+        <v>50.23</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -3562,13 +3562,13 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>48.22</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -3577,13 +3577,13 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>48.75</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -3592,13 +3592,13 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>49.78</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -3607,13 +3607,13 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>49.23</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -3622,13 +3622,13 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>49.17</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -3637,13 +3637,13 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>47.85</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -3652,13 +3652,13 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>47.78</v>
+        <v>50.03</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>47.83</v>
+        <v>48.66</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -3682,13 +3682,13 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>47.91</v>
+        <v>48.38</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -3697,13 +3697,13 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>47.73</v>
+        <v>47.52</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -3712,13 +3712,13 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>47.54</v>
+        <v>48.22</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -3727,13 +3727,13 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>46.72</v>
+        <v>48.33</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -3742,13 +3742,13 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>47.16</v>
+        <v>48.82</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -3757,13 +3757,13 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>46.15</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -3772,13 +3772,13 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>46.11</v>
+        <v>48.22</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -3787,13 +3787,13 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>44.82</v>
+        <v>48.75</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>45.02</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -3817,13 +3817,13 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>45.96</v>
+        <v>49.23</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -3832,13 +3832,13 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>47.35</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -3847,13 +3847,13 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>48.65</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -3862,13 +3862,13 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>47.87</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -3877,13 +3877,13 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>46</v>
+        <v>47.83</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -3892,13 +3892,13 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>46.11</v>
+        <v>47.91</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -3907,13 +3907,13 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>45.42</v>
+        <v>47.73</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -3922,13 +3922,13 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>44.2</v>
+        <v>47.54</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -3937,13 +3937,13 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>43.82</v>
+        <v>46.72</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -3952,13 +3952,13 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>43.48</v>
+        <v>47.16</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -3967,13 +3967,13 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>43.28</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -3982,13 +3982,13 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>43.7</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -3997,13 +3997,13 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>43.32</v>
+        <v>44.82</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -4012,13 +4012,13 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>43.28</v>
+        <v>45.02</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -4027,13 +4027,13 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>42.9</v>
+        <v>45.96</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -4042,13 +4042,13 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>42.51</v>
+        <v>47.35</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -4057,13 +4057,13 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>42.36</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -4072,13 +4072,13 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>42.65</v>
+        <v>47.87</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -4087,13 +4087,13 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>42.85</v>
+        <v>46</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -4102,13 +4102,13 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>43.04</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -4117,13 +4117,13 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>43.92</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -4132,13 +4132,13 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>43.52</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -4147,13 +4147,13 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>43.37</v>
+        <v>43.82</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -4162,13 +4162,13 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>43.24</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -4177,13 +4177,13 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>43.99</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -4192,13 +4192,13 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>44.52</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -4207,13 +4207,13 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>45.66</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -4222,13 +4222,13 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>45.78</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -4237,13 +4237,13 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>46.1</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -4252,13 +4252,13 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>46.42</v>
+        <v>42.51</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -4267,13 +4267,13 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>47.21</v>
+        <v>42.36</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -4282,13 +4282,13 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>47.44</v>
+        <v>42.65</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -4297,13 +4297,13 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>46.5</v>
+        <v>42.85</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -4312,13 +4312,13 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>47.21</v>
+        <v>43.04</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -4327,13 +4327,13 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>46.08</v>
+        <v>43.92</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>46.21</v>
+        <v>43.52</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -4357,13 +4357,13 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>45.72</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -4372,13 +4372,13 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>46.29</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -4387,13 +4387,13 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>45.9</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -4402,13 +4402,13 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>46.05</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -4417,13 +4417,13 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>45.73</v>
+        <v>45.66</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -4432,13 +4432,13 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>45.31</v>
+        <v>45.78</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -4447,13 +4447,13 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>45.75</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -4462,13 +4462,13 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>46.37</v>
+        <v>46.42</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -4477,13 +4477,13 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>45.77</v>
+        <v>47.21</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -4492,13 +4492,13 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>45.1</v>
+        <v>47.44</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -4507,13 +4507,13 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>44.97</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -4522,13 +4522,13 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>45.11</v>
+        <v>47.21</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -4537,13 +4537,13 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>44.88</v>
+        <v>46.08</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -4552,13 +4552,13 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>45.06</v>
+        <v>46.21</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -4567,13 +4567,13 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>44.73</v>
+        <v>45.72</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -4582,13 +4582,13 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>44.3</v>
+        <v>46.29</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -4597,13 +4597,13 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>45.15</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -4612,13 +4612,13 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>45.27</v>
+        <v>46.05</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -4627,13 +4627,13 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>45.03</v>
+        <v>45.73</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -4642,13 +4642,13 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>45.99</v>
+        <v>45.31</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -4657,13 +4657,13 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>46.22</v>
+        <v>45.75</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -4672,13 +4672,13 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>46.06</v>
+        <v>46.37</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -4687,13 +4687,13 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>45.62</v>
+        <v>45.77</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -4702,13 +4702,13 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>43.48</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>42.45</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -4732,13 +4732,13 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>42.17</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -4747,13 +4747,13 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>41.34</v>
+        <v>44.88</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -4762,13 +4762,13 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>40.87</v>
+        <v>45.06</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -4777,13 +4777,13 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>41.09</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -4792,13 +4792,13 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>41.32</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -4807,13 +4807,13 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>41.19</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -4822,13 +4822,13 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>40.94</v>
+        <v>45.27</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -4837,13 +4837,13 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>40.94</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2024-12-24</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -4852,13 +4852,13 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>41.38</v>
+        <v>45.99</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -4867,13 +4867,13 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>41.62</v>
+        <v>46.22</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -4882,13 +4882,13 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>40.87</v>
+        <v>46.06</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -4897,13 +4897,13 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>41.15</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -4912,13 +4912,13 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>40.92</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -4927,13 +4927,13 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>41.73</v>
+        <v>42.45</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -4942,13 +4942,13 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>42.72</v>
+        <v>42.17</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -4957,13 +4957,13 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>43.49</v>
+        <v>41.34</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -4972,13 +4972,13 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>43.53</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -4987,13 +4987,13 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>43.26</v>
+        <v>41.09</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>43.46</v>
+        <v>41.32</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -5017,13 +5017,13 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>43.52</v>
+        <v>41.19</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>43.58</v>
+        <v>40.94</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -5047,13 +5047,13 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>42.89</v>
+        <v>40.94</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>42.12</v>
+        <v>41.38</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -5077,13 +5077,13 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>42.67</v>
+        <v>41.62</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -5092,13 +5092,13 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>42.3</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -5107,13 +5107,13 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>42.39</v>
+        <v>41.15</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -5122,13 +5122,13 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>41.84</v>
+        <v>40.92</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -5137,13 +5137,13 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>43.17</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -5152,13 +5152,13 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>42.27</v>
+        <v>42.72</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -5167,13 +5167,13 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>42.78</v>
+        <v>43.49</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -5182,13 +5182,13 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>43.09</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -5197,13 +5197,13 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>43.95</v>
+        <v>43.26</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -5212,13 +5212,13 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>44.91</v>
+        <v>43.46</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -5227,13 +5227,13 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>45.32</v>
+        <v>43.52</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -5242,13 +5242,13 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>45.24</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -5257,13 +5257,13 @@
         </is>
       </c>
       <c r="C322" t="n">
-        <v>44.48</v>
+        <v>42.89</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -5272,13 +5272,13 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>45.38</v>
+        <v>42.12</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -5287,13 +5287,13 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>46.24</v>
+        <v>42.67</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -5302,13 +5302,13 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>47.78</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -5317,13 +5317,13 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>48.04</v>
+        <v>42.39</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>47.49</v>
+        <v>41.84</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -5347,13 +5347,13 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>45.65</v>
+        <v>43.17</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>45.01</v>
+        <v>42.27</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -5377,13 +5377,13 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>45.36</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -5392,13 +5392,13 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>45.49</v>
+        <v>43.09</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -5407,13 +5407,13 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>44.54</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -5422,13 +5422,13 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>43.62</v>
+        <v>44.91</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -5437,13 +5437,13 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>42.78</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -5452,13 +5452,13 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>42.73</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -5467,13 +5467,13 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>43.65</v>
+        <v>44.48</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -5482,13 +5482,13 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>43.48</v>
+        <v>45.38</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -5497,13 +5497,13 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>42.77</v>
+        <v>46.24</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -5512,13 +5512,13 @@
         </is>
       </c>
       <c r="C339" t="n">
-        <v>42.86</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -5527,13 +5527,13 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>41.8</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -5542,13 +5542,13 @@
         </is>
       </c>
       <c r="C341" t="n">
-        <v>41.24</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -5557,13 +5557,13 @@
         </is>
       </c>
       <c r="C342" t="n">
-        <v>41.92</v>
+        <v>45.65</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -5572,13 +5572,13 @@
         </is>
       </c>
       <c r="C343" t="n">
-        <v>41.59</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -5587,13 +5587,13 @@
         </is>
       </c>
       <c r="C344" t="n">
-        <v>42.03</v>
+        <v>45.36</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -5602,13 +5602,13 @@
         </is>
       </c>
       <c r="C345" t="n">
-        <v>42.03</v>
+        <v>45.49</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -5617,13 +5617,13 @@
         </is>
       </c>
       <c r="C346" t="n">
-        <v>43.28</v>
+        <v>44.54</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>43.74</v>
+        <v>43.62</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -5647,13 +5647,13 @@
         </is>
       </c>
       <c r="C348" t="n">
-        <v>43.16</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -5662,13 +5662,13 @@
         </is>
       </c>
       <c r="C349" t="n">
-        <v>43.22</v>
+        <v>42.73</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -5677,13 +5677,13 @@
         </is>
       </c>
       <c r="C350" t="n">
-        <v>44.73</v>
+        <v>43.65</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -5692,13 +5692,13 @@
         </is>
       </c>
       <c r="C351" t="n">
-        <v>44.08</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -5707,13 +5707,13 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>44.43</v>
+        <v>42.77</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -5722,13 +5722,13 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>43.57</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -5737,13 +5737,13 @@
         </is>
       </c>
       <c r="C354" t="n">
-        <v>43.08</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -5752,13 +5752,13 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>43.05</v>
+        <v>41.24</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -5767,13 +5767,13 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>42.78</v>
+        <v>41.92</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -5782,13 +5782,13 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>43.53</v>
+        <v>41.59</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>43.71</v>
+        <v>42.03</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>43.14</v>
+        <v>42.03</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -5827,13 +5827,13 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>42.09</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -5842,13 +5842,13 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>41.73</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -5857,13 +5857,13 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>41.43</v>
+        <v>43.16</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -5872,13 +5872,13 @@
         </is>
       </c>
       <c r="C363" t="n">
-        <v>41.17</v>
+        <v>43.22</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -5887,13 +5887,13 @@
         </is>
       </c>
       <c r="C364" t="n">
-        <v>40.69</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -5902,13 +5902,13 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>40.11</v>
+        <v>44.08</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -5917,13 +5917,13 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>40.12</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -5932,13 +5932,13 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>40.75</v>
+        <v>43.57</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -5947,13 +5947,13 @@
         </is>
       </c>
       <c r="C368" t="n">
-        <v>40.39</v>
+        <v>43.08</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -5962,13 +5962,13 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>40.6</v>
+        <v>43.05</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -5977,13 +5977,13 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>41.29</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -5992,13 +5992,13 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>40.49</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -6007,13 +6007,13 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>41.62</v>
+        <v>43.71</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -6022,13 +6022,13 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>40.98</v>
+        <v>43.14</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -6037,13 +6037,13 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>41.5</v>
+        <v>42.09</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -6052,13 +6052,13 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>42.26</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -6067,13 +6067,13 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>42.24</v>
+        <v>41.43</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -6082,13 +6082,13 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>41.21</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -6097,13 +6097,13 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>40.93</v>
+        <v>40.69</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -6112,13 +6112,13 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>40.83</v>
+        <v>40.11</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -6127,13 +6127,13 @@
         </is>
       </c>
       <c r="C380" t="n">
-        <v>40.51</v>
+        <v>40.12</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -6142,13 +6142,13 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>39.52</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -6157,13 +6157,13 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>40.05</v>
+        <v>40.39</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -6172,13 +6172,13 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>39.68</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -6187,13 +6187,13 @@
         </is>
       </c>
       <c r="C384" t="n">
-        <v>39.76</v>
+        <v>41.29</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -6202,13 +6202,13 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>39.55</v>
+        <v>40.49</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -6217,13 +6217,13 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>39.29</v>
+        <v>41.62</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -6232,13 +6232,13 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>39.58</v>
+        <v>40.98</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -6247,13 +6247,13 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>39.89</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -6262,13 +6262,13 @@
         </is>
       </c>
       <c r="C389" t="n">
-        <v>40.84</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -6277,13 +6277,13 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>40.75</v>
+        <v>42.24</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -6292,13 +6292,13 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>40.68</v>
+        <v>41.21</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -6307,13 +6307,13 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>40.51</v>
+        <v>40.93</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -6322,13 +6322,13 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>40.16</v>
+        <v>40.83</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -6337,13 +6337,13 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>40.25</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -6352,13 +6352,13 @@
         </is>
       </c>
       <c r="C395" t="n">
-        <v>40.91</v>
+        <v>39.52</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -6367,13 +6367,13 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>41.18</v>
+        <v>40.05</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -6382,13 +6382,13 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>41.72</v>
+        <v>39.68</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -6397,13 +6397,13 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>41.2</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -6412,13 +6412,13 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>41.67</v>
+        <v>39.55</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -6427,13 +6427,13 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>41.34</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -6442,13 +6442,13 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>42.82</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -6457,13 +6457,13 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>42.57</v>
+        <v>39.89</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -6472,13 +6472,13 @@
         </is>
       </c>
       <c r="C403" t="n">
-        <v>43.28</v>
+        <v>40.84</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -6487,13 +6487,13 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>42.86</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -6502,13 +6502,13 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>41.96</v>
+        <v>40.68</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -6517,13 +6517,13 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>42.63</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -6532,13 +6532,13 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>42.6</v>
+        <v>40.16</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>43.39</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -6562,13 +6562,13 @@
         </is>
       </c>
       <c r="C409" t="n">
-        <v>43.49</v>
+        <v>40.91</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -6577,13 +6577,13 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>44.6</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -6592,13 +6592,13 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>45.01</v>
+        <v>41.72</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -6607,13 +6607,13 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>44.73</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -6622,13 +6622,13 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>45.87</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -6637,13 +6637,13 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>46.97</v>
+        <v>41.34</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -6652,13 +6652,13 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>47.02</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -6667,13 +6667,13 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>46.75</v>
+        <v>42.57</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -6682,13 +6682,13 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>45.79</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -6697,13 +6697,13 @@
         </is>
       </c>
       <c r="C418" t="n">
-        <v>44.84</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -6712,13 +6712,13 @@
         </is>
       </c>
       <c r="C419" t="n">
-        <v>43.13</v>
+        <v>41.96</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -6727,13 +6727,13 @@
         </is>
       </c>
       <c r="C420" t="n">
-        <v>42.97</v>
+        <v>42.63</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -6742,13 +6742,13 @@
         </is>
       </c>
       <c r="C421" t="n">
-        <v>43.37</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -6757,13 +6757,13 @@
         </is>
       </c>
       <c r="C422" t="n">
-        <v>42.71</v>
+        <v>43.39</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -6772,13 +6772,13 @@
         </is>
       </c>
       <c r="C423" t="n">
-        <v>43.35</v>
+        <v>43.49</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -6787,13 +6787,13 @@
         </is>
       </c>
       <c r="C424" t="n">
-        <v>43.58</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -6802,13 +6802,13 @@
         </is>
       </c>
       <c r="C425" t="n">
-        <v>43.59</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -6817,13 +6817,13 @@
         </is>
       </c>
       <c r="C426" t="n">
-        <v>44.01</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -6832,13 +6832,13 @@
         </is>
       </c>
       <c r="C427" t="n">
-        <v>43.56</v>
+        <v>45.87</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="C428" t="n">
-        <v>43.53</v>
+        <v>46.97</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -6862,13 +6862,13 @@
         </is>
       </c>
       <c r="C429" t="n">
-        <v>43.76</v>
+        <v>47.02</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -6877,13 +6877,13 @@
         </is>
       </c>
       <c r="C430" t="n">
-        <v>43.87</v>
+        <v>46.75</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -6892,13 +6892,13 @@
         </is>
       </c>
       <c r="C431" t="n">
-        <v>43.76</v>
+        <v>45.79</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -6907,13 +6907,13 @@
         </is>
       </c>
       <c r="C432" t="n">
-        <v>43.98</v>
+        <v>44.84</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -6922,13 +6922,13 @@
         </is>
       </c>
       <c r="C433" t="n">
-        <v>44.29</v>
+        <v>43.13</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -6937,13 +6937,13 @@
         </is>
       </c>
       <c r="C434" t="n">
-        <v>44.83</v>
+        <v>42.97</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -6952,13 +6952,13 @@
         </is>
       </c>
       <c r="C435" t="n">
-        <v>43.88</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -6967,13 +6967,13 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>44.2</v>
+        <v>42.71</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -6982,13 +6982,13 @@
         </is>
       </c>
       <c r="C437" t="n">
-        <v>44.63</v>
+        <v>43.35</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -6997,13 +6997,13 @@
         </is>
       </c>
       <c r="C438" t="n">
-        <v>45.81</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -7012,13 +7012,13 @@
         </is>
       </c>
       <c r="C439" t="n">
-        <v>45.93</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -7027,13 +7027,13 @@
         </is>
       </c>
       <c r="C440" t="n">
-        <v>46.11</v>
+        <v>44.01</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -7042,13 +7042,13 @@
         </is>
       </c>
       <c r="C441" t="n">
-        <v>45.74</v>
+        <v>43.56</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -7057,13 +7057,13 @@
         </is>
       </c>
       <c r="C442" t="n">
-        <v>45.32</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -7072,13 +7072,13 @@
         </is>
       </c>
       <c r="C443" t="n">
-        <v>45.96</v>
+        <v>43.76</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -7087,13 +7087,13 @@
         </is>
       </c>
       <c r="C444" t="n">
-        <v>46.2</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -7102,13 +7102,13 @@
         </is>
       </c>
       <c r="C445" t="n">
-        <v>46.37</v>
+        <v>43.76</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -7117,13 +7117,13 @@
         </is>
       </c>
       <c r="C446" t="n">
-        <v>46.6</v>
+        <v>43.98</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -7132,13 +7132,13 @@
         </is>
       </c>
       <c r="C447" t="n">
-        <v>45.89</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -7147,13 +7147,13 @@
         </is>
       </c>
       <c r="C448" t="n">
-        <v>45.45</v>
+        <v>44.83</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -7162,13 +7162,13 @@
         </is>
       </c>
       <c r="C449" t="n">
-        <v>44.82</v>
+        <v>43.88</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -7177,13 +7177,13 @@
         </is>
       </c>
       <c r="C450" t="n">
-        <v>44.7</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -7192,13 +7192,13 @@
         </is>
       </c>
       <c r="C451" t="n">
-        <v>46.01</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="C452" t="n">
-        <v>45.24</v>
+        <v>45.81</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -7222,13 +7222,13 @@
         </is>
       </c>
       <c r="C453" t="n">
-        <v>44.2</v>
+        <v>45.93</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -7237,13 +7237,13 @@
         </is>
       </c>
       <c r="C454" t="n">
-        <v>44.8</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="C455" t="n">
-        <v>45.29</v>
+        <v>45.74</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -7267,13 +7267,13 @@
         </is>
       </c>
       <c r="C456" t="n">
-        <v>44.66</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -7282,13 +7282,13 @@
         </is>
       </c>
       <c r="C457" t="n">
-        <v>44.34</v>
+        <v>45.96</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -7297,13 +7297,13 @@
         </is>
       </c>
       <c r="C458" t="n">
-        <v>44.43</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -7312,13 +7312,13 @@
         </is>
       </c>
       <c r="C459" t="n">
-        <v>44.49</v>
+        <v>46.37</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -7327,13 +7327,13 @@
         </is>
       </c>
       <c r="C460" t="n">
-        <v>44.32</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -7342,13 +7342,13 @@
         </is>
       </c>
       <c r="C461" t="n">
-        <v>45.01</v>
+        <v>45.89</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -7357,13 +7357,13 @@
         </is>
       </c>
       <c r="C462" t="n">
-        <v>45.94</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -7372,13 +7372,13 @@
         </is>
       </c>
       <c r="C463" t="n">
-        <v>45.67</v>
+        <v>44.82</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -7387,13 +7387,13 @@
         </is>
       </c>
       <c r="C464" t="n">
-        <v>45.58</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -7402,13 +7402,13 @@
         </is>
       </c>
       <c r="C465" t="n">
-        <v>45.95</v>
+        <v>46.01</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -7417,13 +7417,13 @@
         </is>
       </c>
       <c r="C466" t="n">
-        <v>45.8</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -7432,13 +7432,13 @@
         </is>
       </c>
       <c r="C467" t="n">
-        <v>45.14</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -7447,13 +7447,13 @@
         </is>
       </c>
       <c r="C468" t="n">
-        <v>44.97</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="C469" t="n">
-        <v>45.19</v>
+        <v>45.29</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -7477,13 +7477,13 @@
         </is>
       </c>
       <c r="C470" t="n">
-        <v>45.34</v>
+        <v>44.66</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -7492,13 +7492,13 @@
         </is>
       </c>
       <c r="C471" t="n">
-        <v>45.6</v>
+        <v>44.34</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -7507,13 +7507,13 @@
         </is>
       </c>
       <c r="C472" t="n">
-        <v>45.97</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -7522,13 +7522,13 @@
         </is>
       </c>
       <c r="C473" t="n">
-        <v>45.91</v>
+        <v>44.49</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -7537,13 +7537,13 @@
         </is>
       </c>
       <c r="C474" t="n">
-        <v>46.95</v>
+        <v>44.32</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -7552,13 +7552,13 @@
         </is>
       </c>
       <c r="C475" t="n">
-        <v>46.91</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -7567,13 +7567,13 @@
         </is>
       </c>
       <c r="C476" t="n">
-        <v>47.23</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -7582,13 +7582,13 @@
         </is>
       </c>
       <c r="C477" t="n">
-        <v>47.84</v>
+        <v>45.67</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -7597,13 +7597,13 @@
         </is>
       </c>
       <c r="C478" t="n">
-        <v>47.38</v>
+        <v>45.58</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -7612,13 +7612,13 @@
         </is>
       </c>
       <c r="C479" t="n">
-        <v>48</v>
+        <v>45.95</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -7627,13 +7627,13 @@
         </is>
       </c>
       <c r="C480" t="n">
-        <v>47.67</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -7642,13 +7642,13 @@
         </is>
       </c>
       <c r="C481" t="n">
-        <v>47.12</v>
+        <v>45.14</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -7657,13 +7657,13 @@
         </is>
       </c>
       <c r="C482" t="n">
-        <v>47.14</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -7672,13 +7672,13 @@
         </is>
       </c>
       <c r="C483" t="n">
-        <v>46.67</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -7687,13 +7687,13 @@
         </is>
       </c>
       <c r="C484" t="n">
-        <v>47.46</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -7702,13 +7702,13 @@
         </is>
       </c>
       <c r="C485" t="n">
-        <v>47.71</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -7717,13 +7717,13 @@
         </is>
       </c>
       <c r="C486" t="n">
-        <v>46.65</v>
+        <v>45.97</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -7732,13 +7732,13 @@
         </is>
       </c>
       <c r="C487" t="n">
-        <v>47.72</v>
+        <v>45.91</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -7747,13 +7747,13 @@
         </is>
       </c>
       <c r="C488" t="n">
-        <v>47.89</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -7762,13 +7762,13 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>47.23</v>
+        <v>46.91</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -7777,13 +7777,13 @@
         </is>
       </c>
       <c r="C490" t="n">
-        <v>47.63</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -7792,13 +7792,13 @@
         </is>
       </c>
       <c r="C491" t="n">
-        <v>48.16</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="C492" t="n">
-        <v>47.08</v>
+        <v>47.38</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -7822,13 +7822,13 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>47.34</v>
+        <v>48</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -7837,13 +7837,13 @@
         </is>
       </c>
       <c r="C494" t="n">
-        <v>46.61</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -7852,13 +7852,13 @@
         </is>
       </c>
       <c r="C495" t="n">
-        <v>45.84</v>
+        <v>47.12</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -7867,13 +7867,13 @@
         </is>
       </c>
       <c r="C496" t="n">
-        <v>45.28</v>
+        <v>47.14</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -7882,13 +7882,13 @@
         </is>
       </c>
       <c r="C497" t="n">
-        <v>45.23</v>
+        <v>46.67</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -7897,13 +7897,13 @@
         </is>
       </c>
       <c r="C498" t="n">
-        <v>44.51</v>
+        <v>47.46</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -7912,13 +7912,13 @@
         </is>
       </c>
       <c r="C499" t="n">
-        <v>44.37</v>
+        <v>47.71</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -7927,13 +7927,13 @@
         </is>
       </c>
       <c r="C500" t="n">
-        <v>44.55</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -7942,13 +7942,13 @@
         </is>
       </c>
       <c r="C501" t="n">
-        <v>44.45</v>
+        <v>47.72</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -7957,13 +7957,13 @@
         </is>
       </c>
       <c r="C502" t="n">
-        <v>44.56</v>
+        <v>47.89</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -7972,13 +7972,13 @@
         </is>
       </c>
       <c r="C503" t="n">
-        <v>44.63</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -7987,13 +7987,13 @@
         </is>
       </c>
       <c r="C504" t="n">
-        <v>44.69</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>2024-02-26</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -8002,13 +8002,13 @@
         </is>
       </c>
       <c r="C505" t="n">
-        <v>44.2</v>
+        <v>48.16</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -8017,13 +8017,13 @@
         </is>
       </c>
       <c r="C506" t="n">
-        <v>43.78</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -8032,13 +8032,13 @@
         </is>
       </c>
       <c r="C507" t="n">
-        <v>43.99</v>
+        <v>47.34</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -8047,13 +8047,13 @@
         </is>
       </c>
       <c r="C508" t="n">
-        <v>44</v>
+        <v>46.61</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -8062,13 +8062,13 @@
         </is>
       </c>
       <c r="C509" t="n">
-        <v>44.35</v>
+        <v>45.84</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -8077,13 +8077,13 @@
         </is>
       </c>
       <c r="C510" t="n">
-        <v>44.52</v>
+        <v>45.28</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -8092,13 +8092,13 @@
         </is>
       </c>
       <c r="C511" t="n">
-        <v>44.68</v>
+        <v>45.23</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -8107,13 +8107,13 @@
         </is>
       </c>
       <c r="C512" t="n">
-        <v>45.07</v>
+        <v>44.51</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -8122,13 +8122,13 @@
         </is>
       </c>
       <c r="C513" t="n">
-        <v>45.62</v>
+        <v>44.37</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -8137,13 +8137,13 @@
         </is>
       </c>
       <c r="C514" t="n">
-        <v>45.33</v>
+        <v>44.55</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -8152,13 +8152,13 @@
         </is>
       </c>
       <c r="C515" t="n">
-        <v>45.64</v>
+        <v>44.45</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -8167,13 +8167,13 @@
         </is>
       </c>
       <c r="C516" t="n">
-        <v>45.59</v>
+        <v>44.56</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -8182,13 +8182,13 @@
         </is>
       </c>
       <c r="C517" t="n">
-        <v>44.61</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -8197,13 +8197,13 @@
         </is>
       </c>
       <c r="C518" t="n">
-        <v>44.2</v>
+        <v>44.69</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -8212,13 +8212,13 @@
         </is>
       </c>
       <c r="C519" t="n">
-        <v>43.73</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -8227,13 +8227,13 @@
         </is>
       </c>
       <c r="C520" t="n">
-        <v>43.66</v>
+        <v>43.78</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-22</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -8242,13 +8242,13 @@
         </is>
       </c>
       <c r="C521" t="n">
-        <v>44.07</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -8257,13 +8257,13 @@
         </is>
       </c>
       <c r="C522" t="n">
-        <v>44.66</v>
+        <v>44</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -8272,13 +8272,13 @@
         </is>
       </c>
       <c r="C523" t="n">
-        <v>44.75</v>
+        <v>44.35</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="C524" t="n">
-        <v>44.73</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -8302,13 +8302,13 @@
         </is>
       </c>
       <c r="C525" t="n">
-        <v>45.37</v>
+        <v>44.68</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -8317,13 +8317,13 @@
         </is>
       </c>
       <c r="C526" t="n">
-        <v>45.34</v>
+        <v>45.07</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -8332,13 +8332,13 @@
         </is>
       </c>
       <c r="C527" t="n">
-        <v>45.57</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>2024-01-23</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -8347,13 +8347,13 @@
         </is>
       </c>
       <c r="C528" t="n">
-        <v>45.97</v>
+        <v>45.33</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2024-02-09</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -8362,13 +8362,13 @@
         </is>
       </c>
       <c r="C529" t="n">
-        <v>45.94</v>
+        <v>45.64</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>2024-01-19</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="C530" t="n">
-        <v>45.19</v>
+        <v>45.59</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -8392,13 +8392,13 @@
         </is>
       </c>
       <c r="C531" t="n">
-        <v>45.44</v>
+        <v>44.61</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -8407,13 +8407,13 @@
         </is>
       </c>
       <c r="C532" t="n">
-        <v>45.42</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -8422,13 +8422,13 @@
         </is>
       </c>
       <c r="C533" t="n">
-        <v>45.42</v>
+        <v>43.73</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -8437,13 +8437,13 @@
         </is>
       </c>
       <c r="C534" t="n">
-        <v>46.13</v>
+        <v>43.66</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>2024-01-11</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -8452,13 +8452,13 @@
         </is>
       </c>
       <c r="C535" t="n">
-        <v>46.6</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -8467,13 +8467,13 @@
         </is>
       </c>
       <c r="C536" t="n">
-        <v>46.28</v>
+        <v>44.66</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-30</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -8482,13 +8482,13 @@
         </is>
       </c>
       <c r="C537" t="n">
-        <v>46.63</v>
+        <v>44.75</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>2024-01-08</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -8497,13 +8497,13 @@
         </is>
       </c>
       <c r="C538" t="n">
-        <v>45.95</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -8512,13 +8512,13 @@
         </is>
       </c>
       <c r="C539" t="n">
-        <v>45.99</v>
+        <v>45.37</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>2024-01-04</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -8527,13 +8527,13 @@
         </is>
       </c>
       <c r="C540" t="n">
-        <v>46.36</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>2024-01-03</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -8542,13 +8542,13 @@
         </is>
       </c>
       <c r="C541" t="n">
-        <v>46.7</v>
+        <v>45.57</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-01-23</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -8557,13 +8557,13 @@
         </is>
       </c>
       <c r="C542" t="n">
-        <v>46.66</v>
+        <v>45.97</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>2023-12-29</t>
+          <t>2024-01-22</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -8572,13 +8572,13 @@
         </is>
       </c>
       <c r="C543" t="n">
-        <v>46.4</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>2023-12-28</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -8587,13 +8587,13 @@
         </is>
       </c>
       <c r="C544" t="n">
-        <v>46.26</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>2023-12-27</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -8602,13 +8602,13 @@
         </is>
       </c>
       <c r="C545" t="n">
-        <v>46.98</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>2023-12-26</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -8617,13 +8617,13 @@
         </is>
       </c>
       <c r="C546" t="n">
-        <v>47.03</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="C547" t="n">
-        <v>47.28</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -8647,13 +8647,13 @@
         </is>
       </c>
       <c r="C548" t="n">
-        <v>47.36</v>
+        <v>46.13</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -8662,13 +8662,13 @@
         </is>
       </c>
       <c r="C549" t="n">
-        <v>48.24</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2024-01-10</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -8677,13 +8677,13 @@
         </is>
       </c>
       <c r="C550" t="n">
-        <v>48.29</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -8692,13 +8692,13 @@
         </is>
       </c>
       <c r="C551" t="n">
-        <v>48.22</v>
+        <v>46.63</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2024-01-08</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -8707,21 +8707,231 @@
         </is>
       </c>
       <c r="C552" t="n">
-        <v>47.59</v>
+        <v>45.95</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
+          <t>2024-01-05</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C553" t="n">
+        <v>45.99</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2024-01-04</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C554" t="n">
+        <v>46.36</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2024-01-03</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C555" t="n">
+        <v>46.7</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2024-01-02</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C556" t="n">
+        <v>46.66</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2023-12-29</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C557" t="n">
+        <v>46.4</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2023-12-28</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C558" t="n">
+        <v>46.26</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2023-12-27</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C559" t="n">
+        <v>46.98</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2023-12-26</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C560" t="n">
+        <v>47.03</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2023-12-22</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C561" t="n">
+        <v>47.28</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2023-12-21</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C562" t="n">
+        <v>47.36</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C563" t="n">
+        <v>48.24</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C564" t="n">
+        <v>48.29</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C565" t="n">
+        <v>48.22</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2023-12-15</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C566" t="n">
+        <v>47.59</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
           <t>2023-12-14</t>
         </is>
       </c>
-      <c r="B553" t="inlineStr">
-        <is>
-          <t>BOK26</t>
-        </is>
-      </c>
-      <c r="C553" t="n">
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C567" t="n">
         <v>47.31</v>
       </c>
     </row>

--- a/data/lseg_excel/BOK26.xlsx
+++ b/data/lseg_excel/BOK26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C567"/>
+  <dimension ref="A1:C578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>65.64</v>
+        <v>68.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>65.97</v>
+        <v>67.11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>63.94</v>
+        <v>68.88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -502,13 +502,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>67.44</v>
+        <v>68.47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>67.42</v>
+        <v>67.41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>67.16</v>
+        <v>68.02</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>65.62</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -562,13 +562,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>66.09999999999999</v>
+        <v>65.73</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>66.58</v>
+        <v>65.58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>65.7</v>
+        <v>65.51000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>63.59</v>
+        <v>65.41</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>62.82</v>
+        <v>65.53</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -637,13 +637,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>62.74</v>
+        <v>65.97</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -652,13 +652,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>61.85</v>
+        <v>63.94</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -667,13 +667,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>61.76</v>
+        <v>67.44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -682,13 +682,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>60.67</v>
+        <v>67.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -697,13 +697,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>60.5</v>
+        <v>67.16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -712,13 +712,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>59.88</v>
+        <v>65.62</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>59.3</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -742,13 +742,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>60.09</v>
+        <v>66.58</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>59.08</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -772,13 +772,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>57.76</v>
+        <v>63.59</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>57.47</v>
+        <v>62.82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -802,13 +802,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>57.91</v>
+        <v>62.74</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>57.5</v>
+        <v>61.85</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>57.74</v>
+        <v>61.76</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -847,13 +847,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>57.17</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>55.84</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -877,13 +877,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>56.17</v>
+        <v>59.88</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -892,13 +892,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>56.18</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>55.03</v>
+        <v>60.09</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -922,13 +922,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>53.74</v>
+        <v>59.08</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -937,13 +937,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>54.06</v>
+        <v>57.76</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -952,13 +952,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>54.58</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>54.85</v>
+        <v>57.91</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>54.95</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>54.42</v>
+        <v>57.74</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>54.52</v>
+        <v>57.17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1027,13 +1027,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>54.33</v>
+        <v>55.84</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1042,13 +1042,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>54.54</v>
+        <v>56.17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>53.11</v>
+        <v>56.18</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>53.15</v>
+        <v>55.03</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>53.47</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1102,13 +1102,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>51.5</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>51.69</v>
+        <v>54.58</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>50.77</v>
+        <v>54.85</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1147,13 +1147,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>50.2</v>
+        <v>54.95</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1162,13 +1162,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>49.97</v>
+        <v>54.42</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>49.84</v>
+        <v>54.52</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>49.95</v>
+        <v>54.33</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1207,13 +1207,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>50.41</v>
+        <v>54.54</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1222,13 +1222,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>49.83</v>
+        <v>53.11</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1237,13 +1237,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>49.09</v>
+        <v>53.15</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>49.94</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>49.8</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1282,13 +1282,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>49.73</v>
+        <v>51.69</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>50</v>
+        <v>50.77</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>49.28</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>49.58</v>
+        <v>49.97</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1342,13 +1342,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>48.92</v>
+        <v>49.84</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1357,13 +1357,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>49.1</v>
+        <v>49.95</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1372,13 +1372,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>49.53</v>
+        <v>50.41</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>49.4</v>
+        <v>49.83</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1402,13 +1402,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>50.45</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>51.03</v>
+        <v>49.94</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>51.68</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1447,13 +1447,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>51.96</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1462,13 +1462,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>51.88</v>
+        <v>50</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1477,13 +1477,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>52.04</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>52.54</v>
+        <v>49.58</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>52.63</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1522,13 +1522,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>52.54</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1537,13 +1537,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>53.51</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1552,13 +1552,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>53.16</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1567,13 +1567,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>52.84</v>
+        <v>50.45</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1582,13 +1582,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>51.89</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>51.51</v>
+        <v>51.68</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1612,13 +1612,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>51.41</v>
+        <v>51.96</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1627,13 +1627,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>51.47</v>
+        <v>51.88</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1642,13 +1642,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>51.83</v>
+        <v>52.04</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1657,13 +1657,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>52.3</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1672,13 +1672,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>53.35</v>
+        <v>52.63</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1687,13 +1687,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>52.36</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1702,13 +1702,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>51.46</v>
+        <v>53.51</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1717,13 +1717,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>51.56</v>
+        <v>53.16</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>51.9</v>
+        <v>52.84</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1747,13 +1747,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>52.33</v>
+        <v>51.89</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1762,13 +1762,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>51.8</v>
+        <v>51.51</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1777,13 +1777,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>50.9</v>
+        <v>51.41</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1792,13 +1792,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>50.56</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1807,13 +1807,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>50.88</v>
+        <v>51.83</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -1822,13 +1822,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>50.76</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>51.08</v>
+        <v>53.35</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1852,13 +1852,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>50</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1867,13 +1867,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>50.88</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -1882,13 +1882,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>51.34</v>
+        <v>51.56</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1897,13 +1897,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>51.46</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>51.93</v>
+        <v>52.33</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -1927,13 +1927,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>51.4</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -1942,13 +1942,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>51.93</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -1957,13 +1957,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>51.21</v>
+        <v>50.56</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>51.72</v>
+        <v>50.88</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -1987,13 +1987,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>52.32</v>
+        <v>50.76</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2002,13 +2002,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>52.09</v>
+        <v>51.08</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>51.84</v>
+        <v>50</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2032,13 +2032,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>51.73</v>
+        <v>50.88</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2047,13 +2047,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>51.47</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2062,13 +2062,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>51.47</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>50.86</v>
+        <v>51.93</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2092,13 +2092,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>51.84</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2107,13 +2107,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>52.41</v>
+        <v>51.93</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2122,13 +2122,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>51.89</v>
+        <v>51.21</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2137,13 +2137,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>51.33</v>
+        <v>51.72</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2152,13 +2152,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>51.02</v>
+        <v>52.32</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2167,13 +2167,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>51.38</v>
+        <v>52.09</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2182,13 +2182,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>51.34</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2197,13 +2197,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>50.46</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2212,13 +2212,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>50.74</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2227,13 +2227,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>51.27</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2242,13 +2242,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>51.34</v>
+        <v>50.86</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2257,13 +2257,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>50.92</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2272,13 +2272,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>50.93</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>50.7</v>
+        <v>51.89</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2302,13 +2302,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>51.5</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2317,13 +2317,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>52.03</v>
+        <v>51.02</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2332,13 +2332,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>52.59</v>
+        <v>51.38</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>53.81</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2362,13 +2362,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>52.98</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>52.98</v>
+        <v>50.74</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -2392,13 +2392,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>52.41</v>
+        <v>51.27</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -2407,13 +2407,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>51.85</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -2422,13 +2422,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>51.41</v>
+        <v>50.92</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -2437,13 +2437,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>52.36</v>
+        <v>50.93</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -2452,13 +2452,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>52.02</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -2467,13 +2467,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>52.63</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -2482,13 +2482,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>52.54</v>
+        <v>52.03</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -2497,13 +2497,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>53.3</v>
+        <v>52.59</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -2512,13 +2512,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>52.79</v>
+        <v>53.81</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -2527,13 +2527,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>53.07</v>
+        <v>52.98</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>53.82</v>
+        <v>52.98</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -2557,13 +2557,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>53.93</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -2572,13 +2572,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>55.12</v>
+        <v>51.85</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -2587,13 +2587,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>55.41</v>
+        <v>51.41</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -2602,13 +2602,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>54.01</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>51.87</v>
+        <v>52.02</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -2632,13 +2632,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>52.23</v>
+        <v>52.63</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>53.59</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -2662,13 +2662,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>53.31</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -2677,13 +2677,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>52.27</v>
+        <v>52.79</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -2692,13 +2692,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>53.3</v>
+        <v>53.07</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -2707,13 +2707,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>53</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -2722,13 +2722,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>52.87</v>
+        <v>53.93</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -2737,13 +2737,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>52.46</v>
+        <v>55.12</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -2752,13 +2752,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>53.33</v>
+        <v>55.41</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -2767,13 +2767,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>53.53</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -2782,13 +2782,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>53.25</v>
+        <v>51.87</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -2797,13 +2797,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>53.87</v>
+        <v>52.23</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -2812,13 +2812,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>53.61</v>
+        <v>53.59</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -2827,13 +2827,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>54.32</v>
+        <v>53.31</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -2842,13 +2842,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>55.55</v>
+        <v>52.27</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -2857,13 +2857,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>56.24</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -2872,13 +2872,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>55.61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>55.47</v>
+        <v>52.87</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -2902,13 +2902,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>55.8</v>
+        <v>52.46</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>55.34</v>
+        <v>53.33</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -2932,13 +2932,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>54.93</v>
+        <v>53.53</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -2947,13 +2947,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>55.29</v>
+        <v>53.25</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -2962,13 +2962,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>55.02</v>
+        <v>53.87</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -2977,13 +2977,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>55.59</v>
+        <v>53.61</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -2992,13 +2992,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>54.31</v>
+        <v>54.32</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3007,13 +3007,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>54.1</v>
+        <v>55.55</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3022,13 +3022,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>53.8</v>
+        <v>56.24</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -3037,13 +3037,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>53.47</v>
+        <v>55.61</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -3052,13 +3052,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>53.38</v>
+        <v>55.47</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>53.17</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -3082,13 +3082,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>53.82</v>
+        <v>55.34</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3097,13 +3097,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>53.64</v>
+        <v>54.93</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -3112,13 +3112,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>54.46</v>
+        <v>55.29</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -3127,13 +3127,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>54.77</v>
+        <v>55.02</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -3142,13 +3142,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>53.48</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -3157,13 +3157,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>52.62</v>
+        <v>54.31</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -3172,13 +3172,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>52.52</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -3187,13 +3187,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>52.86</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -3202,13 +3202,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>52.43</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -3217,13 +3217,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>52.69</v>
+        <v>53.38</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -3232,13 +3232,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>53.79</v>
+        <v>53.17</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -3247,13 +3247,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>55.04</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -3262,13 +3262,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>55.23</v>
+        <v>53.64</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>55.16</v>
+        <v>54.46</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -3292,13 +3292,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>55.1</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -3307,13 +3307,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>51.65</v>
+        <v>53.48</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -3322,13 +3322,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>48.65</v>
+        <v>52.62</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -3337,13 +3337,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>48.94</v>
+        <v>52.52</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -3352,13 +3352,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>48.82</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -3367,13 +3367,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>48.46</v>
+        <v>52.43</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -3382,13 +3382,13 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>48.62</v>
+        <v>52.69</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>47.95</v>
+        <v>53.79</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -3412,13 +3412,13 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>47.8</v>
+        <v>55.04</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -3427,13 +3427,13 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>47.85</v>
+        <v>55.23</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -3442,13 +3442,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>47.49</v>
+        <v>55.16</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -3457,13 +3457,13 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>47.78</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -3472,13 +3472,13 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>49.05</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -3487,13 +3487,13 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>49.41</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -3502,13 +3502,13 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>50.03</v>
+        <v>48.94</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>49.88</v>
+        <v>48.82</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -3532,13 +3532,13 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>49.73</v>
+        <v>48.46</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -3547,13 +3547,13 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>50.23</v>
+        <v>48.62</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -3562,13 +3562,13 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>49.88</v>
+        <v>47.95</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -3577,13 +3577,13 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>49.78</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -3592,13 +3592,13 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>49.2</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -3607,13 +3607,13 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>48.9</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -3622,13 +3622,13 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>51.9</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -3637,13 +3637,13 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>51.46</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -3652,13 +3652,13 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>50.03</v>
+        <v>49.41</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>48.66</v>
+        <v>50.03</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -3682,13 +3682,13 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>48.38</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -3697,13 +3697,13 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>47.52</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -3712,13 +3712,13 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>48.22</v>
+        <v>50.23</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -3727,13 +3727,13 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>48.33</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -3742,13 +3742,13 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>48.82</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -3757,13 +3757,13 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>48.95</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -3772,13 +3772,13 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>48.22</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -3787,13 +3787,13 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>48.75</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>49.78</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -3817,13 +3817,13 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>49.23</v>
+        <v>50.03</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -3832,13 +3832,13 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>49.17</v>
+        <v>48.66</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -3847,13 +3847,13 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>47.85</v>
+        <v>48.38</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -3862,13 +3862,13 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>47.78</v>
+        <v>47.52</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -3877,13 +3877,13 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>47.83</v>
+        <v>48.22</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -3892,13 +3892,13 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>47.91</v>
+        <v>48.33</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -3907,13 +3907,13 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>47.73</v>
+        <v>48.82</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -3922,13 +3922,13 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>47.54</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -3937,13 +3937,13 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>46.72</v>
+        <v>48.22</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -3952,13 +3952,13 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>47.16</v>
+        <v>48.75</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -3967,13 +3967,13 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>46.15</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -3982,13 +3982,13 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>46.11</v>
+        <v>49.23</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -3997,13 +3997,13 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>44.82</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -4012,13 +4012,13 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>45.02</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -4027,13 +4027,13 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>45.96</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -4042,13 +4042,13 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>47.35</v>
+        <v>47.83</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -4057,13 +4057,13 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>48.65</v>
+        <v>47.91</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -4072,13 +4072,13 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>47.87</v>
+        <v>47.73</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -4087,13 +4087,13 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>46</v>
+        <v>47.54</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -4102,13 +4102,13 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>46.11</v>
+        <v>46.72</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -4117,13 +4117,13 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>45.42</v>
+        <v>47.16</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -4132,13 +4132,13 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>44.2</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -4147,13 +4147,13 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>43.82</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -4162,13 +4162,13 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>43.48</v>
+        <v>44.82</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -4177,13 +4177,13 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>43.28</v>
+        <v>45.02</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -4192,13 +4192,13 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>43.7</v>
+        <v>45.96</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -4207,13 +4207,13 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>43.32</v>
+        <v>47.35</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -4222,13 +4222,13 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>43.28</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -4237,13 +4237,13 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>42.9</v>
+        <v>47.87</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -4252,13 +4252,13 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>42.51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -4267,13 +4267,13 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>42.36</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -4282,13 +4282,13 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>42.65</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -4297,13 +4297,13 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>42.85</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -4312,13 +4312,13 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>43.04</v>
+        <v>43.82</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -4327,13 +4327,13 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>43.92</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>43.52</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -4357,13 +4357,13 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>43.37</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -4372,13 +4372,13 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>43.24</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -4387,13 +4387,13 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>43.99</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -4402,13 +4402,13 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>44.52</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -4417,13 +4417,13 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>45.66</v>
+        <v>42.51</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -4432,13 +4432,13 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>45.78</v>
+        <v>42.36</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -4447,13 +4447,13 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>46.1</v>
+        <v>42.65</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -4462,13 +4462,13 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>46.42</v>
+        <v>42.85</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -4477,13 +4477,13 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>47.21</v>
+        <v>43.04</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -4492,13 +4492,13 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>47.44</v>
+        <v>43.92</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -4507,13 +4507,13 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>46.5</v>
+        <v>43.52</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -4522,13 +4522,13 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>47.21</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -4537,13 +4537,13 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>46.08</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -4552,13 +4552,13 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>46.21</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -4567,13 +4567,13 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>45.72</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -4582,13 +4582,13 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>46.29</v>
+        <v>45.66</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -4597,13 +4597,13 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>45.9</v>
+        <v>45.78</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -4612,13 +4612,13 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>46.05</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -4627,13 +4627,13 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>45.73</v>
+        <v>46.42</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -4642,13 +4642,13 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>45.31</v>
+        <v>47.21</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -4657,13 +4657,13 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>45.75</v>
+        <v>47.44</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -4672,13 +4672,13 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>46.37</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -4687,13 +4687,13 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>45.77</v>
+        <v>47.21</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -4702,13 +4702,13 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>45.1</v>
+        <v>46.08</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>44.97</v>
+        <v>46.21</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -4732,13 +4732,13 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>45.11</v>
+        <v>45.72</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -4747,13 +4747,13 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>44.88</v>
+        <v>46.29</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -4762,13 +4762,13 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>45.06</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -4777,13 +4777,13 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>44.73</v>
+        <v>46.05</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -4792,13 +4792,13 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>44.3</v>
+        <v>45.73</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -4807,13 +4807,13 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>45.15</v>
+        <v>45.31</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -4822,13 +4822,13 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>45.27</v>
+        <v>45.75</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -4837,13 +4837,13 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>45.03</v>
+        <v>46.37</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -4852,13 +4852,13 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>45.99</v>
+        <v>45.77</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -4867,13 +4867,13 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>46.22</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -4882,13 +4882,13 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>46.06</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -4897,13 +4897,13 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>45.62</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -4912,13 +4912,13 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>43.48</v>
+        <v>44.88</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -4927,13 +4927,13 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>42.45</v>
+        <v>45.06</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -4942,13 +4942,13 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>42.17</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -4957,13 +4957,13 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>41.34</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -4972,13 +4972,13 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>40.87</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -4987,13 +4987,13 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>41.09</v>
+        <v>45.27</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>41.32</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -5017,13 +5017,13 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>41.19</v>
+        <v>45.99</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>40.94</v>
+        <v>46.22</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -5047,13 +5047,13 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>40.94</v>
+        <v>46.06</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2024-12-24</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>41.38</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -5077,13 +5077,13 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>41.62</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -5092,13 +5092,13 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>40.87</v>
+        <v>42.45</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -5107,13 +5107,13 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>41.15</v>
+        <v>42.17</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -5122,13 +5122,13 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>40.92</v>
+        <v>41.34</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -5137,13 +5137,13 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>41.73</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -5152,13 +5152,13 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>42.72</v>
+        <v>41.09</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -5167,13 +5167,13 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>43.49</v>
+        <v>41.32</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -5182,13 +5182,13 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>43.53</v>
+        <v>41.19</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -5197,13 +5197,13 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>43.26</v>
+        <v>40.94</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -5212,13 +5212,13 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>43.46</v>
+        <v>40.94</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -5227,13 +5227,13 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>43.52</v>
+        <v>41.38</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -5242,13 +5242,13 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>43.58</v>
+        <v>41.62</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -5257,13 +5257,13 @@
         </is>
       </c>
       <c r="C322" t="n">
-        <v>42.89</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -5272,13 +5272,13 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>42.12</v>
+        <v>41.15</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -5287,13 +5287,13 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>42.67</v>
+        <v>40.92</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -5302,13 +5302,13 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>42.3</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -5317,13 +5317,13 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>42.39</v>
+        <v>42.72</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>41.84</v>
+        <v>43.49</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -5347,13 +5347,13 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>43.17</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>42.27</v>
+        <v>43.26</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -5377,13 +5377,13 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>42.78</v>
+        <v>43.46</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -5392,13 +5392,13 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>43.09</v>
+        <v>43.52</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -5407,13 +5407,13 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>43.95</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -5422,13 +5422,13 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>44.91</v>
+        <v>42.89</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -5437,13 +5437,13 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>45.32</v>
+        <v>42.12</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -5452,13 +5452,13 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>45.24</v>
+        <v>42.67</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -5467,13 +5467,13 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>44.48</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -5482,13 +5482,13 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>45.38</v>
+        <v>42.39</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -5497,13 +5497,13 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>46.24</v>
+        <v>41.84</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -5512,13 +5512,13 @@
         </is>
       </c>
       <c r="C339" t="n">
-        <v>47.78</v>
+        <v>43.17</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -5527,13 +5527,13 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>48.04</v>
+        <v>42.27</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -5542,13 +5542,13 @@
         </is>
       </c>
       <c r="C341" t="n">
-        <v>47.49</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -5557,13 +5557,13 @@
         </is>
       </c>
       <c r="C342" t="n">
-        <v>45.65</v>
+        <v>43.09</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -5572,13 +5572,13 @@
         </is>
       </c>
       <c r="C343" t="n">
-        <v>45.01</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -5587,13 +5587,13 @@
         </is>
       </c>
       <c r="C344" t="n">
-        <v>45.36</v>
+        <v>44.91</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -5602,13 +5602,13 @@
         </is>
       </c>
       <c r="C345" t="n">
-        <v>45.49</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -5617,13 +5617,13 @@
         </is>
       </c>
       <c r="C346" t="n">
-        <v>44.54</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>43.62</v>
+        <v>44.48</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -5647,13 +5647,13 @@
         </is>
       </c>
       <c r="C348" t="n">
-        <v>42.78</v>
+        <v>45.38</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -5662,13 +5662,13 @@
         </is>
       </c>
       <c r="C349" t="n">
-        <v>42.73</v>
+        <v>46.24</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -5677,13 +5677,13 @@
         </is>
       </c>
       <c r="C350" t="n">
-        <v>43.65</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -5692,13 +5692,13 @@
         </is>
       </c>
       <c r="C351" t="n">
-        <v>43.48</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -5707,13 +5707,13 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>42.77</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -5722,13 +5722,13 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>42.86</v>
+        <v>45.65</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -5737,13 +5737,13 @@
         </is>
       </c>
       <c r="C354" t="n">
-        <v>41.8</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -5752,13 +5752,13 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>41.24</v>
+        <v>45.36</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -5767,13 +5767,13 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>41.92</v>
+        <v>45.49</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -5782,13 +5782,13 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>41.59</v>
+        <v>44.54</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>42.03</v>
+        <v>43.62</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>42.03</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -5827,13 +5827,13 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>43.28</v>
+        <v>42.73</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -5842,13 +5842,13 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>43.74</v>
+        <v>43.65</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -5857,13 +5857,13 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>43.16</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -5872,13 +5872,13 @@
         </is>
       </c>
       <c r="C363" t="n">
-        <v>43.22</v>
+        <v>42.77</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -5887,13 +5887,13 @@
         </is>
       </c>
       <c r="C364" t="n">
-        <v>44.73</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -5902,13 +5902,13 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>44.08</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -5917,13 +5917,13 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>44.43</v>
+        <v>41.24</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -5932,13 +5932,13 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>43.57</v>
+        <v>41.92</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -5947,13 +5947,13 @@
         </is>
       </c>
       <c r="C368" t="n">
-        <v>43.08</v>
+        <v>41.59</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -5962,13 +5962,13 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>43.05</v>
+        <v>42.03</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -5977,13 +5977,13 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>42.78</v>
+        <v>42.03</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -5992,13 +5992,13 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>43.53</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -6007,13 +6007,13 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>43.71</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -6022,13 +6022,13 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>43.14</v>
+        <v>43.16</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -6037,13 +6037,13 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>42.09</v>
+        <v>43.22</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -6052,13 +6052,13 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>41.73</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -6067,13 +6067,13 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>41.43</v>
+        <v>44.08</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -6082,13 +6082,13 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>41.17</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -6097,13 +6097,13 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>40.69</v>
+        <v>43.57</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -6112,13 +6112,13 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>40.11</v>
+        <v>43.08</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -6127,13 +6127,13 @@
         </is>
       </c>
       <c r="C380" t="n">
-        <v>40.12</v>
+        <v>43.05</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -6142,13 +6142,13 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>40.75</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -6157,13 +6157,13 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>40.39</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -6172,13 +6172,13 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>40.6</v>
+        <v>43.71</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -6187,13 +6187,13 @@
         </is>
       </c>
       <c r="C384" t="n">
-        <v>41.29</v>
+        <v>43.14</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -6202,13 +6202,13 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>40.49</v>
+        <v>42.09</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -6217,13 +6217,13 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>41.62</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -6232,13 +6232,13 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>40.98</v>
+        <v>41.43</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -6247,13 +6247,13 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>41.5</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -6262,13 +6262,13 @@
         </is>
       </c>
       <c r="C389" t="n">
-        <v>42.26</v>
+        <v>40.69</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -6277,13 +6277,13 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>42.24</v>
+        <v>40.11</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -6292,13 +6292,13 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>41.21</v>
+        <v>40.12</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -6307,13 +6307,13 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>40.93</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -6322,13 +6322,13 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>40.83</v>
+        <v>40.39</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -6337,13 +6337,13 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>40.51</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -6352,13 +6352,13 @@
         </is>
       </c>
       <c r="C395" t="n">
-        <v>39.52</v>
+        <v>41.29</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -6367,13 +6367,13 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>40.05</v>
+        <v>40.49</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -6382,13 +6382,13 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>39.68</v>
+        <v>41.62</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -6397,13 +6397,13 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>39.76</v>
+        <v>40.98</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -6412,13 +6412,13 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>39.55</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -6427,13 +6427,13 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>39.29</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -6442,13 +6442,13 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>39.58</v>
+        <v>42.24</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -6457,13 +6457,13 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>39.89</v>
+        <v>41.21</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -6472,13 +6472,13 @@
         </is>
       </c>
       <c r="C403" t="n">
-        <v>40.84</v>
+        <v>40.93</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -6487,13 +6487,13 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>40.75</v>
+        <v>40.83</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -6502,13 +6502,13 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>40.68</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -6517,13 +6517,13 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>40.51</v>
+        <v>39.52</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -6532,13 +6532,13 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>40.16</v>
+        <v>40.05</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>40.25</v>
+        <v>39.68</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -6562,13 +6562,13 @@
         </is>
       </c>
       <c r="C409" t="n">
-        <v>40.91</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -6577,13 +6577,13 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>41.18</v>
+        <v>39.55</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -6592,13 +6592,13 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>41.72</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -6607,13 +6607,13 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>41.2</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -6622,13 +6622,13 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>41.67</v>
+        <v>39.89</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -6637,13 +6637,13 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>41.34</v>
+        <v>40.84</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -6652,13 +6652,13 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>42.82</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -6667,13 +6667,13 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>42.57</v>
+        <v>40.68</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -6682,13 +6682,13 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>43.28</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -6697,13 +6697,13 @@
         </is>
       </c>
       <c r="C418" t="n">
-        <v>42.86</v>
+        <v>40.16</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -6712,13 +6712,13 @@
         </is>
       </c>
       <c r="C419" t="n">
-        <v>41.96</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -6727,13 +6727,13 @@
         </is>
       </c>
       <c r="C420" t="n">
-        <v>42.63</v>
+        <v>40.91</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -6742,13 +6742,13 @@
         </is>
       </c>
       <c r="C421" t="n">
-        <v>42.6</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -6757,13 +6757,13 @@
         </is>
       </c>
       <c r="C422" t="n">
-        <v>43.39</v>
+        <v>41.72</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -6772,13 +6772,13 @@
         </is>
       </c>
       <c r="C423" t="n">
-        <v>43.49</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -6787,13 +6787,13 @@
         </is>
       </c>
       <c r="C424" t="n">
-        <v>44.6</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -6802,13 +6802,13 @@
         </is>
       </c>
       <c r="C425" t="n">
-        <v>45.01</v>
+        <v>41.34</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -6817,13 +6817,13 @@
         </is>
       </c>
       <c r="C426" t="n">
-        <v>44.73</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -6832,13 +6832,13 @@
         </is>
       </c>
       <c r="C427" t="n">
-        <v>45.87</v>
+        <v>42.57</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="C428" t="n">
-        <v>46.97</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -6862,13 +6862,13 @@
         </is>
       </c>
       <c r="C429" t="n">
-        <v>47.02</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -6877,13 +6877,13 @@
         </is>
       </c>
       <c r="C430" t="n">
-        <v>46.75</v>
+        <v>41.96</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -6892,13 +6892,13 @@
         </is>
       </c>
       <c r="C431" t="n">
-        <v>45.79</v>
+        <v>42.63</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -6907,13 +6907,13 @@
         </is>
       </c>
       <c r="C432" t="n">
-        <v>44.84</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -6922,13 +6922,13 @@
         </is>
       </c>
       <c r="C433" t="n">
-        <v>43.13</v>
+        <v>43.39</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -6937,13 +6937,13 @@
         </is>
       </c>
       <c r="C434" t="n">
-        <v>42.97</v>
+        <v>43.49</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -6952,13 +6952,13 @@
         </is>
       </c>
       <c r="C435" t="n">
-        <v>43.37</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -6967,13 +6967,13 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>42.71</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -6982,13 +6982,13 @@
         </is>
       </c>
       <c r="C437" t="n">
-        <v>43.35</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -6997,13 +6997,13 @@
         </is>
       </c>
       <c r="C438" t="n">
-        <v>43.58</v>
+        <v>45.87</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -7012,13 +7012,13 @@
         </is>
       </c>
       <c r="C439" t="n">
-        <v>43.59</v>
+        <v>46.97</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -7027,13 +7027,13 @@
         </is>
       </c>
       <c r="C440" t="n">
-        <v>44.01</v>
+        <v>47.02</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -7042,13 +7042,13 @@
         </is>
       </c>
       <c r="C441" t="n">
-        <v>43.56</v>
+        <v>46.75</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -7057,13 +7057,13 @@
         </is>
       </c>
       <c r="C442" t="n">
-        <v>43.53</v>
+        <v>45.79</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -7072,13 +7072,13 @@
         </is>
       </c>
       <c r="C443" t="n">
-        <v>43.76</v>
+        <v>44.84</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -7087,13 +7087,13 @@
         </is>
       </c>
       <c r="C444" t="n">
-        <v>43.87</v>
+        <v>43.13</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -7102,13 +7102,13 @@
         </is>
       </c>
       <c r="C445" t="n">
-        <v>43.76</v>
+        <v>42.97</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -7117,13 +7117,13 @@
         </is>
       </c>
       <c r="C446" t="n">
-        <v>43.98</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -7132,13 +7132,13 @@
         </is>
       </c>
       <c r="C447" t="n">
-        <v>44.29</v>
+        <v>42.71</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -7147,13 +7147,13 @@
         </is>
       </c>
       <c r="C448" t="n">
-        <v>44.83</v>
+        <v>43.35</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -7162,13 +7162,13 @@
         </is>
       </c>
       <c r="C449" t="n">
-        <v>43.88</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -7177,13 +7177,13 @@
         </is>
       </c>
       <c r="C450" t="n">
-        <v>44.2</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -7192,13 +7192,13 @@
         </is>
       </c>
       <c r="C451" t="n">
-        <v>44.63</v>
+        <v>44.01</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="C452" t="n">
-        <v>45.81</v>
+        <v>43.56</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -7222,13 +7222,13 @@
         </is>
       </c>
       <c r="C453" t="n">
-        <v>45.93</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -7237,13 +7237,13 @@
         </is>
       </c>
       <c r="C454" t="n">
-        <v>46.11</v>
+        <v>43.76</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="C455" t="n">
-        <v>45.74</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -7267,13 +7267,13 @@
         </is>
       </c>
       <c r="C456" t="n">
-        <v>45.32</v>
+        <v>43.76</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -7282,13 +7282,13 @@
         </is>
       </c>
       <c r="C457" t="n">
-        <v>45.96</v>
+        <v>43.98</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -7297,13 +7297,13 @@
         </is>
       </c>
       <c r="C458" t="n">
-        <v>46.2</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -7312,13 +7312,13 @@
         </is>
       </c>
       <c r="C459" t="n">
-        <v>46.37</v>
+        <v>44.83</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -7327,13 +7327,13 @@
         </is>
       </c>
       <c r="C460" t="n">
-        <v>46.6</v>
+        <v>43.88</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -7342,13 +7342,13 @@
         </is>
       </c>
       <c r="C461" t="n">
-        <v>45.89</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -7357,13 +7357,13 @@
         </is>
       </c>
       <c r="C462" t="n">
-        <v>45.45</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -7372,13 +7372,13 @@
         </is>
       </c>
       <c r="C463" t="n">
-        <v>44.82</v>
+        <v>45.81</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -7387,13 +7387,13 @@
         </is>
       </c>
       <c r="C464" t="n">
-        <v>44.7</v>
+        <v>45.93</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -7402,13 +7402,13 @@
         </is>
       </c>
       <c r="C465" t="n">
-        <v>46.01</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -7417,13 +7417,13 @@
         </is>
       </c>
       <c r="C466" t="n">
-        <v>45.24</v>
+        <v>45.74</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -7432,13 +7432,13 @@
         </is>
       </c>
       <c r="C467" t="n">
-        <v>44.2</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -7447,13 +7447,13 @@
         </is>
       </c>
       <c r="C468" t="n">
-        <v>44.8</v>
+        <v>45.96</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="C469" t="n">
-        <v>45.29</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -7477,13 +7477,13 @@
         </is>
       </c>
       <c r="C470" t="n">
-        <v>44.66</v>
+        <v>46.37</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -7492,13 +7492,13 @@
         </is>
       </c>
       <c r="C471" t="n">
-        <v>44.34</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -7507,13 +7507,13 @@
         </is>
       </c>
       <c r="C472" t="n">
-        <v>44.43</v>
+        <v>45.89</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -7522,13 +7522,13 @@
         </is>
       </c>
       <c r="C473" t="n">
-        <v>44.49</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -7537,13 +7537,13 @@
         </is>
       </c>
       <c r="C474" t="n">
-        <v>44.32</v>
+        <v>44.82</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -7552,13 +7552,13 @@
         </is>
       </c>
       <c r="C475" t="n">
-        <v>45.01</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -7567,13 +7567,13 @@
         </is>
       </c>
       <c r="C476" t="n">
-        <v>45.94</v>
+        <v>46.01</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -7582,13 +7582,13 @@
         </is>
       </c>
       <c r="C477" t="n">
-        <v>45.67</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -7597,13 +7597,13 @@
         </is>
       </c>
       <c r="C478" t="n">
-        <v>45.58</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -7612,13 +7612,13 @@
         </is>
       </c>
       <c r="C479" t="n">
-        <v>45.95</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -7627,13 +7627,13 @@
         </is>
       </c>
       <c r="C480" t="n">
-        <v>45.8</v>
+        <v>45.29</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -7642,13 +7642,13 @@
         </is>
       </c>
       <c r="C481" t="n">
-        <v>45.14</v>
+        <v>44.66</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -7657,13 +7657,13 @@
         </is>
       </c>
       <c r="C482" t="n">
-        <v>44.97</v>
+        <v>44.34</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -7672,13 +7672,13 @@
         </is>
       </c>
       <c r="C483" t="n">
-        <v>45.19</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -7687,13 +7687,13 @@
         </is>
       </c>
       <c r="C484" t="n">
-        <v>45.34</v>
+        <v>44.49</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -7702,13 +7702,13 @@
         </is>
       </c>
       <c r="C485" t="n">
-        <v>45.6</v>
+        <v>44.32</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -7717,13 +7717,13 @@
         </is>
       </c>
       <c r="C486" t="n">
-        <v>45.97</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -7732,13 +7732,13 @@
         </is>
       </c>
       <c r="C487" t="n">
-        <v>45.91</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -7747,13 +7747,13 @@
         </is>
       </c>
       <c r="C488" t="n">
-        <v>46.95</v>
+        <v>45.67</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -7762,13 +7762,13 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>46.91</v>
+        <v>45.58</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -7777,13 +7777,13 @@
         </is>
       </c>
       <c r="C490" t="n">
-        <v>47.23</v>
+        <v>45.95</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -7792,13 +7792,13 @@
         </is>
       </c>
       <c r="C491" t="n">
-        <v>47.84</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="C492" t="n">
-        <v>47.38</v>
+        <v>45.14</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -7822,13 +7822,13 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>48</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -7837,13 +7837,13 @@
         </is>
       </c>
       <c r="C494" t="n">
-        <v>47.67</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -7852,13 +7852,13 @@
         </is>
       </c>
       <c r="C495" t="n">
-        <v>47.12</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -7867,13 +7867,13 @@
         </is>
       </c>
       <c r="C496" t="n">
-        <v>47.14</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -7882,13 +7882,13 @@
         </is>
       </c>
       <c r="C497" t="n">
-        <v>46.67</v>
+        <v>45.97</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -7897,13 +7897,13 @@
         </is>
       </c>
       <c r="C498" t="n">
-        <v>47.46</v>
+        <v>45.91</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -7912,13 +7912,13 @@
         </is>
       </c>
       <c r="C499" t="n">
-        <v>47.71</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -7927,13 +7927,13 @@
         </is>
       </c>
       <c r="C500" t="n">
-        <v>46.65</v>
+        <v>46.91</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -7942,13 +7942,13 @@
         </is>
       </c>
       <c r="C501" t="n">
-        <v>47.72</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -7957,13 +7957,13 @@
         </is>
       </c>
       <c r="C502" t="n">
-        <v>47.89</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -7972,13 +7972,13 @@
         </is>
       </c>
       <c r="C503" t="n">
-        <v>47.23</v>
+        <v>47.38</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -7987,13 +7987,13 @@
         </is>
       </c>
       <c r="C504" t="n">
-        <v>47.63</v>
+        <v>48</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -8002,13 +8002,13 @@
         </is>
       </c>
       <c r="C505" t="n">
-        <v>48.16</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -8017,13 +8017,13 @@
         </is>
       </c>
       <c r="C506" t="n">
-        <v>47.08</v>
+        <v>47.12</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -8032,13 +8032,13 @@
         </is>
       </c>
       <c r="C507" t="n">
-        <v>47.34</v>
+        <v>47.14</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -8047,13 +8047,13 @@
         </is>
       </c>
       <c r="C508" t="n">
-        <v>46.61</v>
+        <v>46.67</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -8062,13 +8062,13 @@
         </is>
       </c>
       <c r="C509" t="n">
-        <v>45.84</v>
+        <v>47.46</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -8077,13 +8077,13 @@
         </is>
       </c>
       <c r="C510" t="n">
-        <v>45.28</v>
+        <v>47.71</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -8092,13 +8092,13 @@
         </is>
       </c>
       <c r="C511" t="n">
-        <v>45.23</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -8107,13 +8107,13 @@
         </is>
       </c>
       <c r="C512" t="n">
-        <v>44.51</v>
+        <v>47.72</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -8122,13 +8122,13 @@
         </is>
       </c>
       <c r="C513" t="n">
-        <v>44.37</v>
+        <v>47.89</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -8137,13 +8137,13 @@
         </is>
       </c>
       <c r="C514" t="n">
-        <v>44.55</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -8152,13 +8152,13 @@
         </is>
       </c>
       <c r="C515" t="n">
-        <v>44.45</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -8167,13 +8167,13 @@
         </is>
       </c>
       <c r="C516" t="n">
-        <v>44.56</v>
+        <v>48.16</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -8182,13 +8182,13 @@
         </is>
       </c>
       <c r="C517" t="n">
-        <v>44.63</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -8197,13 +8197,13 @@
         </is>
       </c>
       <c r="C518" t="n">
-        <v>44.69</v>
+        <v>47.34</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>2024-02-26</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -8212,13 +8212,13 @@
         </is>
       </c>
       <c r="C519" t="n">
-        <v>44.2</v>
+        <v>46.61</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -8227,13 +8227,13 @@
         </is>
       </c>
       <c r="C520" t="n">
-        <v>43.78</v>
+        <v>45.84</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -8242,13 +8242,13 @@
         </is>
       </c>
       <c r="C521" t="n">
-        <v>43.99</v>
+        <v>45.28</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -8257,13 +8257,13 @@
         </is>
       </c>
       <c r="C522" t="n">
-        <v>44</v>
+        <v>45.23</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -8272,13 +8272,13 @@
         </is>
       </c>
       <c r="C523" t="n">
-        <v>44.35</v>
+        <v>44.51</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="C524" t="n">
-        <v>44.52</v>
+        <v>44.37</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -8302,13 +8302,13 @@
         </is>
       </c>
       <c r="C525" t="n">
-        <v>44.68</v>
+        <v>44.55</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -8317,13 +8317,13 @@
         </is>
       </c>
       <c r="C526" t="n">
-        <v>45.07</v>
+        <v>44.45</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -8332,13 +8332,13 @@
         </is>
       </c>
       <c r="C527" t="n">
-        <v>45.62</v>
+        <v>44.56</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -8347,13 +8347,13 @@
         </is>
       </c>
       <c r="C528" t="n">
-        <v>45.33</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -8362,13 +8362,13 @@
         </is>
       </c>
       <c r="C529" t="n">
-        <v>45.64</v>
+        <v>44.69</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="C530" t="n">
-        <v>45.59</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -8392,13 +8392,13 @@
         </is>
       </c>
       <c r="C531" t="n">
-        <v>44.61</v>
+        <v>43.78</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-22</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -8407,13 +8407,13 @@
         </is>
       </c>
       <c r="C532" t="n">
-        <v>44.2</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -8422,13 +8422,13 @@
         </is>
       </c>
       <c r="C533" t="n">
-        <v>43.73</v>
+        <v>44</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -8437,13 +8437,13 @@
         </is>
       </c>
       <c r="C534" t="n">
-        <v>43.66</v>
+        <v>44.35</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -8452,13 +8452,13 @@
         </is>
       </c>
       <c r="C535" t="n">
-        <v>44.07</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -8467,13 +8467,13 @@
         </is>
       </c>
       <c r="C536" t="n">
-        <v>44.66</v>
+        <v>44.68</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -8482,13 +8482,13 @@
         </is>
       </c>
       <c r="C537" t="n">
-        <v>44.75</v>
+        <v>45.07</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -8497,13 +8497,13 @@
         </is>
       </c>
       <c r="C538" t="n">
-        <v>44.73</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -8512,13 +8512,13 @@
         </is>
       </c>
       <c r="C539" t="n">
-        <v>45.37</v>
+        <v>45.33</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2024-02-09</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -8527,13 +8527,13 @@
         </is>
       </c>
       <c r="C540" t="n">
-        <v>45.34</v>
+        <v>45.64</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -8542,13 +8542,13 @@
         </is>
       </c>
       <c r="C541" t="n">
-        <v>45.57</v>
+        <v>45.59</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>2024-01-23</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -8557,13 +8557,13 @@
         </is>
       </c>
       <c r="C542" t="n">
-        <v>45.97</v>
+        <v>44.61</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -8572,13 +8572,13 @@
         </is>
       </c>
       <c r="C543" t="n">
-        <v>45.94</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>2024-01-19</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -8587,13 +8587,13 @@
         </is>
       </c>
       <c r="C544" t="n">
-        <v>45.19</v>
+        <v>43.73</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -8602,13 +8602,13 @@
         </is>
       </c>
       <c r="C545" t="n">
-        <v>45.44</v>
+        <v>43.66</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -8617,13 +8617,13 @@
         </is>
       </c>
       <c r="C546" t="n">
-        <v>45.42</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="C547" t="n">
-        <v>45.42</v>
+        <v>44.66</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>2024-01-30</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -8647,13 +8647,13 @@
         </is>
       </c>
       <c r="C548" t="n">
-        <v>46.13</v>
+        <v>44.75</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>2024-01-11</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -8662,13 +8662,13 @@
         </is>
       </c>
       <c r="C549" t="n">
-        <v>46.6</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -8677,13 +8677,13 @@
         </is>
       </c>
       <c r="C550" t="n">
-        <v>46.28</v>
+        <v>45.37</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -8692,13 +8692,13 @@
         </is>
       </c>
       <c r="C551" t="n">
-        <v>46.63</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>2024-01-08</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="C552" t="n">
-        <v>45.95</v>
+        <v>45.57</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>2024-01-23</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -8722,13 +8722,13 @@
         </is>
       </c>
       <c r="C553" t="n">
-        <v>45.99</v>
+        <v>45.97</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>2024-01-04</t>
+          <t>2024-01-22</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -8737,13 +8737,13 @@
         </is>
       </c>
       <c r="C554" t="n">
-        <v>46.36</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>2024-01-03</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -8752,13 +8752,13 @@
         </is>
       </c>
       <c r="C555" t="n">
-        <v>46.7</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -8767,13 +8767,13 @@
         </is>
       </c>
       <c r="C556" t="n">
-        <v>46.66</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>2023-12-29</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -8782,13 +8782,13 @@
         </is>
       </c>
       <c r="C557" t="n">
-        <v>46.4</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>2023-12-28</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -8797,13 +8797,13 @@
         </is>
       </c>
       <c r="C558" t="n">
-        <v>46.26</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>2023-12-27</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -8812,13 +8812,13 @@
         </is>
       </c>
       <c r="C559" t="n">
-        <v>46.98</v>
+        <v>46.13</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>2023-12-26</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -8827,13 +8827,13 @@
         </is>
       </c>
       <c r="C560" t="n">
-        <v>47.03</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2024-01-10</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -8842,13 +8842,13 @@
         </is>
       </c>
       <c r="C561" t="n">
-        <v>47.28</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -8857,13 +8857,13 @@
         </is>
       </c>
       <c r="C562" t="n">
-        <v>47.36</v>
+        <v>46.63</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2024-01-08</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -8872,13 +8872,13 @@
         </is>
       </c>
       <c r="C563" t="n">
-        <v>48.24</v>
+        <v>45.95</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2024-01-05</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -8887,13 +8887,13 @@
         </is>
       </c>
       <c r="C564" t="n">
-        <v>48.29</v>
+        <v>45.99</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2024-01-04</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -8902,13 +8902,13 @@
         </is>
       </c>
       <c r="C565" t="n">
-        <v>48.22</v>
+        <v>46.36</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2024-01-03</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -8917,21 +8917,186 @@
         </is>
       </c>
       <c r="C566" t="n">
-        <v>47.59</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
+          <t>2024-01-02</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C567" t="n">
+        <v>46.66</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2023-12-29</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C568" t="n">
+        <v>46.4</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2023-12-28</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C569" t="n">
+        <v>46.26</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2023-12-27</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C570" t="n">
+        <v>46.98</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2023-12-26</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C571" t="n">
+        <v>47.03</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2023-12-22</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C572" t="n">
+        <v>47.28</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2023-12-21</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C573" t="n">
+        <v>47.36</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C574" t="n">
+        <v>48.24</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C575" t="n">
+        <v>48.29</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C576" t="n">
+        <v>48.22</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2023-12-15</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C577" t="n">
+        <v>47.59</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
           <t>2023-12-14</t>
         </is>
       </c>
-      <c r="B567" t="inlineStr">
-        <is>
-          <t>BOK26</t>
-        </is>
-      </c>
-      <c r="C567" t="n">
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C578" t="n">
         <v>47.31</v>
       </c>
     </row>

--- a/data/lseg_excel/BOK26.xlsx
+++ b/data/lseg_excel/BOK26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C578"/>
+  <dimension ref="A1:C580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>68.25</v>
+        <v>69.02</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -471,14 +471,12 @@
           <t>BOK26</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>67.11</v>
-      </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,13 +485,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>68.88</v>
+        <v>68.94</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -502,13 +500,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>68.47</v>
+        <v>67.11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -517,13 +515,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>67.41</v>
+        <v>68.88</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -532,13 +530,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>68.02</v>
+        <v>68.47</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -547,13 +545,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>67.09999999999999</v>
+        <v>67.41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -562,13 +560,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>65.73</v>
+        <v>68.02</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -577,13 +575,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>65.58</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -592,13 +590,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>65.51000000000001</v>
+        <v>65.73</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -607,13 +605,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>65.41</v>
+        <v>65.58</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -622,13 +620,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>65.53</v>
+        <v>65.51000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -637,13 +635,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>65.97</v>
+        <v>65.41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -652,13 +650,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>63.94</v>
+        <v>65.53</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -667,13 +665,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>67.44</v>
+        <v>65.97</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -682,13 +680,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>67.42</v>
+        <v>63.94</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -697,13 +695,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>67.16</v>
+        <v>67.44</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -712,13 +710,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>65.62</v>
+        <v>67.42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -727,13 +725,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>66.09999999999999</v>
+        <v>67.16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -742,13 +740,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>66.58</v>
+        <v>65.62</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -757,13 +755,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>65.7</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -772,13 +770,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>63.59</v>
+        <v>66.58</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -787,13 +785,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>62.82</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -802,13 +800,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>62.74</v>
+        <v>63.59</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -817,13 +815,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>61.85</v>
+        <v>62.82</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -832,13 +830,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>61.76</v>
+        <v>62.74</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -847,13 +845,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>60.67</v>
+        <v>61.85</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -862,13 +860,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>60.5</v>
+        <v>61.76</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -877,13 +875,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>59.88</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -892,13 +890,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>59.3</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -907,13 +905,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>60.09</v>
+        <v>59.88</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -922,13 +920,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>59.08</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -937,13 +935,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>57.76</v>
+        <v>60.09</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -952,13 +950,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>57.47</v>
+        <v>59.08</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -967,13 +965,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>57.91</v>
+        <v>57.76</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -982,13 +980,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>57.5</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -997,13 +995,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>57.74</v>
+        <v>57.91</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1012,13 +1010,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>57.17</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1027,13 +1025,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>55.84</v>
+        <v>57.74</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1042,13 +1040,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>56.17</v>
+        <v>57.17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1057,13 +1055,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>56.18</v>
+        <v>55.84</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1072,13 +1070,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>55.03</v>
+        <v>56.17</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1087,13 +1085,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>53.74</v>
+        <v>56.18</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1102,13 +1100,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>54.06</v>
+        <v>55.03</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1117,13 +1115,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>54.58</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1132,13 +1130,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>54.85</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1147,13 +1145,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>54.95</v>
+        <v>54.58</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1162,13 +1160,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>54.42</v>
+        <v>54.85</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1177,13 +1175,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>54.52</v>
+        <v>54.95</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1192,13 +1190,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>54.33</v>
+        <v>54.42</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1207,13 +1205,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>54.54</v>
+        <v>54.52</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1222,13 +1220,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>53.11</v>
+        <v>54.33</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1237,13 +1235,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>53.15</v>
+        <v>54.54</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1252,13 +1250,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>53.47</v>
+        <v>53.11</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1267,13 +1265,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>51.5</v>
+        <v>53.15</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1282,13 +1280,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>51.69</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1297,13 +1295,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>50.77</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1312,13 +1310,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>50.2</v>
+        <v>51.69</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1327,13 +1325,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>49.97</v>
+        <v>50.77</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1342,13 +1340,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>49.84</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1357,13 +1355,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>49.95</v>
+        <v>49.97</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1372,13 +1370,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>50.41</v>
+        <v>49.84</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1387,13 +1385,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>49.83</v>
+        <v>49.95</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1402,13 +1400,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>49.09</v>
+        <v>50.41</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1417,13 +1415,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>49.94</v>
+        <v>49.83</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1432,13 +1430,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>49.8</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1447,13 +1445,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>49.73</v>
+        <v>49.94</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1462,13 +1460,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>50</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1477,13 +1475,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>49.28</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1492,13 +1490,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>49.58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1507,13 +1505,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>48.92</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1522,13 +1520,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>49.1</v>
+        <v>49.58</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1537,13 +1535,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>49.53</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1552,13 +1550,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>49.4</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1567,13 +1565,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>50.45</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1582,13 +1580,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>51.03</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1597,13 +1595,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>51.68</v>
+        <v>50.45</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1612,13 +1610,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>51.96</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1627,13 +1625,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>51.88</v>
+        <v>51.68</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1642,13 +1640,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>52.04</v>
+        <v>51.96</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1657,13 +1655,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>52.54</v>
+        <v>51.88</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1672,13 +1670,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>52.63</v>
+        <v>52.04</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1693,7 +1691,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1702,13 +1700,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>53.51</v>
+        <v>52.63</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1717,13 +1715,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>53.16</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1732,13 +1730,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>52.84</v>
+        <v>53.51</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1747,13 +1745,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>51.89</v>
+        <v>53.16</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1762,13 +1760,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>51.51</v>
+        <v>52.84</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1777,13 +1775,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>51.41</v>
+        <v>51.89</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1792,13 +1790,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>51.47</v>
+        <v>51.51</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1807,13 +1805,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>51.83</v>
+        <v>51.41</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -1822,13 +1820,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>52.3</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -1837,13 +1835,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>53.35</v>
+        <v>51.83</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1852,13 +1850,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>52.36</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1867,13 +1865,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>51.46</v>
+        <v>53.35</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -1882,13 +1880,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>51.56</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1897,13 +1895,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>51.9</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1912,13 +1910,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>52.33</v>
+        <v>51.56</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -1927,13 +1925,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -1942,13 +1940,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>50.9</v>
+        <v>52.33</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -1957,13 +1955,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>50.56</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -1972,13 +1970,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>50.88</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -1987,13 +1985,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>50.76</v>
+        <v>50.56</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2002,13 +2000,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>51.08</v>
+        <v>50.88</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2017,13 +2015,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>50</v>
+        <v>50.76</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2032,13 +2030,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>50.88</v>
+        <v>51.08</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2047,13 +2045,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>51.34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2062,13 +2060,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>51.46</v>
+        <v>50.88</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2077,13 +2075,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>51.93</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2092,13 +2090,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>51.4</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2113,7 +2111,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2122,13 +2120,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>51.21</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2137,13 +2135,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>51.72</v>
+        <v>51.93</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2152,13 +2150,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>52.32</v>
+        <v>51.21</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2167,13 +2165,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>52.09</v>
+        <v>51.72</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2182,13 +2180,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>51.84</v>
+        <v>52.32</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2197,13 +2195,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>51.73</v>
+        <v>52.09</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2212,13 +2210,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>51.47</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2227,13 +2225,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>51.47</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2242,13 +2240,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>50.86</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2257,13 +2255,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>51.84</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2272,13 +2270,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>52.41</v>
+        <v>50.86</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2287,13 +2285,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>51.89</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2302,13 +2300,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>51.33</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2317,13 +2315,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>51.02</v>
+        <v>51.89</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2332,13 +2330,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>51.38</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2347,13 +2345,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>51.34</v>
+        <v>51.02</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2362,13 +2360,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>50.46</v>
+        <v>51.38</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2377,13 +2375,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>50.74</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -2392,13 +2390,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>51.27</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -2407,13 +2405,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>51.34</v>
+        <v>50.74</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -2422,13 +2420,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>50.92</v>
+        <v>51.27</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -2437,13 +2435,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>50.93</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -2452,13 +2450,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>50.7</v>
+        <v>50.92</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -2467,13 +2465,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>51.5</v>
+        <v>50.93</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -2482,13 +2480,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>52.03</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -2497,13 +2495,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>52.59</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -2512,13 +2510,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>53.81</v>
+        <v>52.03</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -2527,13 +2525,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>52.98</v>
+        <v>52.59</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -2542,13 +2540,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>52.98</v>
+        <v>53.81</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -2557,13 +2555,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>52.41</v>
+        <v>52.98</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -2572,13 +2570,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>51.85</v>
+        <v>52.98</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -2587,13 +2585,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>51.41</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -2602,13 +2600,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>52.36</v>
+        <v>51.85</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -2617,13 +2615,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>52.02</v>
+        <v>51.41</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -2632,13 +2630,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>52.63</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -2647,13 +2645,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>52.54</v>
+        <v>52.02</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -2662,13 +2660,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>53.3</v>
+        <v>52.63</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -2677,13 +2675,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>52.79</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -2692,13 +2690,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>53.07</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -2707,13 +2705,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>53.82</v>
+        <v>52.79</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -2722,13 +2720,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>53.93</v>
+        <v>53.07</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -2737,13 +2735,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>55.12</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -2752,13 +2750,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>55.41</v>
+        <v>53.93</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -2767,13 +2765,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>54.01</v>
+        <v>55.12</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -2782,13 +2780,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>51.87</v>
+        <v>55.41</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -2797,13 +2795,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>52.23</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -2812,13 +2810,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>53.59</v>
+        <v>51.87</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -2827,13 +2825,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>53.31</v>
+        <v>52.23</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -2842,13 +2840,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>52.27</v>
+        <v>53.59</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -2857,13 +2855,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>53.3</v>
+        <v>53.31</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -2872,13 +2870,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>53</v>
+        <v>52.27</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -2887,13 +2885,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>52.87</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -2902,13 +2900,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>52.46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -2917,13 +2915,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>53.33</v>
+        <v>52.87</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -2932,13 +2930,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>53.53</v>
+        <v>52.46</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -2947,13 +2945,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>53.25</v>
+        <v>53.33</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -2962,13 +2960,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>53.87</v>
+        <v>53.53</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -2977,13 +2975,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>53.61</v>
+        <v>53.25</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -2992,13 +2990,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>54.32</v>
+        <v>53.87</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3007,13 +3005,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>55.55</v>
+        <v>53.61</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3022,13 +3020,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>56.24</v>
+        <v>54.32</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -3037,13 +3035,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>55.61</v>
+        <v>55.55</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -3052,13 +3050,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>55.47</v>
+        <v>56.24</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3067,13 +3065,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>55.8</v>
+        <v>55.61</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -3082,13 +3080,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>55.34</v>
+        <v>55.47</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3097,13 +3095,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>54.93</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -3112,13 +3110,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>55.29</v>
+        <v>55.34</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -3127,13 +3125,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>55.02</v>
+        <v>54.93</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -3142,13 +3140,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>55.59</v>
+        <v>55.29</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -3157,13 +3155,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>54.31</v>
+        <v>55.02</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -3172,13 +3170,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>54.1</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -3187,13 +3185,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>53.8</v>
+        <v>54.31</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -3202,13 +3200,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>53.47</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -3217,13 +3215,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>53.38</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -3232,13 +3230,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>53.17</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -3247,13 +3245,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>53.82</v>
+        <v>53.38</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -3262,13 +3260,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>53.64</v>
+        <v>53.17</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -3277,13 +3275,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>54.46</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -3292,13 +3290,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>54.77</v>
+        <v>53.64</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -3307,13 +3305,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>53.48</v>
+        <v>54.46</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -3322,13 +3320,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>52.62</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -3337,13 +3335,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>52.52</v>
+        <v>53.48</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -3352,13 +3350,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>52.86</v>
+        <v>52.62</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -3367,13 +3365,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>52.43</v>
+        <v>52.52</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -3382,13 +3380,13 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>52.69</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -3397,13 +3395,13 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>53.79</v>
+        <v>52.43</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -3412,13 +3410,13 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>55.04</v>
+        <v>52.69</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -3427,13 +3425,13 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>55.23</v>
+        <v>53.79</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -3442,13 +3440,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>55.16</v>
+        <v>55.04</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -3457,13 +3455,13 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>55.1</v>
+        <v>55.23</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -3472,13 +3470,13 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>51.65</v>
+        <v>55.16</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -3487,13 +3485,13 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>48.65</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -3502,13 +3500,13 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>48.94</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -3517,13 +3515,13 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>48.82</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -3532,13 +3530,13 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>48.46</v>
+        <v>48.94</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -3547,13 +3545,13 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>48.62</v>
+        <v>48.82</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -3562,13 +3560,13 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>47.95</v>
+        <v>48.46</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -3577,13 +3575,13 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>47.8</v>
+        <v>48.62</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -3592,13 +3590,13 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>47.85</v>
+        <v>47.95</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -3607,13 +3605,13 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>47.49</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -3622,13 +3620,13 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>47.78</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -3637,13 +3635,13 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>49.05</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -3652,13 +3650,13 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>49.41</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -3667,13 +3665,13 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>50.03</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -3682,13 +3680,13 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>49.88</v>
+        <v>49.41</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -3697,13 +3695,13 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>49.73</v>
+        <v>50.03</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -3712,13 +3710,13 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>50.23</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -3727,13 +3725,13 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>49.88</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -3742,13 +3740,13 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>49.78</v>
+        <v>50.23</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -3757,13 +3755,13 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>49.2</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -3772,13 +3770,13 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>48.9</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -3787,13 +3785,13 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>51.9</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -3802,13 +3800,13 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>51.46</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -3817,13 +3815,13 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>50.03</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -3832,13 +3830,13 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>48.66</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -3847,13 +3845,13 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>48.38</v>
+        <v>50.03</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -3862,13 +3860,13 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>47.52</v>
+        <v>48.66</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -3877,13 +3875,13 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>48.22</v>
+        <v>48.38</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -3892,13 +3890,13 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>48.33</v>
+        <v>47.52</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -3907,13 +3905,13 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>48.82</v>
+        <v>48.22</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -3922,13 +3920,13 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>48.95</v>
+        <v>48.33</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -3937,13 +3935,13 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>48.22</v>
+        <v>48.82</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -3952,13 +3950,13 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>48.75</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -3967,13 +3965,13 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>49.78</v>
+        <v>48.22</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -3982,13 +3980,13 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>49.23</v>
+        <v>48.75</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -3997,13 +3995,13 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>49.17</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -4012,13 +4010,13 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>47.85</v>
+        <v>49.23</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -4027,13 +4025,13 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>47.78</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -4042,13 +4040,13 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>47.83</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -4057,13 +4055,13 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>47.91</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -4072,13 +4070,13 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>47.73</v>
+        <v>47.83</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -4087,13 +4085,13 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>47.54</v>
+        <v>47.91</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -4102,13 +4100,13 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>46.72</v>
+        <v>47.73</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -4117,13 +4115,13 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>47.16</v>
+        <v>47.54</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -4132,13 +4130,13 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>46.15</v>
+        <v>46.72</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -4147,13 +4145,13 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>46.11</v>
+        <v>47.16</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -4162,13 +4160,13 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>44.82</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -4177,13 +4175,13 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>45.02</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -4192,13 +4190,13 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>45.96</v>
+        <v>44.82</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -4207,13 +4205,13 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>47.35</v>
+        <v>45.02</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -4222,13 +4220,13 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>48.65</v>
+        <v>45.96</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -4237,13 +4235,13 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>47.87</v>
+        <v>47.35</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -4252,13 +4250,13 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>46</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -4267,13 +4265,13 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>46.11</v>
+        <v>47.87</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -4282,13 +4280,13 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>45.42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -4297,13 +4295,13 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>44.2</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -4312,13 +4310,13 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>43.82</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -4327,13 +4325,13 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>43.48</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -4342,13 +4340,13 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>43.28</v>
+        <v>43.82</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -4357,13 +4355,13 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>43.7</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -4372,13 +4370,13 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>43.32</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -4387,13 +4385,13 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>43.28</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -4402,13 +4400,13 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>42.9</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -4417,13 +4415,13 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>42.51</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -4432,13 +4430,13 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>42.36</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -4447,13 +4445,13 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>42.65</v>
+        <v>42.51</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -4462,13 +4460,13 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>42.85</v>
+        <v>42.36</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -4477,13 +4475,13 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>43.04</v>
+        <v>42.65</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -4492,13 +4490,13 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>43.92</v>
+        <v>42.85</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -4507,13 +4505,13 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>43.52</v>
+        <v>43.04</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -4522,13 +4520,13 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>43.37</v>
+        <v>43.92</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -4537,13 +4535,13 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>43.24</v>
+        <v>43.52</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -4552,13 +4550,13 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>43.99</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -4567,13 +4565,13 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>44.52</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -4582,13 +4580,13 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>45.66</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -4597,13 +4595,13 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>45.78</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -4612,13 +4610,13 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>46.1</v>
+        <v>45.66</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -4627,13 +4625,13 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>46.42</v>
+        <v>45.78</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -4642,13 +4640,13 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>47.21</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -4657,13 +4655,13 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>47.44</v>
+        <v>46.42</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -4672,13 +4670,13 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>46.5</v>
+        <v>47.21</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -4687,13 +4685,13 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>47.21</v>
+        <v>47.44</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -4702,13 +4700,13 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>46.08</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -4717,13 +4715,13 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>46.21</v>
+        <v>47.21</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -4732,13 +4730,13 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>45.72</v>
+        <v>46.08</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -4747,13 +4745,13 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>46.29</v>
+        <v>46.21</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -4762,13 +4760,13 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>45.9</v>
+        <v>45.72</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -4777,13 +4775,13 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>46.05</v>
+        <v>46.29</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -4792,13 +4790,13 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>45.73</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -4807,13 +4805,13 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>45.31</v>
+        <v>46.05</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -4822,13 +4820,13 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>45.75</v>
+        <v>45.73</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -4837,13 +4835,13 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>46.37</v>
+        <v>45.31</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -4852,13 +4850,13 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>45.77</v>
+        <v>45.75</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -4867,13 +4865,13 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>45.1</v>
+        <v>46.37</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -4882,13 +4880,13 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>44.97</v>
+        <v>45.77</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -4897,13 +4895,13 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>45.11</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -4912,13 +4910,13 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>44.88</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -4927,13 +4925,13 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>45.06</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -4942,13 +4940,13 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>44.73</v>
+        <v>44.88</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -4957,13 +4955,13 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>44.3</v>
+        <v>45.06</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -4972,13 +4970,13 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>45.15</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -4987,13 +4985,13 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>45.27</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -5002,13 +5000,13 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>45.03</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -5017,13 +5015,13 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>45.99</v>
+        <v>45.27</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -5032,13 +5030,13 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>46.22</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -5047,13 +5045,13 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>46.06</v>
+        <v>45.99</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -5062,13 +5060,13 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>45.62</v>
+        <v>46.22</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -5077,13 +5075,13 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>43.48</v>
+        <v>46.06</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -5092,13 +5090,13 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>42.45</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -5107,13 +5105,13 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>42.17</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -5122,13 +5120,13 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>41.34</v>
+        <v>42.45</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -5137,13 +5135,13 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>40.87</v>
+        <v>42.17</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -5152,13 +5150,13 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>41.09</v>
+        <v>41.34</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -5167,13 +5165,13 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>41.32</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -5182,13 +5180,13 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>41.19</v>
+        <v>41.09</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -5197,13 +5195,13 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>40.94</v>
+        <v>41.32</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -5212,13 +5210,13 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>40.94</v>
+        <v>41.19</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2024-12-24</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -5227,13 +5225,13 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>41.38</v>
+        <v>40.94</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -5242,13 +5240,13 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>41.62</v>
+        <v>40.94</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -5257,13 +5255,13 @@
         </is>
       </c>
       <c r="C322" t="n">
-        <v>40.87</v>
+        <v>41.38</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -5272,13 +5270,13 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>41.15</v>
+        <v>41.62</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -5287,13 +5285,13 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>40.92</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -5302,13 +5300,13 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>41.73</v>
+        <v>41.15</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -5317,13 +5315,13 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>42.72</v>
+        <v>40.92</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -5332,13 +5330,13 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>43.49</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -5347,13 +5345,13 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>43.53</v>
+        <v>42.72</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -5362,13 +5360,13 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>43.26</v>
+        <v>43.49</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -5377,13 +5375,13 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>43.46</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -5392,13 +5390,13 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>43.52</v>
+        <v>43.26</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -5407,13 +5405,13 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>43.58</v>
+        <v>43.46</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -5422,13 +5420,13 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>42.89</v>
+        <v>43.52</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -5437,13 +5435,13 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>42.12</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -5452,13 +5450,13 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>42.67</v>
+        <v>42.89</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -5467,13 +5465,13 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>42.3</v>
+        <v>42.12</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -5482,13 +5480,13 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>42.39</v>
+        <v>42.67</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -5497,13 +5495,13 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>41.84</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -5512,13 +5510,13 @@
         </is>
       </c>
       <c r="C339" t="n">
-        <v>43.17</v>
+        <v>42.39</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -5527,13 +5525,13 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>42.27</v>
+        <v>41.84</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -5542,13 +5540,13 @@
         </is>
       </c>
       <c r="C341" t="n">
-        <v>42.78</v>
+        <v>43.17</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -5557,13 +5555,13 @@
         </is>
       </c>
       <c r="C342" t="n">
-        <v>43.09</v>
+        <v>42.27</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -5572,13 +5570,13 @@
         </is>
       </c>
       <c r="C343" t="n">
-        <v>43.95</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -5587,13 +5585,13 @@
         </is>
       </c>
       <c r="C344" t="n">
-        <v>44.91</v>
+        <v>43.09</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -5602,13 +5600,13 @@
         </is>
       </c>
       <c r="C345" t="n">
-        <v>45.32</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -5617,13 +5615,13 @@
         </is>
       </c>
       <c r="C346" t="n">
-        <v>45.24</v>
+        <v>44.91</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -5632,13 +5630,13 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>44.48</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -5647,13 +5645,13 @@
         </is>
       </c>
       <c r="C348" t="n">
-        <v>45.38</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -5662,13 +5660,13 @@
         </is>
       </c>
       <c r="C349" t="n">
-        <v>46.24</v>
+        <v>44.48</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -5677,13 +5675,13 @@
         </is>
       </c>
       <c r="C350" t="n">
-        <v>47.78</v>
+        <v>45.38</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -5692,13 +5690,13 @@
         </is>
       </c>
       <c r="C351" t="n">
-        <v>48.04</v>
+        <v>46.24</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -5707,13 +5705,13 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>47.49</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -5722,13 +5720,13 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>45.65</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -5737,13 +5735,13 @@
         </is>
       </c>
       <c r="C354" t="n">
-        <v>45.01</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -5752,13 +5750,13 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>45.36</v>
+        <v>45.65</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -5767,13 +5765,13 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>45.49</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -5782,13 +5780,13 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>44.54</v>
+        <v>45.36</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -5797,13 +5795,13 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>43.62</v>
+        <v>45.49</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -5812,13 +5810,13 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>42.78</v>
+        <v>44.54</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -5827,13 +5825,13 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>42.73</v>
+        <v>43.62</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -5842,13 +5840,13 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>43.65</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -5857,13 +5855,13 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>43.48</v>
+        <v>42.73</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -5872,13 +5870,13 @@
         </is>
       </c>
       <c r="C363" t="n">
-        <v>42.77</v>
+        <v>43.65</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -5887,13 +5885,13 @@
         </is>
       </c>
       <c r="C364" t="n">
-        <v>42.86</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -5902,13 +5900,13 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>41.8</v>
+        <v>42.77</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -5917,13 +5915,13 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>41.24</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -5932,13 +5930,13 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>41.92</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -5947,13 +5945,13 @@
         </is>
       </c>
       <c r="C368" t="n">
-        <v>41.59</v>
+        <v>41.24</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -5962,13 +5960,13 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>42.03</v>
+        <v>41.92</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -5977,13 +5975,13 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>42.03</v>
+        <v>41.59</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -5992,13 +5990,13 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>43.28</v>
+        <v>42.03</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -6007,13 +6005,13 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>43.74</v>
+        <v>42.03</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -6022,13 +6020,13 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>43.16</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -6037,13 +6035,13 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>43.22</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -6052,13 +6050,13 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>44.73</v>
+        <v>43.16</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -6067,13 +6065,13 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>44.08</v>
+        <v>43.22</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -6082,13 +6080,13 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>44.43</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -6097,13 +6095,13 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>43.57</v>
+        <v>44.08</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -6112,13 +6110,13 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>43.08</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -6127,13 +6125,13 @@
         </is>
       </c>
       <c r="C380" t="n">
-        <v>43.05</v>
+        <v>43.57</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -6142,13 +6140,13 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>42.78</v>
+        <v>43.08</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -6157,13 +6155,13 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>43.53</v>
+        <v>43.05</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -6172,13 +6170,13 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>43.71</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -6187,13 +6185,13 @@
         </is>
       </c>
       <c r="C384" t="n">
-        <v>43.14</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -6202,13 +6200,13 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>42.09</v>
+        <v>43.71</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -6217,13 +6215,13 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>41.73</v>
+        <v>43.14</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -6232,13 +6230,13 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>41.43</v>
+        <v>42.09</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -6247,13 +6245,13 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>41.17</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -6262,13 +6260,13 @@
         </is>
       </c>
       <c r="C389" t="n">
-        <v>40.69</v>
+        <v>41.43</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -6277,13 +6275,13 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>40.11</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -6292,13 +6290,13 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>40.12</v>
+        <v>40.69</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -6307,13 +6305,13 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>40.75</v>
+        <v>40.11</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -6322,13 +6320,13 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>40.39</v>
+        <v>40.12</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -6337,13 +6335,13 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>40.6</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -6352,13 +6350,13 @@
         </is>
       </c>
       <c r="C395" t="n">
-        <v>41.29</v>
+        <v>40.39</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -6367,13 +6365,13 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>40.49</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -6382,13 +6380,13 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>41.62</v>
+        <v>41.29</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -6397,13 +6395,13 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>40.98</v>
+        <v>40.49</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -6412,13 +6410,13 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>41.5</v>
+        <v>41.62</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -6427,13 +6425,13 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>42.26</v>
+        <v>40.98</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -6442,13 +6440,13 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>42.24</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -6457,13 +6455,13 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>41.21</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -6472,13 +6470,13 @@
         </is>
       </c>
       <c r="C403" t="n">
-        <v>40.93</v>
+        <v>42.24</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -6487,13 +6485,13 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>40.83</v>
+        <v>41.21</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -6502,13 +6500,13 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>40.51</v>
+        <v>40.93</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -6517,13 +6515,13 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>39.52</v>
+        <v>40.83</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -6532,13 +6530,13 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>40.05</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -6547,13 +6545,13 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>39.68</v>
+        <v>39.52</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -6562,13 +6560,13 @@
         </is>
       </c>
       <c r="C409" t="n">
-        <v>39.76</v>
+        <v>40.05</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -6577,13 +6575,13 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>39.55</v>
+        <v>39.68</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -6592,13 +6590,13 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>39.29</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -6607,13 +6605,13 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>39.58</v>
+        <v>39.55</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -6622,13 +6620,13 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>39.89</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -6637,13 +6635,13 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>40.84</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -6652,13 +6650,13 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>40.75</v>
+        <v>39.89</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -6667,13 +6665,13 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>40.68</v>
+        <v>40.84</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -6682,13 +6680,13 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>40.51</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -6697,13 +6695,13 @@
         </is>
       </c>
       <c r="C418" t="n">
-        <v>40.16</v>
+        <v>40.68</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -6712,13 +6710,13 @@
         </is>
       </c>
       <c r="C419" t="n">
-        <v>40.25</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -6727,13 +6725,13 @@
         </is>
       </c>
       <c r="C420" t="n">
-        <v>40.91</v>
+        <v>40.16</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -6742,13 +6740,13 @@
         </is>
       </c>
       <c r="C421" t="n">
-        <v>41.18</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -6757,13 +6755,13 @@
         </is>
       </c>
       <c r="C422" t="n">
-        <v>41.72</v>
+        <v>40.91</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -6772,13 +6770,13 @@
         </is>
       </c>
       <c r="C423" t="n">
-        <v>41.2</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -6787,13 +6785,13 @@
         </is>
       </c>
       <c r="C424" t="n">
-        <v>41.67</v>
+        <v>41.72</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -6802,13 +6800,13 @@
         </is>
       </c>
       <c r="C425" t="n">
-        <v>41.34</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -6817,13 +6815,13 @@
         </is>
       </c>
       <c r="C426" t="n">
-        <v>42.82</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -6832,13 +6830,13 @@
         </is>
       </c>
       <c r="C427" t="n">
-        <v>42.57</v>
+        <v>41.34</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -6847,13 +6845,13 @@
         </is>
       </c>
       <c r="C428" t="n">
-        <v>43.28</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -6862,13 +6860,13 @@
         </is>
       </c>
       <c r="C429" t="n">
-        <v>42.86</v>
+        <v>42.57</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -6877,13 +6875,13 @@
         </is>
       </c>
       <c r="C430" t="n">
-        <v>41.96</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -6892,13 +6890,13 @@
         </is>
       </c>
       <c r="C431" t="n">
-        <v>42.63</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -6907,13 +6905,13 @@
         </is>
       </c>
       <c r="C432" t="n">
-        <v>42.6</v>
+        <v>41.96</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -6922,13 +6920,13 @@
         </is>
       </c>
       <c r="C433" t="n">
-        <v>43.39</v>
+        <v>42.63</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -6937,13 +6935,13 @@
         </is>
       </c>
       <c r="C434" t="n">
-        <v>43.49</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -6952,13 +6950,13 @@
         </is>
       </c>
       <c r="C435" t="n">
-        <v>44.6</v>
+        <v>43.39</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -6967,13 +6965,13 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>45.01</v>
+        <v>43.49</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -6982,13 +6980,13 @@
         </is>
       </c>
       <c r="C437" t="n">
-        <v>44.73</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -6997,13 +6995,13 @@
         </is>
       </c>
       <c r="C438" t="n">
-        <v>45.87</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -7012,13 +7010,13 @@
         </is>
       </c>
       <c r="C439" t="n">
-        <v>46.97</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -7027,13 +7025,13 @@
         </is>
       </c>
       <c r="C440" t="n">
-        <v>47.02</v>
+        <v>45.87</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -7042,13 +7040,13 @@
         </is>
       </c>
       <c r="C441" t="n">
-        <v>46.75</v>
+        <v>46.97</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -7057,13 +7055,13 @@
         </is>
       </c>
       <c r="C442" t="n">
-        <v>45.79</v>
+        <v>47.02</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -7072,13 +7070,13 @@
         </is>
       </c>
       <c r="C443" t="n">
-        <v>44.84</v>
+        <v>46.75</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -7087,13 +7085,13 @@
         </is>
       </c>
       <c r="C444" t="n">
-        <v>43.13</v>
+        <v>45.79</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -7102,13 +7100,13 @@
         </is>
       </c>
       <c r="C445" t="n">
-        <v>42.97</v>
+        <v>44.84</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -7117,13 +7115,13 @@
         </is>
       </c>
       <c r="C446" t="n">
-        <v>43.37</v>
+        <v>43.13</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -7132,13 +7130,13 @@
         </is>
       </c>
       <c r="C447" t="n">
-        <v>42.71</v>
+        <v>42.97</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -7147,13 +7145,13 @@
         </is>
       </c>
       <c r="C448" t="n">
-        <v>43.35</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -7162,13 +7160,13 @@
         </is>
       </c>
       <c r="C449" t="n">
-        <v>43.58</v>
+        <v>42.71</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -7177,13 +7175,13 @@
         </is>
       </c>
       <c r="C450" t="n">
-        <v>43.59</v>
+        <v>43.35</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -7192,13 +7190,13 @@
         </is>
       </c>
       <c r="C451" t="n">
-        <v>44.01</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -7207,13 +7205,13 @@
         </is>
       </c>
       <c r="C452" t="n">
-        <v>43.56</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -7222,13 +7220,13 @@
         </is>
       </c>
       <c r="C453" t="n">
-        <v>43.53</v>
+        <v>44.01</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -7237,13 +7235,13 @@
         </is>
       </c>
       <c r="C454" t="n">
-        <v>43.76</v>
+        <v>43.56</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -7252,13 +7250,13 @@
         </is>
       </c>
       <c r="C455" t="n">
-        <v>43.87</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -7273,7 +7271,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -7282,13 +7280,13 @@
         </is>
       </c>
       <c r="C457" t="n">
-        <v>43.98</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -7297,13 +7295,13 @@
         </is>
       </c>
       <c r="C458" t="n">
-        <v>44.29</v>
+        <v>43.76</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -7312,13 +7310,13 @@
         </is>
       </c>
       <c r="C459" t="n">
-        <v>44.83</v>
+        <v>43.98</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -7327,13 +7325,13 @@
         </is>
       </c>
       <c r="C460" t="n">
-        <v>43.88</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -7342,13 +7340,13 @@
         </is>
       </c>
       <c r="C461" t="n">
-        <v>44.2</v>
+        <v>44.83</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -7357,13 +7355,13 @@
         </is>
       </c>
       <c r="C462" t="n">
-        <v>44.63</v>
+        <v>43.88</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -7372,13 +7370,13 @@
         </is>
       </c>
       <c r="C463" t="n">
-        <v>45.81</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -7387,13 +7385,13 @@
         </is>
       </c>
       <c r="C464" t="n">
-        <v>45.93</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -7402,13 +7400,13 @@
         </is>
       </c>
       <c r="C465" t="n">
-        <v>46.11</v>
+        <v>45.81</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -7417,13 +7415,13 @@
         </is>
       </c>
       <c r="C466" t="n">
-        <v>45.74</v>
+        <v>45.93</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -7432,13 +7430,13 @@
         </is>
       </c>
       <c r="C467" t="n">
-        <v>45.32</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -7447,13 +7445,13 @@
         </is>
       </c>
       <c r="C468" t="n">
-        <v>45.96</v>
+        <v>45.74</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -7462,13 +7460,13 @@
         </is>
       </c>
       <c r="C469" t="n">
-        <v>46.2</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -7477,13 +7475,13 @@
         </is>
       </c>
       <c r="C470" t="n">
-        <v>46.37</v>
+        <v>45.96</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -7492,13 +7490,13 @@
         </is>
       </c>
       <c r="C471" t="n">
-        <v>46.6</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -7507,13 +7505,13 @@
         </is>
       </c>
       <c r="C472" t="n">
-        <v>45.89</v>
+        <v>46.37</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -7522,13 +7520,13 @@
         </is>
       </c>
       <c r="C473" t="n">
-        <v>45.45</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -7537,13 +7535,13 @@
         </is>
       </c>
       <c r="C474" t="n">
-        <v>44.82</v>
+        <v>45.89</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -7552,13 +7550,13 @@
         </is>
       </c>
       <c r="C475" t="n">
-        <v>44.7</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -7567,13 +7565,13 @@
         </is>
       </c>
       <c r="C476" t="n">
-        <v>46.01</v>
+        <v>44.82</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -7582,13 +7580,13 @@
         </is>
       </c>
       <c r="C477" t="n">
-        <v>45.24</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -7597,13 +7595,13 @@
         </is>
       </c>
       <c r="C478" t="n">
-        <v>44.2</v>
+        <v>46.01</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -7612,13 +7610,13 @@
         </is>
       </c>
       <c r="C479" t="n">
-        <v>44.8</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -7627,13 +7625,13 @@
         </is>
       </c>
       <c r="C480" t="n">
-        <v>45.29</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -7642,13 +7640,13 @@
         </is>
       </c>
       <c r="C481" t="n">
-        <v>44.66</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -7657,13 +7655,13 @@
         </is>
       </c>
       <c r="C482" t="n">
-        <v>44.34</v>
+        <v>45.29</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -7672,13 +7670,13 @@
         </is>
       </c>
       <c r="C483" t="n">
-        <v>44.43</v>
+        <v>44.66</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -7687,13 +7685,13 @@
         </is>
       </c>
       <c r="C484" t="n">
-        <v>44.49</v>
+        <v>44.34</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -7702,13 +7700,13 @@
         </is>
       </c>
       <c r="C485" t="n">
-        <v>44.32</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -7717,13 +7715,13 @@
         </is>
       </c>
       <c r="C486" t="n">
-        <v>45.01</v>
+        <v>44.49</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -7732,13 +7730,13 @@
         </is>
       </c>
       <c r="C487" t="n">
-        <v>45.94</v>
+        <v>44.32</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -7747,13 +7745,13 @@
         </is>
       </c>
       <c r="C488" t="n">
-        <v>45.67</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -7762,13 +7760,13 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>45.58</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -7777,13 +7775,13 @@
         </is>
       </c>
       <c r="C490" t="n">
-        <v>45.95</v>
+        <v>45.67</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -7792,13 +7790,13 @@
         </is>
       </c>
       <c r="C491" t="n">
-        <v>45.8</v>
+        <v>45.58</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -7807,13 +7805,13 @@
         </is>
       </c>
       <c r="C492" t="n">
-        <v>45.14</v>
+        <v>45.95</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -7822,13 +7820,13 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>44.97</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -7837,13 +7835,13 @@
         </is>
       </c>
       <c r="C494" t="n">
-        <v>45.19</v>
+        <v>45.14</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -7852,13 +7850,13 @@
         </is>
       </c>
       <c r="C495" t="n">
-        <v>45.34</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -7867,13 +7865,13 @@
         </is>
       </c>
       <c r="C496" t="n">
-        <v>45.6</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -7882,13 +7880,13 @@
         </is>
       </c>
       <c r="C497" t="n">
-        <v>45.97</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -7897,13 +7895,13 @@
         </is>
       </c>
       <c r="C498" t="n">
-        <v>45.91</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -7912,13 +7910,13 @@
         </is>
       </c>
       <c r="C499" t="n">
-        <v>46.95</v>
+        <v>45.97</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -7927,13 +7925,13 @@
         </is>
       </c>
       <c r="C500" t="n">
-        <v>46.91</v>
+        <v>45.91</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -7942,13 +7940,13 @@
         </is>
       </c>
       <c r="C501" t="n">
-        <v>47.23</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -7957,13 +7955,13 @@
         </is>
       </c>
       <c r="C502" t="n">
-        <v>47.84</v>
+        <v>46.91</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -7972,13 +7970,13 @@
         </is>
       </c>
       <c r="C503" t="n">
-        <v>47.38</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -7987,13 +7985,13 @@
         </is>
       </c>
       <c r="C504" t="n">
-        <v>48</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -8002,13 +8000,13 @@
         </is>
       </c>
       <c r="C505" t="n">
-        <v>47.67</v>
+        <v>47.38</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -8017,13 +8015,13 @@
         </is>
       </c>
       <c r="C506" t="n">
-        <v>47.12</v>
+        <v>48</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -8032,13 +8030,13 @@
         </is>
       </c>
       <c r="C507" t="n">
-        <v>47.14</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -8047,13 +8045,13 @@
         </is>
       </c>
       <c r="C508" t="n">
-        <v>46.67</v>
+        <v>47.12</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -8062,13 +8060,13 @@
         </is>
       </c>
       <c r="C509" t="n">
-        <v>47.46</v>
+        <v>47.14</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -8077,13 +8075,13 @@
         </is>
       </c>
       <c r="C510" t="n">
-        <v>47.71</v>
+        <v>46.67</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -8092,13 +8090,13 @@
         </is>
       </c>
       <c r="C511" t="n">
-        <v>46.65</v>
+        <v>47.46</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -8107,13 +8105,13 @@
         </is>
       </c>
       <c r="C512" t="n">
-        <v>47.72</v>
+        <v>47.71</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -8122,13 +8120,13 @@
         </is>
       </c>
       <c r="C513" t="n">
-        <v>47.89</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -8137,13 +8135,13 @@
         </is>
       </c>
       <c r="C514" t="n">
-        <v>47.23</v>
+        <v>47.72</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -8152,13 +8150,13 @@
         </is>
       </c>
       <c r="C515" t="n">
-        <v>47.63</v>
+        <v>47.89</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -8167,13 +8165,13 @@
         </is>
       </c>
       <c r="C516" t="n">
-        <v>48.16</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -8182,13 +8180,13 @@
         </is>
       </c>
       <c r="C517" t="n">
-        <v>47.08</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -8197,13 +8195,13 @@
         </is>
       </c>
       <c r="C518" t="n">
-        <v>47.34</v>
+        <v>48.16</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -8212,13 +8210,13 @@
         </is>
       </c>
       <c r="C519" t="n">
-        <v>46.61</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -8227,13 +8225,13 @@
         </is>
       </c>
       <c r="C520" t="n">
-        <v>45.84</v>
+        <v>47.34</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -8242,13 +8240,13 @@
         </is>
       </c>
       <c r="C521" t="n">
-        <v>45.28</v>
+        <v>46.61</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -8257,13 +8255,13 @@
         </is>
       </c>
       <c r="C522" t="n">
-        <v>45.23</v>
+        <v>45.84</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -8272,13 +8270,13 @@
         </is>
       </c>
       <c r="C523" t="n">
-        <v>44.51</v>
+        <v>45.28</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -8287,13 +8285,13 @@
         </is>
       </c>
       <c r="C524" t="n">
-        <v>44.37</v>
+        <v>45.23</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -8302,13 +8300,13 @@
         </is>
       </c>
       <c r="C525" t="n">
-        <v>44.55</v>
+        <v>44.51</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -8317,13 +8315,13 @@
         </is>
       </c>
       <c r="C526" t="n">
-        <v>44.45</v>
+        <v>44.37</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -8332,13 +8330,13 @@
         </is>
       </c>
       <c r="C527" t="n">
-        <v>44.56</v>
+        <v>44.55</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -8347,13 +8345,13 @@
         </is>
       </c>
       <c r="C528" t="n">
-        <v>44.63</v>
+        <v>44.45</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -8362,13 +8360,13 @@
         </is>
       </c>
       <c r="C529" t="n">
-        <v>44.69</v>
+        <v>44.56</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>2024-02-26</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -8377,13 +8375,13 @@
         </is>
       </c>
       <c r="C530" t="n">
-        <v>44.2</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -8392,13 +8390,13 @@
         </is>
       </c>
       <c r="C531" t="n">
-        <v>43.78</v>
+        <v>44.69</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -8407,13 +8405,13 @@
         </is>
       </c>
       <c r="C532" t="n">
-        <v>43.99</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -8422,13 +8420,13 @@
         </is>
       </c>
       <c r="C533" t="n">
-        <v>44</v>
+        <v>43.78</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-22</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -8437,13 +8435,13 @@
         </is>
       </c>
       <c r="C534" t="n">
-        <v>44.35</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -8452,13 +8450,13 @@
         </is>
       </c>
       <c r="C535" t="n">
-        <v>44.52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -8467,13 +8465,13 @@
         </is>
       </c>
       <c r="C536" t="n">
-        <v>44.68</v>
+        <v>44.35</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -8482,13 +8480,13 @@
         </is>
       </c>
       <c r="C537" t="n">
-        <v>45.07</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -8497,13 +8495,13 @@
         </is>
       </c>
       <c r="C538" t="n">
-        <v>45.62</v>
+        <v>44.68</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -8512,13 +8510,13 @@
         </is>
       </c>
       <c r="C539" t="n">
-        <v>45.33</v>
+        <v>45.07</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -8527,13 +8525,13 @@
         </is>
       </c>
       <c r="C540" t="n">
-        <v>45.64</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -8542,13 +8540,13 @@
         </is>
       </c>
       <c r="C541" t="n">
-        <v>45.59</v>
+        <v>45.33</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-09</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -8557,13 +8555,13 @@
         </is>
       </c>
       <c r="C542" t="n">
-        <v>44.61</v>
+        <v>45.64</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -8572,13 +8570,13 @@
         </is>
       </c>
       <c r="C543" t="n">
-        <v>44.2</v>
+        <v>45.59</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -8587,13 +8585,13 @@
         </is>
       </c>
       <c r="C544" t="n">
-        <v>43.73</v>
+        <v>44.61</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -8602,13 +8600,13 @@
         </is>
       </c>
       <c r="C545" t="n">
-        <v>43.66</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -8617,13 +8615,13 @@
         </is>
       </c>
       <c r="C546" t="n">
-        <v>44.07</v>
+        <v>43.73</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -8632,13 +8630,13 @@
         </is>
       </c>
       <c r="C547" t="n">
-        <v>44.66</v>
+        <v>43.66</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -8647,13 +8645,13 @@
         </is>
       </c>
       <c r="C548" t="n">
-        <v>44.75</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -8662,13 +8660,13 @@
         </is>
       </c>
       <c r="C549" t="n">
-        <v>44.73</v>
+        <v>44.66</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024-01-30</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -8677,13 +8675,13 @@
         </is>
       </c>
       <c r="C550" t="n">
-        <v>45.37</v>
+        <v>44.75</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -8692,13 +8690,13 @@
         </is>
       </c>
       <c r="C551" t="n">
-        <v>45.34</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -8707,13 +8705,13 @@
         </is>
       </c>
       <c r="C552" t="n">
-        <v>45.57</v>
+        <v>45.37</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>2024-01-23</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -8722,13 +8720,13 @@
         </is>
       </c>
       <c r="C553" t="n">
-        <v>45.97</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -8737,13 +8735,13 @@
         </is>
       </c>
       <c r="C554" t="n">
-        <v>45.94</v>
+        <v>45.57</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>2024-01-19</t>
+          <t>2024-01-23</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -8752,13 +8750,13 @@
         </is>
       </c>
       <c r="C555" t="n">
-        <v>45.19</v>
+        <v>45.97</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-22</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -8767,13 +8765,13 @@
         </is>
       </c>
       <c r="C556" t="n">
-        <v>45.44</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -8782,13 +8780,13 @@
         </is>
       </c>
       <c r="C557" t="n">
-        <v>45.42</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -8797,13 +8795,13 @@
         </is>
       </c>
       <c r="C558" t="n">
-        <v>45.42</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -8812,13 +8810,13 @@
         </is>
       </c>
       <c r="C559" t="n">
-        <v>46.13</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>2024-01-11</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -8827,13 +8825,13 @@
         </is>
       </c>
       <c r="C560" t="n">
-        <v>46.6</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -8842,13 +8840,13 @@
         </is>
       </c>
       <c r="C561" t="n">
-        <v>46.28</v>
+        <v>46.13</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -8857,13 +8855,13 @@
         </is>
       </c>
       <c r="C562" t="n">
-        <v>46.63</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>2024-01-08</t>
+          <t>2024-01-10</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -8872,13 +8870,13 @@
         </is>
       </c>
       <c r="C563" t="n">
-        <v>45.95</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -8887,13 +8885,13 @@
         </is>
       </c>
       <c r="C564" t="n">
-        <v>45.99</v>
+        <v>46.63</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>2024-01-04</t>
+          <t>2024-01-08</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -8902,13 +8900,13 @@
         </is>
       </c>
       <c r="C565" t="n">
-        <v>46.36</v>
+        <v>45.95</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>2024-01-03</t>
+          <t>2024-01-05</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -8917,13 +8915,13 @@
         </is>
       </c>
       <c r="C566" t="n">
-        <v>46.7</v>
+        <v>45.99</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-01-04</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -8932,13 +8930,13 @@
         </is>
       </c>
       <c r="C567" t="n">
-        <v>46.66</v>
+        <v>46.36</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>2023-12-29</t>
+          <t>2024-01-03</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -8947,13 +8945,13 @@
         </is>
       </c>
       <c r="C568" t="n">
-        <v>46.4</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>2023-12-28</t>
+          <t>2024-01-02</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -8962,13 +8960,13 @@
         </is>
       </c>
       <c r="C569" t="n">
-        <v>46.26</v>
+        <v>46.66</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>2023-12-27</t>
+          <t>2023-12-29</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -8977,13 +8975,13 @@
         </is>
       </c>
       <c r="C570" t="n">
-        <v>46.98</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>2023-12-26</t>
+          <t>2023-12-28</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -8992,13 +8990,13 @@
         </is>
       </c>
       <c r="C571" t="n">
-        <v>47.03</v>
+        <v>46.26</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2023-12-27</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -9007,13 +9005,13 @@
         </is>
       </c>
       <c r="C572" t="n">
-        <v>47.28</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2023-12-26</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -9022,13 +9020,13 @@
         </is>
       </c>
       <c r="C573" t="n">
-        <v>47.36</v>
+        <v>47.03</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2023-12-22</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -9037,13 +9035,13 @@
         </is>
       </c>
       <c r="C574" t="n">
-        <v>48.24</v>
+        <v>47.28</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -9052,13 +9050,13 @@
         </is>
       </c>
       <c r="C575" t="n">
-        <v>48.29</v>
+        <v>47.36</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -9067,13 +9065,13 @@
         </is>
       </c>
       <c r="C576" t="n">
-        <v>48.22</v>
+        <v>48.24</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -9082,21 +9080,51 @@
         </is>
       </c>
       <c r="C577" t="n">
-        <v>47.59</v>
+        <v>48.29</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C578" t="n">
+        <v>48.22</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2023-12-15</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C579" t="n">
+        <v>47.59</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
           <t>2023-12-14</t>
         </is>
       </c>
-      <c r="B578" t="inlineStr">
-        <is>
-          <t>BOK26</t>
-        </is>
-      </c>
-      <c r="C578" t="n">
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C580" t="n">
         <v>47.31</v>
       </c>
     </row>

--- a/data/lseg_excel/BOK26.xlsx
+++ b/data/lseg_excel/BOK26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C580"/>
+  <dimension ref="A1:C581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>69.02</v>
+        <v>70.37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -471,12 +471,14 @@
           <t>BOK26</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>69.95</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -484,14 +486,12 @@
           <t>BOK26</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>68.94</v>
-      </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>67.11</v>
+        <v>68.94</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>68.88</v>
+        <v>67.11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>68.47</v>
+        <v>68.88</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -545,13 +545,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>67.41</v>
+        <v>68.47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>68.02</v>
+        <v>67.41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -575,13 +575,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>67.09999999999999</v>
+        <v>68.02</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>65.73</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -605,13 +605,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>65.58</v>
+        <v>65.73</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -620,13 +620,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>65.51000000000001</v>
+        <v>65.58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>65.41</v>
+        <v>65.51000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -650,13 +650,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>65.53</v>
+        <v>65.41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -665,13 +665,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>65.97</v>
+        <v>65.53</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -680,13 +680,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>63.94</v>
+        <v>65.97</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>67.44</v>
+        <v>63.94</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>67.42</v>
+        <v>67.44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>67.16</v>
+        <v>67.42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -740,13 +740,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>65.62</v>
+        <v>67.16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>66.09999999999999</v>
+        <v>65.62</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -770,13 +770,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>66.58</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -785,13 +785,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>65.7</v>
+        <v>66.58</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -800,13 +800,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>63.59</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>62.82</v>
+        <v>63.59</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>62.74</v>
+        <v>62.82</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>61.85</v>
+        <v>62.74</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -860,13 +860,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>61.76</v>
+        <v>61.85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -875,13 +875,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>60.67</v>
+        <v>61.76</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -890,13 +890,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>60.5</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -905,13 +905,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>59.88</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -920,13 +920,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>59.3</v>
+        <v>59.88</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>60.09</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -950,13 +950,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>59.08</v>
+        <v>60.09</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -965,13 +965,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>57.76</v>
+        <v>59.08</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>57.47</v>
+        <v>57.76</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -995,13 +995,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>57.91</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>57.5</v>
+        <v>57.91</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1025,13 +1025,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>57.74</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1040,13 +1040,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>57.17</v>
+        <v>57.74</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1055,13 +1055,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>55.84</v>
+        <v>57.17</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>56.17</v>
+        <v>55.84</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1085,13 +1085,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>56.18</v>
+        <v>56.17</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1100,13 +1100,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>55.03</v>
+        <v>56.18</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>53.74</v>
+        <v>55.03</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1130,13 +1130,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>54.06</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>54.58</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1160,13 +1160,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>54.85</v>
+        <v>54.58</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1175,13 +1175,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>54.95</v>
+        <v>54.85</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>54.42</v>
+        <v>54.95</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>54.52</v>
+        <v>54.42</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1220,13 +1220,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>54.33</v>
+        <v>54.52</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1235,13 +1235,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>54.54</v>
+        <v>54.33</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>53.11</v>
+        <v>54.54</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1265,13 +1265,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>53.15</v>
+        <v>53.11</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1280,13 +1280,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>53.47</v>
+        <v>53.15</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>51.5</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1310,13 +1310,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>51.69</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1325,13 +1325,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>50.77</v>
+        <v>51.69</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1340,13 +1340,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>50.2</v>
+        <v>50.77</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1355,13 +1355,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>49.97</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1370,13 +1370,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>49.84</v>
+        <v>49.97</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>49.95</v>
+        <v>49.84</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>50.41</v>
+        <v>49.95</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1415,13 +1415,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>49.83</v>
+        <v>50.41</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1430,13 +1430,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>49.09</v>
+        <v>49.83</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1445,13 +1445,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>49.94</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1460,13 +1460,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>49.8</v>
+        <v>49.94</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>49.73</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1490,13 +1490,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>50</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>49.28</v>
+        <v>50</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>49.58</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1535,13 +1535,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>48.92</v>
+        <v>49.58</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1550,13 +1550,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>49.1</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1565,13 +1565,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>49.53</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1580,13 +1580,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>49.4</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1595,13 +1595,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>50.45</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>51.03</v>
+        <v>50.45</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1625,13 +1625,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>51.68</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1640,13 +1640,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>51.96</v>
+        <v>51.68</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1655,13 +1655,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>51.88</v>
+        <v>51.96</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1670,13 +1670,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>52.04</v>
+        <v>51.88</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>52.54</v>
+        <v>52.04</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1700,13 +1700,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>52.63</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>52.54</v>
+        <v>52.63</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>53.51</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1745,13 +1745,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>53.16</v>
+        <v>53.51</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1760,13 +1760,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>52.84</v>
+        <v>53.16</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>51.89</v>
+        <v>52.84</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1790,13 +1790,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>51.51</v>
+        <v>51.89</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1805,13 +1805,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>51.41</v>
+        <v>51.51</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>51.47</v>
+        <v>51.41</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>51.83</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>52.3</v>
+        <v>51.83</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1865,13 +1865,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>53.35</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -1880,13 +1880,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>52.36</v>
+        <v>53.35</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1895,13 +1895,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>51.46</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1910,13 +1910,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>51.56</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>51.9</v>
+        <v>51.56</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -1940,13 +1940,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>52.33</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -1955,13 +1955,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>51.8</v>
+        <v>52.33</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -1970,13 +1970,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>50.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -1985,13 +1985,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>50.56</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2000,13 +2000,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>50.88</v>
+        <v>50.56</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2015,13 +2015,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>50.76</v>
+        <v>50.88</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>51.08</v>
+        <v>50.76</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2045,13 +2045,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>50</v>
+        <v>51.08</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2060,13 +2060,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>50.88</v>
+        <v>50</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2075,13 +2075,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>51.34</v>
+        <v>50.88</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>51.46</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2105,13 +2105,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>51.93</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2120,13 +2120,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>51.4</v>
+        <v>51.93</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>51.93</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2150,13 +2150,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>51.21</v>
+        <v>51.93</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>51.72</v>
+        <v>51.21</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>52.32</v>
+        <v>51.72</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2195,13 +2195,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>52.09</v>
+        <v>52.32</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2210,13 +2210,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>51.84</v>
+        <v>52.09</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2225,13 +2225,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>51.73</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>51.47</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2270,13 +2270,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>50.86</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2285,13 +2285,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>51.84</v>
+        <v>50.86</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>52.41</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>51.89</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2330,13 +2330,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>51.33</v>
+        <v>51.89</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>51.02</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2360,13 +2360,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>51.38</v>
+        <v>51.02</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>51.34</v>
+        <v>51.38</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>50.46</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>50.74</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -2420,13 +2420,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>51.27</v>
+        <v>50.74</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -2435,13 +2435,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>51.34</v>
+        <v>51.27</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>50.92</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -2465,13 +2465,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>50.93</v>
+        <v>50.92</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -2480,13 +2480,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>50.7</v>
+        <v>50.93</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -2495,13 +2495,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>51.5</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>52.03</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>52.59</v>
+        <v>52.03</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -2540,13 +2540,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>53.81</v>
+        <v>52.59</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -2555,13 +2555,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>52.98</v>
+        <v>53.81</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -2576,7 +2576,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -2585,13 +2585,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>52.41</v>
+        <v>52.98</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -2600,13 +2600,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>51.85</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -2615,13 +2615,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>51.41</v>
+        <v>51.85</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -2630,13 +2630,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>52.36</v>
+        <v>51.41</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -2645,13 +2645,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>52.02</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -2660,13 +2660,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>52.63</v>
+        <v>52.02</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -2675,13 +2675,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>52.54</v>
+        <v>52.63</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -2690,13 +2690,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>53.3</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -2705,13 +2705,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>52.79</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -2720,13 +2720,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>53.07</v>
+        <v>52.79</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -2735,13 +2735,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>53.82</v>
+        <v>53.07</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>53.93</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>55.12</v>
+        <v>53.93</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -2780,13 +2780,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>55.41</v>
+        <v>55.12</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -2795,13 +2795,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>54.01</v>
+        <v>55.41</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -2810,13 +2810,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>51.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -2825,13 +2825,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>52.23</v>
+        <v>51.87</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -2840,13 +2840,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>53.59</v>
+        <v>52.23</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -2855,13 +2855,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>53.31</v>
+        <v>53.59</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -2870,13 +2870,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>52.27</v>
+        <v>53.31</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -2885,13 +2885,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>53.3</v>
+        <v>52.27</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -2900,13 +2900,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>53</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -2915,13 +2915,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>52.87</v>
+        <v>53</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -2930,13 +2930,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>52.46</v>
+        <v>52.87</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>53.33</v>
+        <v>52.46</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -2960,13 +2960,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>53.53</v>
+        <v>53.33</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -2975,13 +2975,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>53.25</v>
+        <v>53.53</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -2990,13 +2990,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>53.87</v>
+        <v>53.25</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3005,13 +3005,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>53.61</v>
+        <v>53.87</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3020,13 +3020,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>54.32</v>
+        <v>53.61</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -3035,13 +3035,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>55.55</v>
+        <v>54.32</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>56.24</v>
+        <v>55.55</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3065,13 +3065,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>55.61</v>
+        <v>56.24</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>55.47</v>
+        <v>55.61</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3095,13 +3095,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>55.8</v>
+        <v>55.47</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>55.34</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -3125,13 +3125,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>54.93</v>
+        <v>55.34</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -3140,13 +3140,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>55.29</v>
+        <v>54.93</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -3155,13 +3155,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>55.02</v>
+        <v>55.29</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -3170,13 +3170,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>55.59</v>
+        <v>55.02</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -3185,13 +3185,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>54.31</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>54.1</v>
+        <v>54.31</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -3215,13 +3215,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>53.8</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -3230,13 +3230,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>53.47</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -3245,13 +3245,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>53.38</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -3260,13 +3260,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>53.17</v>
+        <v>53.38</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>53.82</v>
+        <v>53.17</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -3290,13 +3290,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>53.64</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -3305,13 +3305,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>54.46</v>
+        <v>53.64</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -3320,13 +3320,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>54.77</v>
+        <v>54.46</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -3335,13 +3335,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>53.48</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -3350,13 +3350,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>52.62</v>
+        <v>53.48</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -3365,13 +3365,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>52.52</v>
+        <v>52.62</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -3380,13 +3380,13 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>52.86</v>
+        <v>52.52</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -3395,13 +3395,13 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>52.43</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -3410,13 +3410,13 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>52.69</v>
+        <v>52.43</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -3425,13 +3425,13 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>53.79</v>
+        <v>52.69</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>55.04</v>
+        <v>53.79</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -3455,13 +3455,13 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>55.23</v>
+        <v>55.04</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -3470,13 +3470,13 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>55.16</v>
+        <v>55.23</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -3485,13 +3485,13 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>55.1</v>
+        <v>55.16</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -3500,13 +3500,13 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>51.65</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>48.65</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -3530,13 +3530,13 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>48.94</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -3545,13 +3545,13 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>48.82</v>
+        <v>48.94</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -3560,13 +3560,13 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>48.46</v>
+        <v>48.82</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -3575,13 +3575,13 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>48.62</v>
+        <v>48.46</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -3590,13 +3590,13 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>47.95</v>
+        <v>48.62</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -3605,13 +3605,13 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>47.8</v>
+        <v>47.95</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -3620,13 +3620,13 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>47.85</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -3635,13 +3635,13 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>47.49</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>47.78</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -3665,13 +3665,13 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>49.05</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>49.41</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -3695,13 +3695,13 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>50.03</v>
+        <v>49.41</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>49.88</v>
+        <v>50.03</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -3725,13 +3725,13 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>49.73</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -3740,13 +3740,13 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>50.23</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -3755,13 +3755,13 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>49.88</v>
+        <v>50.23</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -3770,13 +3770,13 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>49.78</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -3785,13 +3785,13 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>49.2</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -3800,13 +3800,13 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>48.9</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -3815,13 +3815,13 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>51.9</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -3830,13 +3830,13 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>51.46</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -3845,13 +3845,13 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>50.03</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -3860,13 +3860,13 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>48.66</v>
+        <v>50.03</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -3875,13 +3875,13 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>48.38</v>
+        <v>48.66</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -3890,13 +3890,13 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>47.52</v>
+        <v>48.38</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>48.22</v>
+        <v>47.52</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -3920,13 +3920,13 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>48.33</v>
+        <v>48.22</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -3935,13 +3935,13 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>48.82</v>
+        <v>48.33</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -3950,13 +3950,13 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>48.95</v>
+        <v>48.82</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -3965,13 +3965,13 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>48.22</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -3980,13 +3980,13 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>48.75</v>
+        <v>48.22</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -3995,13 +3995,13 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>49.78</v>
+        <v>48.75</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -4010,13 +4010,13 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>49.23</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -4025,13 +4025,13 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>49.17</v>
+        <v>49.23</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -4040,13 +4040,13 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>47.85</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -4055,13 +4055,13 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>47.78</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -4070,13 +4070,13 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>47.83</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -4085,13 +4085,13 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>47.91</v>
+        <v>47.83</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -4100,13 +4100,13 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>47.73</v>
+        <v>47.91</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -4115,13 +4115,13 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>47.54</v>
+        <v>47.73</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -4130,13 +4130,13 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>46.72</v>
+        <v>47.54</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -4145,13 +4145,13 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>47.16</v>
+        <v>46.72</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -4160,13 +4160,13 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>46.15</v>
+        <v>47.16</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -4175,13 +4175,13 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>46.11</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -4190,13 +4190,13 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>44.82</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -4205,13 +4205,13 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>45.02</v>
+        <v>44.82</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -4220,13 +4220,13 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>45.96</v>
+        <v>45.02</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -4235,13 +4235,13 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>47.35</v>
+        <v>45.96</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -4250,13 +4250,13 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>48.65</v>
+        <v>47.35</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -4265,13 +4265,13 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>47.87</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -4280,13 +4280,13 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>46</v>
+        <v>47.87</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -4295,13 +4295,13 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>46.11</v>
+        <v>46</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -4310,13 +4310,13 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>45.42</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -4325,13 +4325,13 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>44.2</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -4340,13 +4340,13 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>43.82</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>43.48</v>
+        <v>43.82</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>43.28</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -4385,13 +4385,13 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>43.7</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -4400,13 +4400,13 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>43.32</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -4415,13 +4415,13 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>43.28</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -4430,13 +4430,13 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>42.9</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -4445,13 +4445,13 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>42.51</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -4460,13 +4460,13 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>42.36</v>
+        <v>42.51</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -4475,13 +4475,13 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>42.65</v>
+        <v>42.36</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -4490,13 +4490,13 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>42.85</v>
+        <v>42.65</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>43.04</v>
+        <v>42.85</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -4520,13 +4520,13 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>43.92</v>
+        <v>43.04</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -4535,13 +4535,13 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>43.52</v>
+        <v>43.92</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -4550,13 +4550,13 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>43.37</v>
+        <v>43.52</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -4565,13 +4565,13 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>43.24</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -4580,13 +4580,13 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>43.99</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>44.52</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -4610,13 +4610,13 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>45.66</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -4625,13 +4625,13 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>45.78</v>
+        <v>45.66</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -4640,13 +4640,13 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>46.1</v>
+        <v>45.78</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -4655,13 +4655,13 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>46.42</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -4670,13 +4670,13 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>47.21</v>
+        <v>46.42</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -4685,13 +4685,13 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>47.44</v>
+        <v>47.21</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>46.5</v>
+        <v>47.44</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -4715,13 +4715,13 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>47.21</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>46.08</v>
+        <v>47.21</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -4745,13 +4745,13 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>46.21</v>
+        <v>46.08</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -4760,13 +4760,13 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>45.72</v>
+        <v>46.21</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -4775,13 +4775,13 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>46.29</v>
+        <v>45.72</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -4790,13 +4790,13 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>45.9</v>
+        <v>46.29</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -4805,13 +4805,13 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>46.05</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -4820,13 +4820,13 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>45.73</v>
+        <v>46.05</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -4835,13 +4835,13 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>45.31</v>
+        <v>45.73</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -4850,13 +4850,13 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>45.75</v>
+        <v>45.31</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -4865,13 +4865,13 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>46.37</v>
+        <v>45.75</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -4880,13 +4880,13 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>45.77</v>
+        <v>46.37</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -4895,13 +4895,13 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>45.1</v>
+        <v>45.77</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -4910,13 +4910,13 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>44.97</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -4925,13 +4925,13 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>45.11</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -4940,13 +4940,13 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>44.88</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -4955,13 +4955,13 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>45.06</v>
+        <v>44.88</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -4970,13 +4970,13 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>44.73</v>
+        <v>45.06</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -4985,13 +4985,13 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>44.3</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -5000,13 +5000,13 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>45.15</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -5015,13 +5015,13 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>45.27</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>45.03</v>
+        <v>45.27</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -5045,13 +5045,13 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>45.99</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>46.22</v>
+        <v>45.99</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -5075,13 +5075,13 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>46.06</v>
+        <v>46.22</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -5090,13 +5090,13 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>45.62</v>
+        <v>46.06</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -5105,13 +5105,13 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>43.48</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -5120,13 +5120,13 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>42.45</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>42.17</v>
+        <v>42.45</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -5150,13 +5150,13 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>41.34</v>
+        <v>42.17</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -5165,13 +5165,13 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>40.87</v>
+        <v>41.34</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -5180,13 +5180,13 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>41.09</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -5195,13 +5195,13 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>41.32</v>
+        <v>41.09</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -5210,13 +5210,13 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>41.19</v>
+        <v>41.32</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -5225,13 +5225,13 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>40.94</v>
+        <v>41.19</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -5246,7 +5246,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2024-12-24</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -5255,13 +5255,13 @@
         </is>
       </c>
       <c r="C322" t="n">
-        <v>41.38</v>
+        <v>40.94</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -5270,13 +5270,13 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>41.62</v>
+        <v>41.38</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -5285,13 +5285,13 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>40.87</v>
+        <v>41.62</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>41.15</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -5315,13 +5315,13 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>40.92</v>
+        <v>41.15</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -5330,13 +5330,13 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>41.73</v>
+        <v>40.92</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -5345,13 +5345,13 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>42.72</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -5360,13 +5360,13 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>43.49</v>
+        <v>42.72</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -5375,13 +5375,13 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>43.53</v>
+        <v>43.49</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -5390,13 +5390,13 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>43.26</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -5405,13 +5405,13 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>43.46</v>
+        <v>43.26</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -5420,13 +5420,13 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>43.52</v>
+        <v>43.46</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -5435,13 +5435,13 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>43.58</v>
+        <v>43.52</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -5450,13 +5450,13 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>42.89</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -5465,13 +5465,13 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>42.12</v>
+        <v>42.89</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -5480,13 +5480,13 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>42.67</v>
+        <v>42.12</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>42.3</v>
+        <v>42.67</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="C339" t="n">
-        <v>42.39</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>41.84</v>
+        <v>42.39</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -5540,13 +5540,13 @@
         </is>
       </c>
       <c r="C341" t="n">
-        <v>43.17</v>
+        <v>41.84</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -5555,13 +5555,13 @@
         </is>
       </c>
       <c r="C342" t="n">
-        <v>42.27</v>
+        <v>43.17</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -5570,13 +5570,13 @@
         </is>
       </c>
       <c r="C343" t="n">
-        <v>42.78</v>
+        <v>42.27</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -5585,13 +5585,13 @@
         </is>
       </c>
       <c r="C344" t="n">
-        <v>43.09</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -5600,13 +5600,13 @@
         </is>
       </c>
       <c r="C345" t="n">
-        <v>43.95</v>
+        <v>43.09</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -5615,13 +5615,13 @@
         </is>
       </c>
       <c r="C346" t="n">
-        <v>44.91</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -5630,13 +5630,13 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>45.32</v>
+        <v>44.91</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -5645,13 +5645,13 @@
         </is>
       </c>
       <c r="C348" t="n">
-        <v>45.24</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -5660,13 +5660,13 @@
         </is>
       </c>
       <c r="C349" t="n">
-        <v>44.48</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -5675,13 +5675,13 @@
         </is>
       </c>
       <c r="C350" t="n">
-        <v>45.38</v>
+        <v>44.48</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="C351" t="n">
-        <v>46.24</v>
+        <v>45.38</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -5705,13 +5705,13 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>47.78</v>
+        <v>46.24</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -5720,13 +5720,13 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>48.04</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -5735,13 +5735,13 @@
         </is>
       </c>
       <c r="C354" t="n">
-        <v>47.49</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -5750,13 +5750,13 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>45.65</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>45.01</v>
+        <v>45.65</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -5780,13 +5780,13 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>45.36</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -5795,13 +5795,13 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>45.49</v>
+        <v>45.36</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -5810,13 +5810,13 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>44.54</v>
+        <v>45.49</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -5825,13 +5825,13 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>43.62</v>
+        <v>44.54</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -5840,13 +5840,13 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>42.78</v>
+        <v>43.62</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -5855,13 +5855,13 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>42.73</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -5870,13 +5870,13 @@
         </is>
       </c>
       <c r="C363" t="n">
-        <v>43.65</v>
+        <v>42.73</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -5885,13 +5885,13 @@
         </is>
       </c>
       <c r="C364" t="n">
-        <v>43.48</v>
+        <v>43.65</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -5900,13 +5900,13 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>42.77</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -5915,13 +5915,13 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>42.86</v>
+        <v>42.77</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -5930,13 +5930,13 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>41.8</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -5945,13 +5945,13 @@
         </is>
       </c>
       <c r="C368" t="n">
-        <v>41.24</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -5960,13 +5960,13 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>41.92</v>
+        <v>41.24</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -5975,13 +5975,13 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>41.59</v>
+        <v>41.92</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -5990,13 +5990,13 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>42.03</v>
+        <v>41.59</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -6011,7 +6011,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -6020,13 +6020,13 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>43.28</v>
+        <v>42.03</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -6035,13 +6035,13 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>43.74</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -6050,13 +6050,13 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>43.16</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -6065,13 +6065,13 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>43.22</v>
+        <v>43.16</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -6080,13 +6080,13 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>44.73</v>
+        <v>43.22</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -6095,13 +6095,13 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>44.08</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -6110,13 +6110,13 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>44.43</v>
+        <v>44.08</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -6125,13 +6125,13 @@
         </is>
       </c>
       <c r="C380" t="n">
-        <v>43.57</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -6140,13 +6140,13 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>43.08</v>
+        <v>43.57</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -6155,13 +6155,13 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>43.05</v>
+        <v>43.08</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -6170,13 +6170,13 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>42.78</v>
+        <v>43.05</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="C384" t="n">
-        <v>43.53</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -6200,13 +6200,13 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>43.71</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>43.14</v>
+        <v>43.71</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -6230,13 +6230,13 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>42.09</v>
+        <v>43.14</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -6245,13 +6245,13 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>41.73</v>
+        <v>42.09</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -6260,13 +6260,13 @@
         </is>
       </c>
       <c r="C389" t="n">
-        <v>41.43</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -6275,13 +6275,13 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>41.17</v>
+        <v>41.43</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>40.69</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -6305,13 +6305,13 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>40.11</v>
+        <v>40.69</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -6320,13 +6320,13 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>40.12</v>
+        <v>40.11</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -6335,13 +6335,13 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>40.75</v>
+        <v>40.12</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="C395" t="n">
-        <v>40.39</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -6365,13 +6365,13 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>40.6</v>
+        <v>40.39</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -6380,13 +6380,13 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>41.29</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -6395,13 +6395,13 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>40.49</v>
+        <v>41.29</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -6410,13 +6410,13 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>41.62</v>
+        <v>40.49</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>40.98</v>
+        <v>41.62</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -6440,13 +6440,13 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>41.5</v>
+        <v>40.98</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -6455,13 +6455,13 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>42.26</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="C403" t="n">
-        <v>42.24</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -6485,13 +6485,13 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>41.21</v>
+        <v>42.24</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -6500,13 +6500,13 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>40.93</v>
+        <v>41.21</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -6515,13 +6515,13 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>40.83</v>
+        <v>40.93</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -6530,13 +6530,13 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>40.51</v>
+        <v>40.83</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -6545,13 +6545,13 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>39.52</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -6560,13 +6560,13 @@
         </is>
       </c>
       <c r="C409" t="n">
-        <v>40.05</v>
+        <v>39.52</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -6575,13 +6575,13 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>39.68</v>
+        <v>40.05</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -6590,13 +6590,13 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>39.76</v>
+        <v>39.68</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -6605,13 +6605,13 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>39.55</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -6620,13 +6620,13 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>39.29</v>
+        <v>39.55</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -6635,13 +6635,13 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>39.58</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -6650,13 +6650,13 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>39.89</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -6665,13 +6665,13 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>40.84</v>
+        <v>39.89</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -6680,13 +6680,13 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>40.75</v>
+        <v>40.84</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -6695,13 +6695,13 @@
         </is>
       </c>
       <c r="C418" t="n">
-        <v>40.68</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -6710,13 +6710,13 @@
         </is>
       </c>
       <c r="C419" t="n">
-        <v>40.51</v>
+        <v>40.68</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -6725,13 +6725,13 @@
         </is>
       </c>
       <c r="C420" t="n">
-        <v>40.16</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -6740,13 +6740,13 @@
         </is>
       </c>
       <c r="C421" t="n">
-        <v>40.25</v>
+        <v>40.16</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -6755,13 +6755,13 @@
         </is>
       </c>
       <c r="C422" t="n">
-        <v>40.91</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -6770,13 +6770,13 @@
         </is>
       </c>
       <c r="C423" t="n">
-        <v>41.18</v>
+        <v>40.91</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -6785,13 +6785,13 @@
         </is>
       </c>
       <c r="C424" t="n">
-        <v>41.72</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -6800,13 +6800,13 @@
         </is>
       </c>
       <c r="C425" t="n">
-        <v>41.2</v>
+        <v>41.72</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -6815,13 +6815,13 @@
         </is>
       </c>
       <c r="C426" t="n">
-        <v>41.67</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -6830,13 +6830,13 @@
         </is>
       </c>
       <c r="C427" t="n">
-        <v>41.34</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -6845,13 +6845,13 @@
         </is>
       </c>
       <c r="C428" t="n">
-        <v>42.82</v>
+        <v>41.34</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -6860,13 +6860,13 @@
         </is>
       </c>
       <c r="C429" t="n">
-        <v>42.57</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -6875,13 +6875,13 @@
         </is>
       </c>
       <c r="C430" t="n">
-        <v>43.28</v>
+        <v>42.57</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -6890,13 +6890,13 @@
         </is>
       </c>
       <c r="C431" t="n">
-        <v>42.86</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -6905,13 +6905,13 @@
         </is>
       </c>
       <c r="C432" t="n">
-        <v>41.96</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -6920,13 +6920,13 @@
         </is>
       </c>
       <c r="C433" t="n">
-        <v>42.63</v>
+        <v>41.96</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -6935,13 +6935,13 @@
         </is>
       </c>
       <c r="C434" t="n">
-        <v>42.6</v>
+        <v>42.63</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -6950,13 +6950,13 @@
         </is>
       </c>
       <c r="C435" t="n">
-        <v>43.39</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -6965,13 +6965,13 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>43.49</v>
+        <v>43.39</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -6980,13 +6980,13 @@
         </is>
       </c>
       <c r="C437" t="n">
-        <v>44.6</v>
+        <v>43.49</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -6995,13 +6995,13 @@
         </is>
       </c>
       <c r="C438" t="n">
-        <v>45.01</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="C439" t="n">
-        <v>44.73</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -7025,13 +7025,13 @@
         </is>
       </c>
       <c r="C440" t="n">
-        <v>45.87</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -7040,13 +7040,13 @@
         </is>
       </c>
       <c r="C441" t="n">
-        <v>46.97</v>
+        <v>45.87</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -7055,13 +7055,13 @@
         </is>
       </c>
       <c r="C442" t="n">
-        <v>47.02</v>
+        <v>46.97</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -7070,13 +7070,13 @@
         </is>
       </c>
       <c r="C443" t="n">
-        <v>46.75</v>
+        <v>47.02</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="C444" t="n">
-        <v>45.79</v>
+        <v>46.75</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -7100,13 +7100,13 @@
         </is>
       </c>
       <c r="C445" t="n">
-        <v>44.84</v>
+        <v>45.79</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -7115,13 +7115,13 @@
         </is>
       </c>
       <c r="C446" t="n">
-        <v>43.13</v>
+        <v>44.84</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -7130,13 +7130,13 @@
         </is>
       </c>
       <c r="C447" t="n">
-        <v>42.97</v>
+        <v>43.13</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -7145,13 +7145,13 @@
         </is>
       </c>
       <c r="C448" t="n">
-        <v>43.37</v>
+        <v>42.97</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -7160,13 +7160,13 @@
         </is>
       </c>
       <c r="C449" t="n">
-        <v>42.71</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="C450" t="n">
-        <v>43.35</v>
+        <v>42.71</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -7190,13 +7190,13 @@
         </is>
       </c>
       <c r="C451" t="n">
-        <v>43.58</v>
+        <v>43.35</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -7205,13 +7205,13 @@
         </is>
       </c>
       <c r="C452" t="n">
-        <v>43.59</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -7220,13 +7220,13 @@
         </is>
       </c>
       <c r="C453" t="n">
-        <v>44.01</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -7235,13 +7235,13 @@
         </is>
       </c>
       <c r="C454" t="n">
-        <v>43.56</v>
+        <v>44.01</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -7250,13 +7250,13 @@
         </is>
       </c>
       <c r="C455" t="n">
-        <v>43.53</v>
+        <v>43.56</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -7265,13 +7265,13 @@
         </is>
       </c>
       <c r="C456" t="n">
-        <v>43.76</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -7280,13 +7280,13 @@
         </is>
       </c>
       <c r="C457" t="n">
-        <v>43.87</v>
+        <v>43.76</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -7295,13 +7295,13 @@
         </is>
       </c>
       <c r="C458" t="n">
-        <v>43.76</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -7310,13 +7310,13 @@
         </is>
       </c>
       <c r="C459" t="n">
-        <v>43.98</v>
+        <v>43.76</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -7325,13 +7325,13 @@
         </is>
       </c>
       <c r="C460" t="n">
-        <v>44.29</v>
+        <v>43.98</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="C461" t="n">
-        <v>44.83</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -7355,13 +7355,13 @@
         </is>
       </c>
       <c r="C462" t="n">
-        <v>43.88</v>
+        <v>44.83</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -7370,13 +7370,13 @@
         </is>
       </c>
       <c r="C463" t="n">
-        <v>44.2</v>
+        <v>43.88</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -7385,13 +7385,13 @@
         </is>
       </c>
       <c r="C464" t="n">
-        <v>44.63</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -7400,13 +7400,13 @@
         </is>
       </c>
       <c r="C465" t="n">
-        <v>45.81</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -7415,13 +7415,13 @@
         </is>
       </c>
       <c r="C466" t="n">
-        <v>45.93</v>
+        <v>45.81</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -7430,13 +7430,13 @@
         </is>
       </c>
       <c r="C467" t="n">
-        <v>46.11</v>
+        <v>45.93</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -7445,13 +7445,13 @@
         </is>
       </c>
       <c r="C468" t="n">
-        <v>45.74</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -7460,13 +7460,13 @@
         </is>
       </c>
       <c r="C469" t="n">
-        <v>45.32</v>
+        <v>45.74</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -7475,13 +7475,13 @@
         </is>
       </c>
       <c r="C470" t="n">
-        <v>45.96</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -7490,13 +7490,13 @@
         </is>
       </c>
       <c r="C471" t="n">
-        <v>46.2</v>
+        <v>45.96</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -7505,13 +7505,13 @@
         </is>
       </c>
       <c r="C472" t="n">
-        <v>46.37</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -7520,13 +7520,13 @@
         </is>
       </c>
       <c r="C473" t="n">
-        <v>46.6</v>
+        <v>46.37</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -7535,13 +7535,13 @@
         </is>
       </c>
       <c r="C474" t="n">
-        <v>45.89</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -7550,13 +7550,13 @@
         </is>
       </c>
       <c r="C475" t="n">
-        <v>45.45</v>
+        <v>45.89</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -7565,13 +7565,13 @@
         </is>
       </c>
       <c r="C476" t="n">
-        <v>44.82</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -7580,13 +7580,13 @@
         </is>
       </c>
       <c r="C477" t="n">
-        <v>44.7</v>
+        <v>44.82</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -7595,13 +7595,13 @@
         </is>
       </c>
       <c r="C478" t="n">
-        <v>46.01</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -7610,13 +7610,13 @@
         </is>
       </c>
       <c r="C479" t="n">
-        <v>45.24</v>
+        <v>46.01</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -7625,13 +7625,13 @@
         </is>
       </c>
       <c r="C480" t="n">
-        <v>44.2</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="C481" t="n">
-        <v>44.8</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -7655,13 +7655,13 @@
         </is>
       </c>
       <c r="C482" t="n">
-        <v>45.29</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="C483" t="n">
-        <v>44.66</v>
+        <v>45.29</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -7685,13 +7685,13 @@
         </is>
       </c>
       <c r="C484" t="n">
-        <v>44.34</v>
+        <v>44.66</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -7700,13 +7700,13 @@
         </is>
       </c>
       <c r="C485" t="n">
-        <v>44.43</v>
+        <v>44.34</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -7715,13 +7715,13 @@
         </is>
       </c>
       <c r="C486" t="n">
-        <v>44.49</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -7730,13 +7730,13 @@
         </is>
       </c>
       <c r="C487" t="n">
-        <v>44.32</v>
+        <v>44.49</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -7745,13 +7745,13 @@
         </is>
       </c>
       <c r="C488" t="n">
-        <v>45.01</v>
+        <v>44.32</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -7760,13 +7760,13 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>45.94</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -7775,13 +7775,13 @@
         </is>
       </c>
       <c r="C490" t="n">
-        <v>45.67</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -7790,13 +7790,13 @@
         </is>
       </c>
       <c r="C491" t="n">
-        <v>45.58</v>
+        <v>45.67</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -7805,13 +7805,13 @@
         </is>
       </c>
       <c r="C492" t="n">
-        <v>45.95</v>
+        <v>45.58</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -7820,13 +7820,13 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>45.8</v>
+        <v>45.95</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -7835,13 +7835,13 @@
         </is>
       </c>
       <c r="C494" t="n">
-        <v>45.14</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -7850,13 +7850,13 @@
         </is>
       </c>
       <c r="C495" t="n">
-        <v>44.97</v>
+        <v>45.14</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -7865,13 +7865,13 @@
         </is>
       </c>
       <c r="C496" t="n">
-        <v>45.19</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="C497" t="n">
-        <v>45.34</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -7895,13 +7895,13 @@
         </is>
       </c>
       <c r="C498" t="n">
-        <v>45.6</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -7910,13 +7910,13 @@
         </is>
       </c>
       <c r="C499" t="n">
-        <v>45.97</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -7925,13 +7925,13 @@
         </is>
       </c>
       <c r="C500" t="n">
-        <v>45.91</v>
+        <v>45.97</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -7940,13 +7940,13 @@
         </is>
       </c>
       <c r="C501" t="n">
-        <v>46.95</v>
+        <v>45.91</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -7955,13 +7955,13 @@
         </is>
       </c>
       <c r="C502" t="n">
-        <v>46.91</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="C503" t="n">
-        <v>47.23</v>
+        <v>46.91</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -7985,13 +7985,13 @@
         </is>
       </c>
       <c r="C504" t="n">
-        <v>47.84</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -8000,13 +8000,13 @@
         </is>
       </c>
       <c r="C505" t="n">
-        <v>47.38</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -8015,13 +8015,13 @@
         </is>
       </c>
       <c r="C506" t="n">
-        <v>48</v>
+        <v>47.38</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -8030,13 +8030,13 @@
         </is>
       </c>
       <c r="C507" t="n">
-        <v>47.67</v>
+        <v>48</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -8045,13 +8045,13 @@
         </is>
       </c>
       <c r="C508" t="n">
-        <v>47.12</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -8060,13 +8060,13 @@
         </is>
       </c>
       <c r="C509" t="n">
-        <v>47.14</v>
+        <v>47.12</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -8075,13 +8075,13 @@
         </is>
       </c>
       <c r="C510" t="n">
-        <v>46.67</v>
+        <v>47.14</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="C511" t="n">
-        <v>47.46</v>
+        <v>46.67</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -8105,13 +8105,13 @@
         </is>
       </c>
       <c r="C512" t="n">
-        <v>47.71</v>
+        <v>47.46</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -8120,13 +8120,13 @@
         </is>
       </c>
       <c r="C513" t="n">
-        <v>46.65</v>
+        <v>47.71</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -8135,13 +8135,13 @@
         </is>
       </c>
       <c r="C514" t="n">
-        <v>47.72</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -8150,13 +8150,13 @@
         </is>
       </c>
       <c r="C515" t="n">
-        <v>47.89</v>
+        <v>47.72</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -8165,13 +8165,13 @@
         </is>
       </c>
       <c r="C516" t="n">
-        <v>47.23</v>
+        <v>47.89</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -8180,13 +8180,13 @@
         </is>
       </c>
       <c r="C517" t="n">
-        <v>47.63</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -8195,13 +8195,13 @@
         </is>
       </c>
       <c r="C518" t="n">
-        <v>48.16</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -8210,13 +8210,13 @@
         </is>
       </c>
       <c r="C519" t="n">
-        <v>47.08</v>
+        <v>48.16</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -8225,13 +8225,13 @@
         </is>
       </c>
       <c r="C520" t="n">
-        <v>47.34</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -8240,13 +8240,13 @@
         </is>
       </c>
       <c r="C521" t="n">
-        <v>46.61</v>
+        <v>47.34</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="C522" t="n">
-        <v>45.84</v>
+        <v>46.61</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -8270,13 +8270,13 @@
         </is>
       </c>
       <c r="C523" t="n">
-        <v>45.28</v>
+        <v>45.84</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -8285,13 +8285,13 @@
         </is>
       </c>
       <c r="C524" t="n">
-        <v>45.23</v>
+        <v>45.28</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -8300,13 +8300,13 @@
         </is>
       </c>
       <c r="C525" t="n">
-        <v>44.51</v>
+        <v>45.23</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -8315,13 +8315,13 @@
         </is>
       </c>
       <c r="C526" t="n">
-        <v>44.37</v>
+        <v>44.51</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -8330,13 +8330,13 @@
         </is>
       </c>
       <c r="C527" t="n">
-        <v>44.55</v>
+        <v>44.37</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -8345,13 +8345,13 @@
         </is>
       </c>
       <c r="C528" t="n">
-        <v>44.45</v>
+        <v>44.55</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -8360,13 +8360,13 @@
         </is>
       </c>
       <c r="C529" t="n">
-        <v>44.56</v>
+        <v>44.45</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -8375,13 +8375,13 @@
         </is>
       </c>
       <c r="C530" t="n">
-        <v>44.63</v>
+        <v>44.56</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -8390,13 +8390,13 @@
         </is>
       </c>
       <c r="C531" t="n">
-        <v>44.69</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>2024-02-26</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -8405,13 +8405,13 @@
         </is>
       </c>
       <c r="C532" t="n">
-        <v>44.2</v>
+        <v>44.69</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -8420,13 +8420,13 @@
         </is>
       </c>
       <c r="C533" t="n">
-        <v>43.78</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -8435,13 +8435,13 @@
         </is>
       </c>
       <c r="C534" t="n">
-        <v>43.99</v>
+        <v>43.78</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-22</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -8450,13 +8450,13 @@
         </is>
       </c>
       <c r="C535" t="n">
-        <v>44</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -8465,13 +8465,13 @@
         </is>
       </c>
       <c r="C536" t="n">
-        <v>44.35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -8480,13 +8480,13 @@
         </is>
       </c>
       <c r="C537" t="n">
-        <v>44.52</v>
+        <v>44.35</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -8495,13 +8495,13 @@
         </is>
       </c>
       <c r="C538" t="n">
-        <v>44.68</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -8510,13 +8510,13 @@
         </is>
       </c>
       <c r="C539" t="n">
-        <v>45.07</v>
+        <v>44.68</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -8525,13 +8525,13 @@
         </is>
       </c>
       <c r="C540" t="n">
-        <v>45.62</v>
+        <v>45.07</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -8540,13 +8540,13 @@
         </is>
       </c>
       <c r="C541" t="n">
-        <v>45.33</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -8555,13 +8555,13 @@
         </is>
       </c>
       <c r="C542" t="n">
-        <v>45.64</v>
+        <v>45.33</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-09</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -8570,13 +8570,13 @@
         </is>
       </c>
       <c r="C543" t="n">
-        <v>45.59</v>
+        <v>45.64</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -8585,13 +8585,13 @@
         </is>
       </c>
       <c r="C544" t="n">
-        <v>44.61</v>
+        <v>45.59</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -8600,13 +8600,13 @@
         </is>
       </c>
       <c r="C545" t="n">
-        <v>44.2</v>
+        <v>44.61</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -8615,13 +8615,13 @@
         </is>
       </c>
       <c r="C546" t="n">
-        <v>43.73</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -8630,13 +8630,13 @@
         </is>
       </c>
       <c r="C547" t="n">
-        <v>43.66</v>
+        <v>43.73</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -8645,13 +8645,13 @@
         </is>
       </c>
       <c r="C548" t="n">
-        <v>44.07</v>
+        <v>43.66</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -8660,13 +8660,13 @@
         </is>
       </c>
       <c r="C549" t="n">
-        <v>44.66</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="C550" t="n">
-        <v>44.75</v>
+        <v>44.66</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-01-30</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -8690,13 +8690,13 @@
         </is>
       </c>
       <c r="C551" t="n">
-        <v>44.73</v>
+        <v>44.75</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -8705,13 +8705,13 @@
         </is>
       </c>
       <c r="C552" t="n">
-        <v>45.37</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -8720,13 +8720,13 @@
         </is>
       </c>
       <c r="C553" t="n">
-        <v>45.34</v>
+        <v>45.37</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -8735,13 +8735,13 @@
         </is>
       </c>
       <c r="C554" t="n">
-        <v>45.57</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>2024-01-23</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -8750,13 +8750,13 @@
         </is>
       </c>
       <c r="C555" t="n">
-        <v>45.97</v>
+        <v>45.57</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2024-01-23</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -8765,13 +8765,13 @@
         </is>
       </c>
       <c r="C556" t="n">
-        <v>45.94</v>
+        <v>45.97</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>2024-01-19</t>
+          <t>2024-01-22</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -8780,13 +8780,13 @@
         </is>
       </c>
       <c r="C557" t="n">
-        <v>45.19</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -8795,13 +8795,13 @@
         </is>
       </c>
       <c r="C558" t="n">
-        <v>45.44</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -8810,13 +8810,13 @@
         </is>
       </c>
       <c r="C559" t="n">
-        <v>45.42</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -8831,7 +8831,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -8840,13 +8840,13 @@
         </is>
       </c>
       <c r="C561" t="n">
-        <v>46.13</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>2024-01-11</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -8855,13 +8855,13 @@
         </is>
       </c>
       <c r="C562" t="n">
-        <v>46.6</v>
+        <v>46.13</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="C563" t="n">
-        <v>46.28</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-10</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -8885,13 +8885,13 @@
         </is>
       </c>
       <c r="C564" t="n">
-        <v>46.63</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>2024-01-08</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -8900,13 +8900,13 @@
         </is>
       </c>
       <c r="C565" t="n">
-        <v>45.95</v>
+        <v>46.63</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>2024-01-08</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -8915,13 +8915,13 @@
         </is>
       </c>
       <c r="C566" t="n">
-        <v>45.99</v>
+        <v>45.95</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>2024-01-04</t>
+          <t>2024-01-05</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -8930,13 +8930,13 @@
         </is>
       </c>
       <c r="C567" t="n">
-        <v>46.36</v>
+        <v>45.99</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>2024-01-03</t>
+          <t>2024-01-04</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -8945,13 +8945,13 @@
         </is>
       </c>
       <c r="C568" t="n">
-        <v>46.7</v>
+        <v>46.36</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-01-03</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -8960,13 +8960,13 @@
         </is>
       </c>
       <c r="C569" t="n">
-        <v>46.66</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>2023-12-29</t>
+          <t>2024-01-02</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -8975,13 +8975,13 @@
         </is>
       </c>
       <c r="C570" t="n">
-        <v>46.4</v>
+        <v>46.66</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>2023-12-28</t>
+          <t>2023-12-29</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="C571" t="n">
-        <v>46.26</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>2023-12-27</t>
+          <t>2023-12-28</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -9005,13 +9005,13 @@
         </is>
       </c>
       <c r="C572" t="n">
-        <v>46.98</v>
+        <v>46.26</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>2023-12-26</t>
+          <t>2023-12-27</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -9020,13 +9020,13 @@
         </is>
       </c>
       <c r="C573" t="n">
-        <v>47.03</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2023-12-26</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -9035,13 +9035,13 @@
         </is>
       </c>
       <c r="C574" t="n">
-        <v>47.28</v>
+        <v>47.03</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2023-12-22</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -9050,13 +9050,13 @@
         </is>
       </c>
       <c r="C575" t="n">
-        <v>47.36</v>
+        <v>47.28</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -9065,13 +9065,13 @@
         </is>
       </c>
       <c r="C576" t="n">
-        <v>48.24</v>
+        <v>47.36</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -9080,13 +9080,13 @@
         </is>
       </c>
       <c r="C577" t="n">
-        <v>48.29</v>
+        <v>48.24</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -9095,13 +9095,13 @@
         </is>
       </c>
       <c r="C578" t="n">
-        <v>48.22</v>
+        <v>48.29</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -9110,21 +9110,36 @@
         </is>
       </c>
       <c r="C579" t="n">
-        <v>47.59</v>
+        <v>48.22</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
+          <t>2023-12-15</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C580" t="n">
+        <v>47.59</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
           <t>2023-12-14</t>
         </is>
       </c>
-      <c r="B580" t="inlineStr">
-        <is>
-          <t>BOK26</t>
-        </is>
-      </c>
-      <c r="C580" t="n">
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C581" t="n">
         <v>47.31</v>
       </c>
     </row>

--- a/data/lseg_excel/BOK26.xlsx
+++ b/data/lseg_excel/BOK26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C581"/>
+  <dimension ref="A1:C582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>70.37</v>
+        <v>67.20999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>69.95</v>
+        <v>69.72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -486,12 +486,14 @@
           <t>BOK26</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>69.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -506,7 +508,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -515,13 +517,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>67.11</v>
+        <v>68.94</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -530,13 +532,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>68.88</v>
+        <v>67.11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -545,13 +547,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>68.47</v>
+        <v>68.88</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -560,13 +562,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>67.41</v>
+        <v>68.47</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -575,13 +577,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>68.02</v>
+        <v>67.41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -590,13 +592,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>67.09999999999999</v>
+        <v>68.02</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -605,13 +607,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>65.73</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -620,13 +622,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>65.58</v>
+        <v>65.73</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -635,13 +637,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>65.51000000000001</v>
+        <v>65.58</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -650,13 +652,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>65.41</v>
+        <v>65.51000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -665,13 +667,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>65.53</v>
+        <v>65.41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -680,13 +682,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>65.97</v>
+        <v>65.53</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -695,13 +697,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>63.94</v>
+        <v>65.97</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -710,13 +712,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>67.44</v>
+        <v>63.94</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -725,13 +727,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>67.42</v>
+        <v>67.44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -740,13 +742,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>67.16</v>
+        <v>67.42</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -755,13 +757,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>65.62</v>
+        <v>67.16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -770,13 +772,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>66.09999999999999</v>
+        <v>65.62</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -785,13 +787,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>66.58</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -800,13 +802,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>65.7</v>
+        <v>66.58</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -815,13 +817,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>63.59</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -830,13 +832,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>62.82</v>
+        <v>63.59</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -845,13 +847,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>62.74</v>
+        <v>62.82</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -860,13 +862,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>61.85</v>
+        <v>62.74</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -875,13 +877,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>61.76</v>
+        <v>61.85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -890,13 +892,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>60.67</v>
+        <v>61.76</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -905,13 +907,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>60.5</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -920,13 +922,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>59.88</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -935,13 +937,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>59.3</v>
+        <v>59.88</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -950,13 +952,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>60.09</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -965,13 +967,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>59.08</v>
+        <v>60.09</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -980,13 +982,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>57.76</v>
+        <v>59.08</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -995,13 +997,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>57.47</v>
+        <v>57.76</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1010,13 +1012,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>57.91</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1025,13 +1027,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>57.5</v>
+        <v>57.91</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1040,13 +1042,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>57.74</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1055,13 +1057,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>57.17</v>
+        <v>57.74</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1070,13 +1072,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>55.84</v>
+        <v>57.17</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1085,13 +1087,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>56.17</v>
+        <v>55.84</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1100,13 +1102,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>56.18</v>
+        <v>56.17</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1115,13 +1117,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>55.03</v>
+        <v>56.18</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1130,13 +1132,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>53.74</v>
+        <v>55.03</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1145,13 +1147,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>54.06</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1160,13 +1162,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>54.58</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1175,13 +1177,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>54.85</v>
+        <v>54.58</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1190,13 +1192,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>54.95</v>
+        <v>54.85</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1205,13 +1207,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>54.42</v>
+        <v>54.95</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1220,13 +1222,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>54.52</v>
+        <v>54.42</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1235,13 +1237,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>54.33</v>
+        <v>54.52</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1250,13 +1252,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>54.54</v>
+        <v>54.33</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1265,13 +1267,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>53.11</v>
+        <v>54.54</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1280,13 +1282,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>53.15</v>
+        <v>53.11</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1295,13 +1297,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>53.47</v>
+        <v>53.15</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1310,13 +1312,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>51.5</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1325,13 +1327,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>51.69</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1340,13 +1342,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>50.77</v>
+        <v>51.69</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1355,13 +1357,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>50.2</v>
+        <v>50.77</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1370,13 +1372,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>49.97</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1385,13 +1387,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>49.84</v>
+        <v>49.97</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1400,13 +1402,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>49.95</v>
+        <v>49.84</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1415,13 +1417,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>50.41</v>
+        <v>49.95</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1430,13 +1432,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>49.83</v>
+        <v>50.41</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1445,13 +1447,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>49.09</v>
+        <v>49.83</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1460,13 +1462,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>49.94</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1475,13 +1477,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>49.8</v>
+        <v>49.94</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1490,13 +1492,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>49.73</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1505,13 +1507,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>50</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1520,13 +1522,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>49.28</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1535,13 +1537,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>49.58</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1550,13 +1552,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>48.92</v>
+        <v>49.58</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1565,13 +1567,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>49.1</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1580,13 +1582,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>49.53</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1595,13 +1597,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>49.4</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1610,13 +1612,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>50.45</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1625,13 +1627,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>51.03</v>
+        <v>50.45</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1640,13 +1642,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>51.68</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1655,13 +1657,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>51.96</v>
+        <v>51.68</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1670,13 +1672,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>51.88</v>
+        <v>51.96</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1685,13 +1687,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>52.04</v>
+        <v>51.88</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1700,13 +1702,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>52.54</v>
+        <v>52.04</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1715,13 +1717,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>52.63</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1730,13 +1732,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>52.54</v>
+        <v>52.63</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1745,13 +1747,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>53.51</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1760,13 +1762,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>53.16</v>
+        <v>53.51</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1775,13 +1777,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>52.84</v>
+        <v>53.16</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1790,13 +1792,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>51.89</v>
+        <v>52.84</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1805,13 +1807,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>51.51</v>
+        <v>51.89</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -1820,13 +1822,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>51.41</v>
+        <v>51.51</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -1835,13 +1837,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>51.47</v>
+        <v>51.41</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1850,13 +1852,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>51.83</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1865,13 +1867,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>52.3</v>
+        <v>51.83</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -1880,13 +1882,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>53.35</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1895,13 +1897,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>52.36</v>
+        <v>53.35</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1910,13 +1912,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>51.46</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -1925,13 +1927,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>51.56</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -1940,13 +1942,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>51.9</v>
+        <v>51.56</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -1955,13 +1957,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>52.33</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -1970,13 +1972,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>51.8</v>
+        <v>52.33</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -1985,13 +1987,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>50.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2000,13 +2002,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>50.56</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2015,13 +2017,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>50.88</v>
+        <v>50.56</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2030,13 +2032,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>50.76</v>
+        <v>50.88</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2045,13 +2047,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>51.08</v>
+        <v>50.76</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2060,13 +2062,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>50</v>
+        <v>51.08</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2075,13 +2077,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>50.88</v>
+        <v>50</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2090,13 +2092,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>51.34</v>
+        <v>50.88</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2105,13 +2107,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>51.46</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2120,13 +2122,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>51.93</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2135,13 +2137,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>51.4</v>
+        <v>51.93</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2150,13 +2152,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>51.93</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2165,13 +2167,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>51.21</v>
+        <v>51.93</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2180,13 +2182,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>51.72</v>
+        <v>51.21</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2195,13 +2197,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>52.32</v>
+        <v>51.72</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2210,13 +2212,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>52.09</v>
+        <v>52.32</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2225,13 +2227,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>51.84</v>
+        <v>52.09</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2240,13 +2242,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>51.73</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2255,13 +2257,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>51.47</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2276,7 +2278,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2285,13 +2287,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>50.86</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2300,13 +2302,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>51.84</v>
+        <v>50.86</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2315,13 +2317,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>52.41</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2330,13 +2332,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>51.89</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2345,13 +2347,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>51.33</v>
+        <v>51.89</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2360,13 +2362,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>51.02</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2375,13 +2377,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>51.38</v>
+        <v>51.02</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -2390,13 +2392,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>51.34</v>
+        <v>51.38</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -2405,13 +2407,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>50.46</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -2420,13 +2422,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>50.74</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -2435,13 +2437,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>51.27</v>
+        <v>50.74</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -2450,13 +2452,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>51.34</v>
+        <v>51.27</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -2465,13 +2467,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>50.92</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -2480,13 +2482,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>50.93</v>
+        <v>50.92</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -2495,13 +2497,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>50.7</v>
+        <v>50.93</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -2510,13 +2512,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>51.5</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -2525,13 +2527,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>52.03</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -2540,13 +2542,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>52.59</v>
+        <v>52.03</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -2555,13 +2557,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>53.81</v>
+        <v>52.59</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -2570,13 +2572,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>52.98</v>
+        <v>53.81</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -2591,7 +2593,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -2600,13 +2602,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>52.41</v>
+        <v>52.98</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -2615,13 +2617,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>51.85</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -2630,13 +2632,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>51.41</v>
+        <v>51.85</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -2645,13 +2647,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>52.36</v>
+        <v>51.41</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -2660,13 +2662,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>52.02</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -2675,13 +2677,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>52.63</v>
+        <v>52.02</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -2690,13 +2692,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>52.54</v>
+        <v>52.63</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -2705,13 +2707,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>53.3</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -2720,13 +2722,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>52.79</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -2735,13 +2737,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>53.07</v>
+        <v>52.79</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -2750,13 +2752,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>53.82</v>
+        <v>53.07</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -2765,13 +2767,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>53.93</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -2780,13 +2782,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>55.12</v>
+        <v>53.93</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -2795,13 +2797,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>55.41</v>
+        <v>55.12</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -2810,13 +2812,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>54.01</v>
+        <v>55.41</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -2825,13 +2827,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>51.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -2840,13 +2842,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>52.23</v>
+        <v>51.87</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -2855,13 +2857,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>53.59</v>
+        <v>52.23</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -2870,13 +2872,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>53.31</v>
+        <v>53.59</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -2885,13 +2887,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>52.27</v>
+        <v>53.31</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -2900,13 +2902,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>53.3</v>
+        <v>52.27</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -2915,13 +2917,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>53</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -2930,13 +2932,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>52.87</v>
+        <v>53</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -2945,13 +2947,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>52.46</v>
+        <v>52.87</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -2960,13 +2962,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>53.33</v>
+        <v>52.46</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -2975,13 +2977,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>53.53</v>
+        <v>53.33</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -2990,13 +2992,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>53.25</v>
+        <v>53.53</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3005,13 +3007,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>53.87</v>
+        <v>53.25</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3020,13 +3022,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>53.61</v>
+        <v>53.87</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -3035,13 +3037,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>54.32</v>
+        <v>53.61</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -3050,13 +3052,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>55.55</v>
+        <v>54.32</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3065,13 +3067,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>56.24</v>
+        <v>55.55</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -3080,13 +3082,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>55.61</v>
+        <v>56.24</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3095,13 +3097,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>55.47</v>
+        <v>55.61</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -3110,13 +3112,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>55.8</v>
+        <v>55.47</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -3125,13 +3127,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>55.34</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -3140,13 +3142,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>54.93</v>
+        <v>55.34</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -3155,13 +3157,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>55.29</v>
+        <v>54.93</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -3170,13 +3172,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>55.02</v>
+        <v>55.29</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -3185,13 +3187,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>55.59</v>
+        <v>55.02</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -3200,13 +3202,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>54.31</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -3215,13 +3217,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>54.1</v>
+        <v>54.31</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -3230,13 +3232,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>53.8</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -3245,13 +3247,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>53.47</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -3260,13 +3262,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>53.38</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -3275,13 +3277,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>53.17</v>
+        <v>53.38</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -3290,13 +3292,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>53.82</v>
+        <v>53.17</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -3305,13 +3307,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>53.64</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -3320,13 +3322,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>54.46</v>
+        <v>53.64</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -3335,13 +3337,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>54.77</v>
+        <v>54.46</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -3350,13 +3352,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>53.48</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -3365,13 +3367,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>52.62</v>
+        <v>53.48</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -3380,13 +3382,13 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>52.52</v>
+        <v>52.62</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -3395,13 +3397,13 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>52.86</v>
+        <v>52.52</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -3410,13 +3412,13 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>52.43</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -3425,13 +3427,13 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>52.69</v>
+        <v>52.43</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -3440,13 +3442,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>53.79</v>
+        <v>52.69</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -3455,13 +3457,13 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>55.04</v>
+        <v>53.79</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -3470,13 +3472,13 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>55.23</v>
+        <v>55.04</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -3485,13 +3487,13 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>55.16</v>
+        <v>55.23</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -3500,13 +3502,13 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>55.1</v>
+        <v>55.16</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -3515,13 +3517,13 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>51.65</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -3530,13 +3532,13 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>48.65</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -3545,13 +3547,13 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>48.94</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -3560,13 +3562,13 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>48.82</v>
+        <v>48.94</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -3575,13 +3577,13 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>48.46</v>
+        <v>48.82</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -3590,13 +3592,13 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>48.62</v>
+        <v>48.46</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -3605,13 +3607,13 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>47.95</v>
+        <v>48.62</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -3620,13 +3622,13 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>47.8</v>
+        <v>47.95</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -3635,13 +3637,13 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>47.85</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -3650,13 +3652,13 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>47.49</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -3665,13 +3667,13 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>47.78</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -3680,13 +3682,13 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>49.05</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -3695,13 +3697,13 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>49.41</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -3710,13 +3712,13 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>50.03</v>
+        <v>49.41</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -3725,13 +3727,13 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>49.88</v>
+        <v>50.03</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -3740,13 +3742,13 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>49.73</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -3755,13 +3757,13 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>50.23</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -3770,13 +3772,13 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>49.88</v>
+        <v>50.23</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -3785,13 +3787,13 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>49.78</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -3800,13 +3802,13 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>49.2</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -3815,13 +3817,13 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>48.9</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -3830,13 +3832,13 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>51.9</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -3845,13 +3847,13 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>51.46</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -3860,13 +3862,13 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>50.03</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -3875,13 +3877,13 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>48.66</v>
+        <v>50.03</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -3890,13 +3892,13 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>48.38</v>
+        <v>48.66</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -3905,13 +3907,13 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>47.52</v>
+        <v>48.38</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -3920,13 +3922,13 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>48.22</v>
+        <v>47.52</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -3935,13 +3937,13 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>48.33</v>
+        <v>48.22</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -3950,13 +3952,13 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>48.82</v>
+        <v>48.33</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -3965,13 +3967,13 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>48.95</v>
+        <v>48.82</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -3980,13 +3982,13 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>48.22</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -3995,13 +3997,13 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>48.75</v>
+        <v>48.22</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -4010,13 +4012,13 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>49.78</v>
+        <v>48.75</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -4025,13 +4027,13 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>49.23</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -4040,13 +4042,13 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>49.17</v>
+        <v>49.23</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -4055,13 +4057,13 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>47.85</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -4070,13 +4072,13 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>47.78</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -4085,13 +4087,13 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>47.83</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -4100,13 +4102,13 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>47.91</v>
+        <v>47.83</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -4115,13 +4117,13 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>47.73</v>
+        <v>47.91</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -4130,13 +4132,13 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>47.54</v>
+        <v>47.73</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -4145,13 +4147,13 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>46.72</v>
+        <v>47.54</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -4160,13 +4162,13 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>47.16</v>
+        <v>46.72</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -4175,13 +4177,13 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>46.15</v>
+        <v>47.16</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -4190,13 +4192,13 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>46.11</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -4205,13 +4207,13 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>44.82</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -4220,13 +4222,13 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>45.02</v>
+        <v>44.82</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -4235,13 +4237,13 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>45.96</v>
+        <v>45.02</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -4250,13 +4252,13 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>47.35</v>
+        <v>45.96</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -4265,13 +4267,13 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>48.65</v>
+        <v>47.35</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -4280,13 +4282,13 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>47.87</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -4295,13 +4297,13 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>46</v>
+        <v>47.87</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -4310,13 +4312,13 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>46.11</v>
+        <v>46</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -4325,13 +4327,13 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>45.42</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -4340,13 +4342,13 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>44.2</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -4355,13 +4357,13 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>43.82</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -4370,13 +4372,13 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>43.48</v>
+        <v>43.82</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -4385,13 +4387,13 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>43.28</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -4400,13 +4402,13 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>43.7</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -4415,13 +4417,13 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>43.32</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -4430,13 +4432,13 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>43.28</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -4445,13 +4447,13 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>42.9</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -4460,13 +4462,13 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>42.51</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -4475,13 +4477,13 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>42.36</v>
+        <v>42.51</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -4490,13 +4492,13 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>42.65</v>
+        <v>42.36</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -4505,13 +4507,13 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>42.85</v>
+        <v>42.65</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -4520,13 +4522,13 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>43.04</v>
+        <v>42.85</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -4535,13 +4537,13 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>43.92</v>
+        <v>43.04</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -4550,13 +4552,13 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>43.52</v>
+        <v>43.92</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -4565,13 +4567,13 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>43.37</v>
+        <v>43.52</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -4580,13 +4582,13 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>43.24</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -4595,13 +4597,13 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>43.99</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -4610,13 +4612,13 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>44.52</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -4625,13 +4627,13 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>45.66</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -4640,13 +4642,13 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>45.78</v>
+        <v>45.66</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -4655,13 +4657,13 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>46.1</v>
+        <v>45.78</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -4670,13 +4672,13 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>46.42</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -4685,13 +4687,13 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>47.21</v>
+        <v>46.42</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -4700,13 +4702,13 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>47.44</v>
+        <v>47.21</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -4715,13 +4717,13 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>46.5</v>
+        <v>47.44</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -4730,13 +4732,13 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>47.21</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -4745,13 +4747,13 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>46.08</v>
+        <v>47.21</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -4760,13 +4762,13 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>46.21</v>
+        <v>46.08</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -4775,13 +4777,13 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>45.72</v>
+        <v>46.21</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -4790,13 +4792,13 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>46.29</v>
+        <v>45.72</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -4805,13 +4807,13 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>45.9</v>
+        <v>46.29</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -4820,13 +4822,13 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>46.05</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -4835,13 +4837,13 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>45.73</v>
+        <v>46.05</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -4850,13 +4852,13 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>45.31</v>
+        <v>45.73</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -4865,13 +4867,13 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>45.75</v>
+        <v>45.31</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -4880,13 +4882,13 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>46.37</v>
+        <v>45.75</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -4895,13 +4897,13 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>45.77</v>
+        <v>46.37</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -4910,13 +4912,13 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>45.1</v>
+        <v>45.77</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -4925,13 +4927,13 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>44.97</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -4940,13 +4942,13 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>45.11</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -4955,13 +4957,13 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>44.88</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -4970,13 +4972,13 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>45.06</v>
+        <v>44.88</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -4985,13 +4987,13 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>44.73</v>
+        <v>45.06</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -5000,13 +5002,13 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>44.3</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -5015,13 +5017,13 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>45.15</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -5030,13 +5032,13 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>45.27</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -5045,13 +5047,13 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>45.03</v>
+        <v>45.27</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -5060,13 +5062,13 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>45.99</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -5075,13 +5077,13 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>46.22</v>
+        <v>45.99</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -5090,13 +5092,13 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>46.06</v>
+        <v>46.22</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -5105,13 +5107,13 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>45.62</v>
+        <v>46.06</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -5120,13 +5122,13 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>43.48</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -5135,13 +5137,13 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>42.45</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -5150,13 +5152,13 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>42.17</v>
+        <v>42.45</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -5165,13 +5167,13 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>41.34</v>
+        <v>42.17</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -5180,13 +5182,13 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>40.87</v>
+        <v>41.34</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -5195,13 +5197,13 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>41.09</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -5210,13 +5212,13 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>41.32</v>
+        <v>41.09</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -5225,13 +5227,13 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>41.19</v>
+        <v>41.32</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -5240,13 +5242,13 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>40.94</v>
+        <v>41.19</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -5261,7 +5263,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2024-12-24</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -5270,13 +5272,13 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>41.38</v>
+        <v>40.94</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -5285,13 +5287,13 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>41.62</v>
+        <v>41.38</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -5300,13 +5302,13 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>40.87</v>
+        <v>41.62</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -5315,13 +5317,13 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>41.15</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -5330,13 +5332,13 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>40.92</v>
+        <v>41.15</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -5345,13 +5347,13 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>41.73</v>
+        <v>40.92</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -5360,13 +5362,13 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>42.72</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -5375,13 +5377,13 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>43.49</v>
+        <v>42.72</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -5390,13 +5392,13 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>43.53</v>
+        <v>43.49</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -5405,13 +5407,13 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>43.26</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -5420,13 +5422,13 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>43.46</v>
+        <v>43.26</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -5435,13 +5437,13 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>43.52</v>
+        <v>43.46</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -5450,13 +5452,13 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>43.58</v>
+        <v>43.52</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -5465,13 +5467,13 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>42.89</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -5480,13 +5482,13 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>42.12</v>
+        <v>42.89</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -5495,13 +5497,13 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>42.67</v>
+        <v>42.12</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -5510,13 +5512,13 @@
         </is>
       </c>
       <c r="C339" t="n">
-        <v>42.3</v>
+        <v>42.67</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -5525,13 +5527,13 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>42.39</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -5540,13 +5542,13 @@
         </is>
       </c>
       <c r="C341" t="n">
-        <v>41.84</v>
+        <v>42.39</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -5555,13 +5557,13 @@
         </is>
       </c>
       <c r="C342" t="n">
-        <v>43.17</v>
+        <v>41.84</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -5570,13 +5572,13 @@
         </is>
       </c>
       <c r="C343" t="n">
-        <v>42.27</v>
+        <v>43.17</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -5585,13 +5587,13 @@
         </is>
       </c>
       <c r="C344" t="n">
-        <v>42.78</v>
+        <v>42.27</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -5600,13 +5602,13 @@
         </is>
       </c>
       <c r="C345" t="n">
-        <v>43.09</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -5615,13 +5617,13 @@
         </is>
       </c>
       <c r="C346" t="n">
-        <v>43.95</v>
+        <v>43.09</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -5630,13 +5632,13 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>44.91</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -5645,13 +5647,13 @@
         </is>
       </c>
       <c r="C348" t="n">
-        <v>45.32</v>
+        <v>44.91</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -5660,13 +5662,13 @@
         </is>
       </c>
       <c r="C349" t="n">
-        <v>45.24</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -5675,13 +5677,13 @@
         </is>
       </c>
       <c r="C350" t="n">
-        <v>44.48</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -5690,13 +5692,13 @@
         </is>
       </c>
       <c r="C351" t="n">
-        <v>45.38</v>
+        <v>44.48</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -5705,13 +5707,13 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>46.24</v>
+        <v>45.38</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -5720,13 +5722,13 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>47.78</v>
+        <v>46.24</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -5735,13 +5737,13 @@
         </is>
       </c>
       <c r="C354" t="n">
-        <v>48.04</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -5750,13 +5752,13 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>47.49</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -5765,13 +5767,13 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>45.65</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -5780,13 +5782,13 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>45.01</v>
+        <v>45.65</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -5795,13 +5797,13 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>45.36</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -5810,13 +5812,13 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>45.49</v>
+        <v>45.36</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -5825,13 +5827,13 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>44.54</v>
+        <v>45.49</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -5840,13 +5842,13 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>43.62</v>
+        <v>44.54</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -5855,13 +5857,13 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>42.78</v>
+        <v>43.62</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -5870,13 +5872,13 @@
         </is>
       </c>
       <c r="C363" t="n">
-        <v>42.73</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -5885,13 +5887,13 @@
         </is>
       </c>
       <c r="C364" t="n">
-        <v>43.65</v>
+        <v>42.73</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -5900,13 +5902,13 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>43.48</v>
+        <v>43.65</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -5915,13 +5917,13 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>42.77</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -5930,13 +5932,13 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>42.86</v>
+        <v>42.77</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -5945,13 +5947,13 @@
         </is>
       </c>
       <c r="C368" t="n">
-        <v>41.8</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -5960,13 +5962,13 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>41.24</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -5975,13 +5977,13 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>41.92</v>
+        <v>41.24</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -5990,13 +5992,13 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>41.59</v>
+        <v>41.92</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -6005,13 +6007,13 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>42.03</v>
+        <v>41.59</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -6026,7 +6028,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -6035,13 +6037,13 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>43.28</v>
+        <v>42.03</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -6050,13 +6052,13 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>43.74</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -6065,13 +6067,13 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>43.16</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -6080,13 +6082,13 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>43.22</v>
+        <v>43.16</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -6095,13 +6097,13 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>44.73</v>
+        <v>43.22</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -6110,13 +6112,13 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>44.08</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -6125,13 +6127,13 @@
         </is>
       </c>
       <c r="C380" t="n">
-        <v>44.43</v>
+        <v>44.08</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -6140,13 +6142,13 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>43.57</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -6155,13 +6157,13 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>43.08</v>
+        <v>43.57</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -6170,13 +6172,13 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>43.05</v>
+        <v>43.08</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -6185,13 +6187,13 @@
         </is>
       </c>
       <c r="C384" t="n">
-        <v>42.78</v>
+        <v>43.05</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -6200,13 +6202,13 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>43.53</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -6215,13 +6217,13 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>43.71</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -6230,13 +6232,13 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>43.14</v>
+        <v>43.71</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -6245,13 +6247,13 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>42.09</v>
+        <v>43.14</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -6260,13 +6262,13 @@
         </is>
       </c>
       <c r="C389" t="n">
-        <v>41.73</v>
+        <v>42.09</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -6275,13 +6277,13 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>41.43</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -6290,13 +6292,13 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>41.17</v>
+        <v>41.43</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -6305,13 +6307,13 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>40.69</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -6320,13 +6322,13 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>40.11</v>
+        <v>40.69</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -6335,13 +6337,13 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>40.12</v>
+        <v>40.11</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -6350,13 +6352,13 @@
         </is>
       </c>
       <c r="C395" t="n">
-        <v>40.75</v>
+        <v>40.12</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -6365,13 +6367,13 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>40.39</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -6380,13 +6382,13 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>40.6</v>
+        <v>40.39</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -6395,13 +6397,13 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>41.29</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -6410,13 +6412,13 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>40.49</v>
+        <v>41.29</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -6425,13 +6427,13 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>41.62</v>
+        <v>40.49</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -6440,13 +6442,13 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>40.98</v>
+        <v>41.62</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -6455,13 +6457,13 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>41.5</v>
+        <v>40.98</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -6470,13 +6472,13 @@
         </is>
       </c>
       <c r="C403" t="n">
-        <v>42.26</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -6485,13 +6487,13 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>42.24</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -6500,13 +6502,13 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>41.21</v>
+        <v>42.24</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -6515,13 +6517,13 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>40.93</v>
+        <v>41.21</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -6530,13 +6532,13 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>40.83</v>
+        <v>40.93</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -6545,13 +6547,13 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>40.51</v>
+        <v>40.83</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -6560,13 +6562,13 @@
         </is>
       </c>
       <c r="C409" t="n">
-        <v>39.52</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -6575,13 +6577,13 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>40.05</v>
+        <v>39.52</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -6590,13 +6592,13 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>39.68</v>
+        <v>40.05</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -6605,13 +6607,13 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>39.76</v>
+        <v>39.68</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -6620,13 +6622,13 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>39.55</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -6635,13 +6637,13 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>39.29</v>
+        <v>39.55</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -6650,13 +6652,13 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>39.58</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -6665,13 +6667,13 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>39.89</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -6680,13 +6682,13 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>40.84</v>
+        <v>39.89</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -6695,13 +6697,13 @@
         </is>
       </c>
       <c r="C418" t="n">
-        <v>40.75</v>
+        <v>40.84</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -6710,13 +6712,13 @@
         </is>
       </c>
       <c r="C419" t="n">
-        <v>40.68</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -6725,13 +6727,13 @@
         </is>
       </c>
       <c r="C420" t="n">
-        <v>40.51</v>
+        <v>40.68</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -6740,13 +6742,13 @@
         </is>
       </c>
       <c r="C421" t="n">
-        <v>40.16</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -6755,13 +6757,13 @@
         </is>
       </c>
       <c r="C422" t="n">
-        <v>40.25</v>
+        <v>40.16</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -6770,13 +6772,13 @@
         </is>
       </c>
       <c r="C423" t="n">
-        <v>40.91</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -6785,13 +6787,13 @@
         </is>
       </c>
       <c r="C424" t="n">
-        <v>41.18</v>
+        <v>40.91</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -6800,13 +6802,13 @@
         </is>
       </c>
       <c r="C425" t="n">
-        <v>41.72</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -6815,13 +6817,13 @@
         </is>
       </c>
       <c r="C426" t="n">
-        <v>41.2</v>
+        <v>41.72</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -6830,13 +6832,13 @@
         </is>
       </c>
       <c r="C427" t="n">
-        <v>41.67</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -6845,13 +6847,13 @@
         </is>
       </c>
       <c r="C428" t="n">
-        <v>41.34</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -6860,13 +6862,13 @@
         </is>
       </c>
       <c r="C429" t="n">
-        <v>42.82</v>
+        <v>41.34</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -6875,13 +6877,13 @@
         </is>
       </c>
       <c r="C430" t="n">
-        <v>42.57</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -6890,13 +6892,13 @@
         </is>
       </c>
       <c r="C431" t="n">
-        <v>43.28</v>
+        <v>42.57</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -6905,13 +6907,13 @@
         </is>
       </c>
       <c r="C432" t="n">
-        <v>42.86</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -6920,13 +6922,13 @@
         </is>
       </c>
       <c r="C433" t="n">
-        <v>41.96</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -6935,13 +6937,13 @@
         </is>
       </c>
       <c r="C434" t="n">
-        <v>42.63</v>
+        <v>41.96</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -6950,13 +6952,13 @@
         </is>
       </c>
       <c r="C435" t="n">
-        <v>42.6</v>
+        <v>42.63</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -6965,13 +6967,13 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>43.39</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -6980,13 +6982,13 @@
         </is>
       </c>
       <c r="C437" t="n">
-        <v>43.49</v>
+        <v>43.39</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -6995,13 +6997,13 @@
         </is>
       </c>
       <c r="C438" t="n">
-        <v>44.6</v>
+        <v>43.49</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -7010,13 +7012,13 @@
         </is>
       </c>
       <c r="C439" t="n">
-        <v>45.01</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -7025,13 +7027,13 @@
         </is>
       </c>
       <c r="C440" t="n">
-        <v>44.73</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -7040,13 +7042,13 @@
         </is>
       </c>
       <c r="C441" t="n">
-        <v>45.87</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -7055,13 +7057,13 @@
         </is>
       </c>
       <c r="C442" t="n">
-        <v>46.97</v>
+        <v>45.87</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -7070,13 +7072,13 @@
         </is>
       </c>
       <c r="C443" t="n">
-        <v>47.02</v>
+        <v>46.97</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -7085,13 +7087,13 @@
         </is>
       </c>
       <c r="C444" t="n">
-        <v>46.75</v>
+        <v>47.02</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -7100,13 +7102,13 @@
         </is>
       </c>
       <c r="C445" t="n">
-        <v>45.79</v>
+        <v>46.75</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -7115,13 +7117,13 @@
         </is>
       </c>
       <c r="C446" t="n">
-        <v>44.84</v>
+        <v>45.79</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -7130,13 +7132,13 @@
         </is>
       </c>
       <c r="C447" t="n">
-        <v>43.13</v>
+        <v>44.84</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -7145,13 +7147,13 @@
         </is>
       </c>
       <c r="C448" t="n">
-        <v>42.97</v>
+        <v>43.13</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -7160,13 +7162,13 @@
         </is>
       </c>
       <c r="C449" t="n">
-        <v>43.37</v>
+        <v>42.97</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -7175,13 +7177,13 @@
         </is>
       </c>
       <c r="C450" t="n">
-        <v>42.71</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -7190,13 +7192,13 @@
         </is>
       </c>
       <c r="C451" t="n">
-        <v>43.35</v>
+        <v>42.71</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -7205,13 +7207,13 @@
         </is>
       </c>
       <c r="C452" t="n">
-        <v>43.58</v>
+        <v>43.35</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -7220,13 +7222,13 @@
         </is>
       </c>
       <c r="C453" t="n">
-        <v>43.59</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -7235,13 +7237,13 @@
         </is>
       </c>
       <c r="C454" t="n">
-        <v>44.01</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -7250,13 +7252,13 @@
         </is>
       </c>
       <c r="C455" t="n">
-        <v>43.56</v>
+        <v>44.01</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -7265,13 +7267,13 @@
         </is>
       </c>
       <c r="C456" t="n">
-        <v>43.53</v>
+        <v>43.56</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -7280,13 +7282,13 @@
         </is>
       </c>
       <c r="C457" t="n">
-        <v>43.76</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -7295,13 +7297,13 @@
         </is>
       </c>
       <c r="C458" t="n">
-        <v>43.87</v>
+        <v>43.76</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -7310,13 +7312,13 @@
         </is>
       </c>
       <c r="C459" t="n">
-        <v>43.76</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -7325,13 +7327,13 @@
         </is>
       </c>
       <c r="C460" t="n">
-        <v>43.98</v>
+        <v>43.76</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -7340,13 +7342,13 @@
         </is>
       </c>
       <c r="C461" t="n">
-        <v>44.29</v>
+        <v>43.98</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -7355,13 +7357,13 @@
         </is>
       </c>
       <c r="C462" t="n">
-        <v>44.83</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -7370,13 +7372,13 @@
         </is>
       </c>
       <c r="C463" t="n">
-        <v>43.88</v>
+        <v>44.83</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -7385,13 +7387,13 @@
         </is>
       </c>
       <c r="C464" t="n">
-        <v>44.2</v>
+        <v>43.88</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -7400,13 +7402,13 @@
         </is>
       </c>
       <c r="C465" t="n">
-        <v>44.63</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -7415,13 +7417,13 @@
         </is>
       </c>
       <c r="C466" t="n">
-        <v>45.81</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -7430,13 +7432,13 @@
         </is>
       </c>
       <c r="C467" t="n">
-        <v>45.93</v>
+        <v>45.81</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -7445,13 +7447,13 @@
         </is>
       </c>
       <c r="C468" t="n">
-        <v>46.11</v>
+        <v>45.93</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -7460,13 +7462,13 @@
         </is>
       </c>
       <c r="C469" t="n">
-        <v>45.74</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -7475,13 +7477,13 @@
         </is>
       </c>
       <c r="C470" t="n">
-        <v>45.32</v>
+        <v>45.74</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -7490,13 +7492,13 @@
         </is>
       </c>
       <c r="C471" t="n">
-        <v>45.96</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -7505,13 +7507,13 @@
         </is>
       </c>
       <c r="C472" t="n">
-        <v>46.2</v>
+        <v>45.96</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -7520,13 +7522,13 @@
         </is>
       </c>
       <c r="C473" t="n">
-        <v>46.37</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -7535,13 +7537,13 @@
         </is>
       </c>
       <c r="C474" t="n">
-        <v>46.6</v>
+        <v>46.37</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -7550,13 +7552,13 @@
         </is>
       </c>
       <c r="C475" t="n">
-        <v>45.89</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -7565,13 +7567,13 @@
         </is>
       </c>
       <c r="C476" t="n">
-        <v>45.45</v>
+        <v>45.89</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -7580,13 +7582,13 @@
         </is>
       </c>
       <c r="C477" t="n">
-        <v>44.82</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -7595,13 +7597,13 @@
         </is>
       </c>
       <c r="C478" t="n">
-        <v>44.7</v>
+        <v>44.82</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -7610,13 +7612,13 @@
         </is>
       </c>
       <c r="C479" t="n">
-        <v>46.01</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -7625,13 +7627,13 @@
         </is>
       </c>
       <c r="C480" t="n">
-        <v>45.24</v>
+        <v>46.01</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -7640,13 +7642,13 @@
         </is>
       </c>
       <c r="C481" t="n">
-        <v>44.2</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -7655,13 +7657,13 @@
         </is>
       </c>
       <c r="C482" t="n">
-        <v>44.8</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -7670,13 +7672,13 @@
         </is>
       </c>
       <c r="C483" t="n">
-        <v>45.29</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -7685,13 +7687,13 @@
         </is>
       </c>
       <c r="C484" t="n">
-        <v>44.66</v>
+        <v>45.29</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -7700,13 +7702,13 @@
         </is>
       </c>
       <c r="C485" t="n">
-        <v>44.34</v>
+        <v>44.66</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -7715,13 +7717,13 @@
         </is>
       </c>
       <c r="C486" t="n">
-        <v>44.43</v>
+        <v>44.34</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -7730,13 +7732,13 @@
         </is>
       </c>
       <c r="C487" t="n">
-        <v>44.49</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -7745,13 +7747,13 @@
         </is>
       </c>
       <c r="C488" t="n">
-        <v>44.32</v>
+        <v>44.49</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -7760,13 +7762,13 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>45.01</v>
+        <v>44.32</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -7775,13 +7777,13 @@
         </is>
       </c>
       <c r="C490" t="n">
-        <v>45.94</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -7790,13 +7792,13 @@
         </is>
       </c>
       <c r="C491" t="n">
-        <v>45.67</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -7805,13 +7807,13 @@
         </is>
       </c>
       <c r="C492" t="n">
-        <v>45.58</v>
+        <v>45.67</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -7820,13 +7822,13 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>45.95</v>
+        <v>45.58</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -7835,13 +7837,13 @@
         </is>
       </c>
       <c r="C494" t="n">
-        <v>45.8</v>
+        <v>45.95</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -7850,13 +7852,13 @@
         </is>
       </c>
       <c r="C495" t="n">
-        <v>45.14</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -7865,13 +7867,13 @@
         </is>
       </c>
       <c r="C496" t="n">
-        <v>44.97</v>
+        <v>45.14</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -7880,13 +7882,13 @@
         </is>
       </c>
       <c r="C497" t="n">
-        <v>45.19</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -7895,13 +7897,13 @@
         </is>
       </c>
       <c r="C498" t="n">
-        <v>45.34</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -7910,13 +7912,13 @@
         </is>
       </c>
       <c r="C499" t="n">
-        <v>45.6</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -7925,13 +7927,13 @@
         </is>
       </c>
       <c r="C500" t="n">
-        <v>45.97</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -7940,13 +7942,13 @@
         </is>
       </c>
       <c r="C501" t="n">
-        <v>45.91</v>
+        <v>45.97</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -7955,13 +7957,13 @@
         </is>
       </c>
       <c r="C502" t="n">
-        <v>46.95</v>
+        <v>45.91</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -7970,13 +7972,13 @@
         </is>
       </c>
       <c r="C503" t="n">
-        <v>46.91</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -7985,13 +7987,13 @@
         </is>
       </c>
       <c r="C504" t="n">
-        <v>47.23</v>
+        <v>46.91</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -8000,13 +8002,13 @@
         </is>
       </c>
       <c r="C505" t="n">
-        <v>47.84</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -8015,13 +8017,13 @@
         </is>
       </c>
       <c r="C506" t="n">
-        <v>47.38</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -8030,13 +8032,13 @@
         </is>
       </c>
       <c r="C507" t="n">
-        <v>48</v>
+        <v>47.38</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -8045,13 +8047,13 @@
         </is>
       </c>
       <c r="C508" t="n">
-        <v>47.67</v>
+        <v>48</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -8060,13 +8062,13 @@
         </is>
       </c>
       <c r="C509" t="n">
-        <v>47.12</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -8075,13 +8077,13 @@
         </is>
       </c>
       <c r="C510" t="n">
-        <v>47.14</v>
+        <v>47.12</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -8090,13 +8092,13 @@
         </is>
       </c>
       <c r="C511" t="n">
-        <v>46.67</v>
+        <v>47.14</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -8105,13 +8107,13 @@
         </is>
       </c>
       <c r="C512" t="n">
-        <v>47.46</v>
+        <v>46.67</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -8120,13 +8122,13 @@
         </is>
       </c>
       <c r="C513" t="n">
-        <v>47.71</v>
+        <v>47.46</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -8135,13 +8137,13 @@
         </is>
       </c>
       <c r="C514" t="n">
-        <v>46.65</v>
+        <v>47.71</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -8150,13 +8152,13 @@
         </is>
       </c>
       <c r="C515" t="n">
-        <v>47.72</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -8165,13 +8167,13 @@
         </is>
       </c>
       <c r="C516" t="n">
-        <v>47.89</v>
+        <v>47.72</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -8180,13 +8182,13 @@
         </is>
       </c>
       <c r="C517" t="n">
-        <v>47.23</v>
+        <v>47.89</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -8195,13 +8197,13 @@
         </is>
       </c>
       <c r="C518" t="n">
-        <v>47.63</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -8210,13 +8212,13 @@
         </is>
       </c>
       <c r="C519" t="n">
-        <v>48.16</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -8225,13 +8227,13 @@
         </is>
       </c>
       <c r="C520" t="n">
-        <v>47.08</v>
+        <v>48.16</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -8240,13 +8242,13 @@
         </is>
       </c>
       <c r="C521" t="n">
-        <v>47.34</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -8255,13 +8257,13 @@
         </is>
       </c>
       <c r="C522" t="n">
-        <v>46.61</v>
+        <v>47.34</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -8270,13 +8272,13 @@
         </is>
       </c>
       <c r="C523" t="n">
-        <v>45.84</v>
+        <v>46.61</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -8285,13 +8287,13 @@
         </is>
       </c>
       <c r="C524" t="n">
-        <v>45.28</v>
+        <v>45.84</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -8300,13 +8302,13 @@
         </is>
       </c>
       <c r="C525" t="n">
-        <v>45.23</v>
+        <v>45.28</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -8315,13 +8317,13 @@
         </is>
       </c>
       <c r="C526" t="n">
-        <v>44.51</v>
+        <v>45.23</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -8330,13 +8332,13 @@
         </is>
       </c>
       <c r="C527" t="n">
-        <v>44.37</v>
+        <v>44.51</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -8345,13 +8347,13 @@
         </is>
       </c>
       <c r="C528" t="n">
-        <v>44.55</v>
+        <v>44.37</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -8360,13 +8362,13 @@
         </is>
       </c>
       <c r="C529" t="n">
-        <v>44.45</v>
+        <v>44.55</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -8375,13 +8377,13 @@
         </is>
       </c>
       <c r="C530" t="n">
-        <v>44.56</v>
+        <v>44.45</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -8390,13 +8392,13 @@
         </is>
       </c>
       <c r="C531" t="n">
-        <v>44.63</v>
+        <v>44.56</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -8405,13 +8407,13 @@
         </is>
       </c>
       <c r="C532" t="n">
-        <v>44.69</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>2024-02-26</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -8420,13 +8422,13 @@
         </is>
       </c>
       <c r="C533" t="n">
-        <v>44.2</v>
+        <v>44.69</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -8435,13 +8437,13 @@
         </is>
       </c>
       <c r="C534" t="n">
-        <v>43.78</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -8450,13 +8452,13 @@
         </is>
       </c>
       <c r="C535" t="n">
-        <v>43.99</v>
+        <v>43.78</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-22</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -8465,13 +8467,13 @@
         </is>
       </c>
       <c r="C536" t="n">
-        <v>44</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -8480,13 +8482,13 @@
         </is>
       </c>
       <c r="C537" t="n">
-        <v>44.35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -8495,13 +8497,13 @@
         </is>
       </c>
       <c r="C538" t="n">
-        <v>44.52</v>
+        <v>44.35</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -8510,13 +8512,13 @@
         </is>
       </c>
       <c r="C539" t="n">
-        <v>44.68</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -8525,13 +8527,13 @@
         </is>
       </c>
       <c r="C540" t="n">
-        <v>45.07</v>
+        <v>44.68</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -8540,13 +8542,13 @@
         </is>
       </c>
       <c r="C541" t="n">
-        <v>45.62</v>
+        <v>45.07</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -8555,13 +8557,13 @@
         </is>
       </c>
       <c r="C542" t="n">
-        <v>45.33</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -8570,13 +8572,13 @@
         </is>
       </c>
       <c r="C543" t="n">
-        <v>45.64</v>
+        <v>45.33</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-09</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -8585,13 +8587,13 @@
         </is>
       </c>
       <c r="C544" t="n">
-        <v>45.59</v>
+        <v>45.64</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -8600,13 +8602,13 @@
         </is>
       </c>
       <c r="C545" t="n">
-        <v>44.61</v>
+        <v>45.59</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -8615,13 +8617,13 @@
         </is>
       </c>
       <c r="C546" t="n">
-        <v>44.2</v>
+        <v>44.61</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -8630,13 +8632,13 @@
         </is>
       </c>
       <c r="C547" t="n">
-        <v>43.73</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -8645,13 +8647,13 @@
         </is>
       </c>
       <c r="C548" t="n">
-        <v>43.66</v>
+        <v>43.73</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -8660,13 +8662,13 @@
         </is>
       </c>
       <c r="C549" t="n">
-        <v>44.07</v>
+        <v>43.66</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -8675,13 +8677,13 @@
         </is>
       </c>
       <c r="C550" t="n">
-        <v>44.66</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -8690,13 +8692,13 @@
         </is>
       </c>
       <c r="C551" t="n">
-        <v>44.75</v>
+        <v>44.66</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-01-30</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -8705,13 +8707,13 @@
         </is>
       </c>
       <c r="C552" t="n">
-        <v>44.73</v>
+        <v>44.75</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -8720,13 +8722,13 @@
         </is>
       </c>
       <c r="C553" t="n">
-        <v>45.37</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -8735,13 +8737,13 @@
         </is>
       </c>
       <c r="C554" t="n">
-        <v>45.34</v>
+        <v>45.37</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -8750,13 +8752,13 @@
         </is>
       </c>
       <c r="C555" t="n">
-        <v>45.57</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>2024-01-23</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -8765,13 +8767,13 @@
         </is>
       </c>
       <c r="C556" t="n">
-        <v>45.97</v>
+        <v>45.57</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2024-01-23</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -8780,13 +8782,13 @@
         </is>
       </c>
       <c r="C557" t="n">
-        <v>45.94</v>
+        <v>45.97</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>2024-01-19</t>
+          <t>2024-01-22</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -8795,13 +8797,13 @@
         </is>
       </c>
       <c r="C558" t="n">
-        <v>45.19</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -8810,13 +8812,13 @@
         </is>
       </c>
       <c r="C559" t="n">
-        <v>45.44</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -8825,13 +8827,13 @@
         </is>
       </c>
       <c r="C560" t="n">
-        <v>45.42</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -8846,7 +8848,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -8855,13 +8857,13 @@
         </is>
       </c>
       <c r="C562" t="n">
-        <v>46.13</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>2024-01-11</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -8870,13 +8872,13 @@
         </is>
       </c>
       <c r="C563" t="n">
-        <v>46.6</v>
+        <v>46.13</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -8885,13 +8887,13 @@
         </is>
       </c>
       <c r="C564" t="n">
-        <v>46.28</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-10</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -8900,13 +8902,13 @@
         </is>
       </c>
       <c r="C565" t="n">
-        <v>46.63</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>2024-01-08</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -8915,13 +8917,13 @@
         </is>
       </c>
       <c r="C566" t="n">
-        <v>45.95</v>
+        <v>46.63</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>2024-01-08</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -8930,13 +8932,13 @@
         </is>
       </c>
       <c r="C567" t="n">
-        <v>45.99</v>
+        <v>45.95</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>2024-01-04</t>
+          <t>2024-01-05</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -8945,13 +8947,13 @@
         </is>
       </c>
       <c r="C568" t="n">
-        <v>46.36</v>
+        <v>45.99</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>2024-01-03</t>
+          <t>2024-01-04</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -8960,13 +8962,13 @@
         </is>
       </c>
       <c r="C569" t="n">
-        <v>46.7</v>
+        <v>46.36</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-01-03</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -8975,13 +8977,13 @@
         </is>
       </c>
       <c r="C570" t="n">
-        <v>46.66</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>2023-12-29</t>
+          <t>2024-01-02</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -8990,13 +8992,13 @@
         </is>
       </c>
       <c r="C571" t="n">
-        <v>46.4</v>
+        <v>46.66</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>2023-12-28</t>
+          <t>2023-12-29</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -9005,13 +9007,13 @@
         </is>
       </c>
       <c r="C572" t="n">
-        <v>46.26</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>2023-12-27</t>
+          <t>2023-12-28</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -9020,13 +9022,13 @@
         </is>
       </c>
       <c r="C573" t="n">
-        <v>46.98</v>
+        <v>46.26</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>2023-12-26</t>
+          <t>2023-12-27</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -9035,13 +9037,13 @@
         </is>
       </c>
       <c r="C574" t="n">
-        <v>47.03</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2023-12-26</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -9050,13 +9052,13 @@
         </is>
       </c>
       <c r="C575" t="n">
-        <v>47.28</v>
+        <v>47.03</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2023-12-22</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -9065,13 +9067,13 @@
         </is>
       </c>
       <c r="C576" t="n">
-        <v>47.36</v>
+        <v>47.28</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -9080,13 +9082,13 @@
         </is>
       </c>
       <c r="C577" t="n">
-        <v>48.24</v>
+        <v>47.36</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -9095,13 +9097,13 @@
         </is>
       </c>
       <c r="C578" t="n">
-        <v>48.29</v>
+        <v>48.24</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -9110,13 +9112,13 @@
         </is>
       </c>
       <c r="C579" t="n">
-        <v>48.22</v>
+        <v>48.29</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -9125,21 +9127,36 @@
         </is>
       </c>
       <c r="C580" t="n">
-        <v>47.59</v>
+        <v>48.22</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
+          <t>2023-12-15</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C581" t="n">
+        <v>47.59</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
           <t>2023-12-14</t>
         </is>
       </c>
-      <c r="B581" t="inlineStr">
-        <is>
-          <t>BOK26</t>
-        </is>
-      </c>
-      <c r="C581" t="n">
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C582" t="n">
         <v>47.31</v>
       </c>
     </row>

--- a/data/lseg_excel/BOK26.xlsx
+++ b/data/lseg_excel/BOK26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C582"/>
+  <dimension ref="A1:C587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>67.20999999999999</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>69.72</v>
+        <v>66.44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>69.95</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -502,13 +502,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>68.94</v>
+        <v>67.09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>68.94</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>67.11</v>
+        <v>67.42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>68.88</v>
+        <v>69.72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -562,13 +562,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>68.47</v>
+        <v>69.95</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>67.41</v>
+        <v>68.94</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>68.02</v>
+        <v>68.94</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>67.09999999999999</v>
+        <v>67.11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>65.73</v>
+        <v>68.88</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -637,13 +637,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>65.58</v>
+        <v>68.47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -652,13 +652,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>65.51000000000001</v>
+        <v>67.41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -667,13 +667,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>65.41</v>
+        <v>68.02</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -682,13 +682,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>65.53</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -697,13 +697,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>65.97</v>
+        <v>65.73</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -712,13 +712,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>63.94</v>
+        <v>65.58</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>67.44</v>
+        <v>65.51000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -742,13 +742,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>67.42</v>
+        <v>65.41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>67.16</v>
+        <v>65.53</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -772,13 +772,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>65.62</v>
+        <v>65.97</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>66.09999999999999</v>
+        <v>63.94</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -802,13 +802,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>66.58</v>
+        <v>67.44</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>65.7</v>
+        <v>67.42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>63.59</v>
+        <v>67.16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -847,13 +847,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>62.82</v>
+        <v>65.62</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>62.74</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -877,13 +877,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>61.85</v>
+        <v>66.58</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -892,13 +892,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>61.76</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>60.67</v>
+        <v>63.59</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -922,13 +922,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>60.5</v>
+        <v>62.82</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -937,13 +937,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>59.88</v>
+        <v>62.74</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -952,13 +952,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>59.3</v>
+        <v>61.85</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>60.09</v>
+        <v>61.76</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>59.08</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>57.76</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>57.47</v>
+        <v>59.88</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1027,13 +1027,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>57.91</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1042,13 +1042,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>57.5</v>
+        <v>60.09</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>57.74</v>
+        <v>59.08</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>57.17</v>
+        <v>57.76</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>55.84</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1102,13 +1102,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>56.17</v>
+        <v>57.91</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>56.18</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>55.03</v>
+        <v>57.74</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1147,13 +1147,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>53.74</v>
+        <v>57.17</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1162,13 +1162,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>54.06</v>
+        <v>55.84</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>54.58</v>
+        <v>56.17</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>54.85</v>
+        <v>56.18</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1207,13 +1207,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>54.95</v>
+        <v>55.03</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1222,13 +1222,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>54.42</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1237,13 +1237,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>54.52</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>54.33</v>
+        <v>54.58</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>54.54</v>
+        <v>54.85</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1282,13 +1282,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>53.11</v>
+        <v>54.95</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>53.15</v>
+        <v>54.42</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>53.47</v>
+        <v>54.52</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>51.5</v>
+        <v>54.33</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1342,13 +1342,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>51.69</v>
+        <v>54.54</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1357,13 +1357,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>50.77</v>
+        <v>53.11</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1372,13 +1372,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>50.2</v>
+        <v>53.15</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>49.97</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1402,13 +1402,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>49.84</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>49.95</v>
+        <v>51.69</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>50.41</v>
+        <v>50.77</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1447,13 +1447,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>49.83</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1462,13 +1462,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>49.09</v>
+        <v>49.97</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1477,13 +1477,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>49.94</v>
+        <v>49.84</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>49.8</v>
+        <v>49.95</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>49.73</v>
+        <v>50.41</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1522,13 +1522,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>50</v>
+        <v>49.83</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1537,13 +1537,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>49.28</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1552,13 +1552,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>49.58</v>
+        <v>49.94</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1567,13 +1567,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>48.92</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1582,13 +1582,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>49.1</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>49.53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1612,13 +1612,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>49.4</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1627,13 +1627,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>50.45</v>
+        <v>49.58</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1642,13 +1642,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>51.03</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1657,13 +1657,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>51.68</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1672,13 +1672,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>51.96</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1687,13 +1687,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>51.88</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1702,13 +1702,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>52.04</v>
+        <v>50.45</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1717,13 +1717,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>52.54</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>52.63</v>
+        <v>51.68</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1747,13 +1747,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>52.54</v>
+        <v>51.96</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1762,13 +1762,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>53.51</v>
+        <v>51.88</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1777,13 +1777,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>53.16</v>
+        <v>52.04</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1792,13 +1792,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>52.84</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1807,13 +1807,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>51.89</v>
+        <v>52.63</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -1822,13 +1822,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>51.51</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>51.41</v>
+        <v>53.51</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1852,13 +1852,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>51.47</v>
+        <v>53.16</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1867,13 +1867,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>51.83</v>
+        <v>52.84</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -1882,13 +1882,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>52.3</v>
+        <v>51.89</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1897,13 +1897,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>53.35</v>
+        <v>51.51</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>52.36</v>
+        <v>51.41</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -1927,13 +1927,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>51.46</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -1942,13 +1942,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>51.56</v>
+        <v>51.83</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -1957,13 +1957,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>51.9</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>52.33</v>
+        <v>53.35</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -1987,13 +1987,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>51.8</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2002,13 +2002,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>50.9</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>50.56</v>
+        <v>51.56</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2032,13 +2032,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>50.88</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2047,13 +2047,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>50.76</v>
+        <v>52.33</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2062,13 +2062,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>51.08</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>50</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2092,13 +2092,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>50.88</v>
+        <v>50.56</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2107,13 +2107,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>51.34</v>
+        <v>50.88</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2122,13 +2122,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>51.46</v>
+        <v>50.76</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2137,13 +2137,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>51.93</v>
+        <v>51.08</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2152,13 +2152,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>51.4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2167,13 +2167,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>51.93</v>
+        <v>50.88</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2182,13 +2182,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>51.21</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2197,13 +2197,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>51.72</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2212,13 +2212,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>52.32</v>
+        <v>51.93</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2227,13 +2227,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>52.09</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2242,13 +2242,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>51.84</v>
+        <v>51.93</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2257,13 +2257,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>51.73</v>
+        <v>51.21</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2272,13 +2272,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>51.47</v>
+        <v>51.72</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>51.47</v>
+        <v>52.32</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2302,13 +2302,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>50.86</v>
+        <v>52.09</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2323,7 +2323,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2332,13 +2332,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>52.41</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>51.89</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2362,13 +2362,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>51.33</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>51.02</v>
+        <v>50.86</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -2392,13 +2392,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>51.38</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -2407,13 +2407,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>51.34</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -2422,13 +2422,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>50.46</v>
+        <v>51.89</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -2437,13 +2437,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>50.74</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -2452,13 +2452,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>51.27</v>
+        <v>51.02</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -2467,13 +2467,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>51.34</v>
+        <v>51.38</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -2482,13 +2482,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>50.92</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -2497,13 +2497,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>50.93</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -2512,13 +2512,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>50.7</v>
+        <v>50.74</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -2527,13 +2527,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>51.5</v>
+        <v>51.27</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>52.03</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -2557,13 +2557,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>52.59</v>
+        <v>50.92</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -2572,13 +2572,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>53.81</v>
+        <v>50.93</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -2587,13 +2587,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>52.98</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -2602,13 +2602,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>52.98</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>52.41</v>
+        <v>52.03</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -2632,13 +2632,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>51.85</v>
+        <v>52.59</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>51.41</v>
+        <v>53.81</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -2662,13 +2662,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>52.36</v>
+        <v>52.98</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -2677,13 +2677,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>52.02</v>
+        <v>52.98</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -2692,13 +2692,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>52.63</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -2707,13 +2707,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>52.54</v>
+        <v>51.85</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -2722,13 +2722,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>53.3</v>
+        <v>51.41</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -2737,13 +2737,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>52.79</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -2752,13 +2752,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>53.07</v>
+        <v>52.02</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -2767,13 +2767,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>53.82</v>
+        <v>52.63</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -2782,13 +2782,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>53.93</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -2797,13 +2797,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>55.12</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -2812,13 +2812,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>55.41</v>
+        <v>52.79</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -2827,13 +2827,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>54.01</v>
+        <v>53.07</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -2842,13 +2842,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>51.87</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -2857,13 +2857,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>52.23</v>
+        <v>53.93</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -2872,13 +2872,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>53.59</v>
+        <v>55.12</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>53.31</v>
+        <v>55.41</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -2902,13 +2902,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>52.27</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>53.3</v>
+        <v>51.87</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -2932,13 +2932,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>53</v>
+        <v>52.23</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -2947,13 +2947,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>52.87</v>
+        <v>53.59</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -2962,13 +2962,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>52.46</v>
+        <v>53.31</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -2977,13 +2977,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>53.33</v>
+        <v>52.27</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -2992,13 +2992,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>53.53</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3007,13 +3007,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>53.25</v>
+        <v>53</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3022,13 +3022,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>53.87</v>
+        <v>52.87</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -3037,13 +3037,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>53.61</v>
+        <v>52.46</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -3052,13 +3052,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>54.32</v>
+        <v>53.33</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>55.55</v>
+        <v>53.53</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -3082,13 +3082,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>56.24</v>
+        <v>53.25</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3097,13 +3097,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>55.61</v>
+        <v>53.87</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -3112,13 +3112,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>55.47</v>
+        <v>53.61</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -3127,13 +3127,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>55.8</v>
+        <v>54.32</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -3142,13 +3142,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>55.34</v>
+        <v>55.55</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -3157,13 +3157,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>54.93</v>
+        <v>56.24</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -3172,13 +3172,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>55.29</v>
+        <v>55.61</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -3187,13 +3187,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>55.02</v>
+        <v>55.47</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -3202,13 +3202,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>55.59</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -3217,13 +3217,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>54.31</v>
+        <v>55.34</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -3232,13 +3232,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>54.1</v>
+        <v>54.93</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -3247,13 +3247,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>53.8</v>
+        <v>55.29</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -3262,13 +3262,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>53.47</v>
+        <v>55.02</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>53.38</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -3292,13 +3292,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>53.17</v>
+        <v>54.31</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -3307,13 +3307,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>53.82</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -3322,13 +3322,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>53.64</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -3337,13 +3337,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>54.46</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -3352,13 +3352,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>54.77</v>
+        <v>53.38</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -3367,13 +3367,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>53.48</v>
+        <v>53.17</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -3382,13 +3382,13 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>52.62</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>52.52</v>
+        <v>53.64</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -3412,13 +3412,13 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>52.86</v>
+        <v>54.46</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -3427,13 +3427,13 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>52.43</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -3442,13 +3442,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>52.69</v>
+        <v>53.48</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -3457,13 +3457,13 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>53.79</v>
+        <v>52.62</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -3472,13 +3472,13 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>55.04</v>
+        <v>52.52</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -3487,13 +3487,13 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>55.23</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -3502,13 +3502,13 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>55.16</v>
+        <v>52.43</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>55.1</v>
+        <v>52.69</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -3532,13 +3532,13 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>51.65</v>
+        <v>53.79</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -3547,13 +3547,13 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>48.65</v>
+        <v>55.04</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -3562,13 +3562,13 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>48.94</v>
+        <v>55.23</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -3577,13 +3577,13 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>48.82</v>
+        <v>55.16</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -3592,13 +3592,13 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>48.46</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -3607,13 +3607,13 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>48.62</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -3622,13 +3622,13 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>47.95</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -3637,13 +3637,13 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>47.8</v>
+        <v>48.94</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -3652,13 +3652,13 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>47.85</v>
+        <v>48.82</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>47.49</v>
+        <v>48.46</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -3682,13 +3682,13 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>47.78</v>
+        <v>48.62</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -3697,13 +3697,13 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>49.05</v>
+        <v>47.95</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -3712,13 +3712,13 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>49.41</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -3727,13 +3727,13 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>50.03</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -3742,13 +3742,13 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>49.88</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -3757,13 +3757,13 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>49.73</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -3772,13 +3772,13 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>50.23</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -3787,13 +3787,13 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>49.88</v>
+        <v>49.41</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>49.78</v>
+        <v>50.03</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -3817,13 +3817,13 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>49.2</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -3832,13 +3832,13 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>48.9</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -3847,13 +3847,13 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>51.9</v>
+        <v>50.23</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -3862,13 +3862,13 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>51.46</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -3877,13 +3877,13 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>50.03</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -3892,13 +3892,13 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>48.66</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -3907,13 +3907,13 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>48.38</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -3922,13 +3922,13 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>47.52</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -3937,13 +3937,13 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>48.22</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -3952,13 +3952,13 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>48.33</v>
+        <v>50.03</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -3967,13 +3967,13 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>48.82</v>
+        <v>48.66</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -3982,13 +3982,13 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>48.95</v>
+        <v>48.38</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -3997,13 +3997,13 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>48.22</v>
+        <v>47.52</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -4012,13 +4012,13 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>48.75</v>
+        <v>48.22</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -4027,13 +4027,13 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>49.78</v>
+        <v>48.33</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -4042,13 +4042,13 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>49.23</v>
+        <v>48.82</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -4057,13 +4057,13 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>49.17</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -4072,13 +4072,13 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>47.85</v>
+        <v>48.22</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -4087,13 +4087,13 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>47.78</v>
+        <v>48.75</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -4102,13 +4102,13 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>47.83</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -4117,13 +4117,13 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>47.91</v>
+        <v>49.23</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -4132,13 +4132,13 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>47.73</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -4147,13 +4147,13 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>47.54</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -4162,13 +4162,13 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>46.72</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -4177,13 +4177,13 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>47.16</v>
+        <v>47.83</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -4192,13 +4192,13 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>46.15</v>
+        <v>47.91</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -4207,13 +4207,13 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>46.11</v>
+        <v>47.73</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -4222,13 +4222,13 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>44.82</v>
+        <v>47.54</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -4237,13 +4237,13 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>45.02</v>
+        <v>46.72</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -4252,13 +4252,13 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>45.96</v>
+        <v>47.16</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -4267,13 +4267,13 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>47.35</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -4282,13 +4282,13 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>48.65</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -4297,13 +4297,13 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>47.87</v>
+        <v>44.82</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -4312,13 +4312,13 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>46</v>
+        <v>45.02</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -4327,13 +4327,13 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>46.11</v>
+        <v>45.96</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>45.42</v>
+        <v>47.35</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -4357,13 +4357,13 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>44.2</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -4372,13 +4372,13 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>43.82</v>
+        <v>47.87</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -4387,13 +4387,13 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>43.48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -4402,13 +4402,13 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>43.28</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -4417,13 +4417,13 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>43.7</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -4432,13 +4432,13 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>43.32</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -4447,13 +4447,13 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>43.28</v>
+        <v>43.82</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -4462,13 +4462,13 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>42.9</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -4477,13 +4477,13 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>42.51</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -4492,13 +4492,13 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>42.36</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -4507,13 +4507,13 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>42.65</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -4522,13 +4522,13 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>42.85</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -4537,13 +4537,13 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>43.04</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -4552,13 +4552,13 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>43.92</v>
+        <v>42.51</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -4567,13 +4567,13 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>43.52</v>
+        <v>42.36</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -4582,13 +4582,13 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>43.37</v>
+        <v>42.65</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -4597,13 +4597,13 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>43.24</v>
+        <v>42.85</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -4612,13 +4612,13 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>43.99</v>
+        <v>43.04</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -4627,13 +4627,13 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>44.52</v>
+        <v>43.92</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -4642,13 +4642,13 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>45.66</v>
+        <v>43.52</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -4657,13 +4657,13 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>45.78</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -4672,13 +4672,13 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>46.1</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -4687,13 +4687,13 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>46.42</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -4702,13 +4702,13 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>47.21</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>47.44</v>
+        <v>45.66</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -4732,13 +4732,13 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>46.5</v>
+        <v>45.78</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -4747,13 +4747,13 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>47.21</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -4762,13 +4762,13 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>46.08</v>
+        <v>46.42</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -4777,13 +4777,13 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>46.21</v>
+        <v>47.21</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -4792,13 +4792,13 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>45.72</v>
+        <v>47.44</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -4807,13 +4807,13 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>46.29</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -4822,13 +4822,13 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>45.9</v>
+        <v>47.21</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -4837,13 +4837,13 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>46.05</v>
+        <v>46.08</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -4852,13 +4852,13 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>45.73</v>
+        <v>46.21</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -4867,13 +4867,13 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>45.31</v>
+        <v>45.72</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -4882,13 +4882,13 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>45.75</v>
+        <v>46.29</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -4897,13 +4897,13 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>46.37</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -4912,13 +4912,13 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>45.77</v>
+        <v>46.05</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -4927,13 +4927,13 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>45.1</v>
+        <v>45.73</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -4942,13 +4942,13 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>44.97</v>
+        <v>45.31</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -4957,13 +4957,13 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>45.11</v>
+        <v>45.75</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -4972,13 +4972,13 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>44.88</v>
+        <v>46.37</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -4987,13 +4987,13 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>45.06</v>
+        <v>45.77</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>44.73</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -5017,13 +5017,13 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>44.3</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>45.15</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -5047,13 +5047,13 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>45.27</v>
+        <v>44.88</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>45.03</v>
+        <v>45.06</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -5077,13 +5077,13 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>45.99</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -5092,13 +5092,13 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>46.22</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -5107,13 +5107,13 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>46.06</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -5122,13 +5122,13 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>45.62</v>
+        <v>45.27</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -5137,13 +5137,13 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>43.48</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -5152,13 +5152,13 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>42.45</v>
+        <v>45.99</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -5167,13 +5167,13 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>42.17</v>
+        <v>46.22</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -5182,13 +5182,13 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>41.34</v>
+        <v>46.06</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -5197,13 +5197,13 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>40.87</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -5212,13 +5212,13 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>41.09</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -5227,13 +5227,13 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>41.32</v>
+        <v>42.45</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -5242,13 +5242,13 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>41.19</v>
+        <v>42.17</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -5257,13 +5257,13 @@
         </is>
       </c>
       <c r="C322" t="n">
-        <v>40.94</v>
+        <v>41.34</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -5272,13 +5272,13 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>40.94</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2024-12-24</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -5287,13 +5287,13 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>41.38</v>
+        <v>41.09</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -5302,13 +5302,13 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>41.62</v>
+        <v>41.32</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -5317,13 +5317,13 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>40.87</v>
+        <v>41.19</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>41.15</v>
+        <v>40.94</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -5347,13 +5347,13 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>40.92</v>
+        <v>40.94</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>41.73</v>
+        <v>41.38</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -5377,13 +5377,13 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>42.72</v>
+        <v>41.62</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -5392,13 +5392,13 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>43.49</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -5407,13 +5407,13 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>43.53</v>
+        <v>41.15</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -5422,13 +5422,13 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>43.26</v>
+        <v>40.92</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -5437,13 +5437,13 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>43.46</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -5452,13 +5452,13 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>43.52</v>
+        <v>42.72</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -5467,13 +5467,13 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>43.58</v>
+        <v>43.49</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -5482,13 +5482,13 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>42.89</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -5497,13 +5497,13 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>42.12</v>
+        <v>43.26</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -5512,13 +5512,13 @@
         </is>
       </c>
       <c r="C339" t="n">
-        <v>42.67</v>
+        <v>43.46</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -5527,13 +5527,13 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>42.3</v>
+        <v>43.52</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -5542,13 +5542,13 @@
         </is>
       </c>
       <c r="C341" t="n">
-        <v>42.39</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -5557,13 +5557,13 @@
         </is>
       </c>
       <c r="C342" t="n">
-        <v>41.84</v>
+        <v>42.89</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -5572,13 +5572,13 @@
         </is>
       </c>
       <c r="C343" t="n">
-        <v>43.17</v>
+        <v>42.12</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -5587,13 +5587,13 @@
         </is>
       </c>
       <c r="C344" t="n">
-        <v>42.27</v>
+        <v>42.67</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -5602,13 +5602,13 @@
         </is>
       </c>
       <c r="C345" t="n">
-        <v>42.78</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -5617,13 +5617,13 @@
         </is>
       </c>
       <c r="C346" t="n">
-        <v>43.09</v>
+        <v>42.39</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>43.95</v>
+        <v>41.84</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -5647,13 +5647,13 @@
         </is>
       </c>
       <c r="C348" t="n">
-        <v>44.91</v>
+        <v>43.17</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -5662,13 +5662,13 @@
         </is>
       </c>
       <c r="C349" t="n">
-        <v>45.32</v>
+        <v>42.27</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -5677,13 +5677,13 @@
         </is>
       </c>
       <c r="C350" t="n">
-        <v>45.24</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -5692,13 +5692,13 @@
         </is>
       </c>
       <c r="C351" t="n">
-        <v>44.48</v>
+        <v>43.09</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -5707,13 +5707,13 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>45.38</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -5722,13 +5722,13 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>46.24</v>
+        <v>44.91</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -5737,13 +5737,13 @@
         </is>
       </c>
       <c r="C354" t="n">
-        <v>47.78</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -5752,13 +5752,13 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>48.04</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -5767,13 +5767,13 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>47.49</v>
+        <v>44.48</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -5782,13 +5782,13 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>45.65</v>
+        <v>45.38</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>45.01</v>
+        <v>46.24</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>45.36</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -5827,13 +5827,13 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>45.49</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -5842,13 +5842,13 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>44.54</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -5857,13 +5857,13 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>43.62</v>
+        <v>45.65</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -5872,13 +5872,13 @@
         </is>
       </c>
       <c r="C363" t="n">
-        <v>42.78</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -5887,13 +5887,13 @@
         </is>
       </c>
       <c r="C364" t="n">
-        <v>42.73</v>
+        <v>45.36</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -5902,13 +5902,13 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>43.65</v>
+        <v>45.49</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -5917,13 +5917,13 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>43.48</v>
+        <v>44.54</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -5932,13 +5932,13 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>42.77</v>
+        <v>43.62</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -5947,13 +5947,13 @@
         </is>
       </c>
       <c r="C368" t="n">
-        <v>42.86</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -5962,13 +5962,13 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>41.8</v>
+        <v>42.73</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -5977,13 +5977,13 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>41.24</v>
+        <v>43.65</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -5992,13 +5992,13 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>41.92</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -6007,13 +6007,13 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>41.59</v>
+        <v>42.77</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -6022,13 +6022,13 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>42.03</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -6037,13 +6037,13 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>42.03</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -6052,13 +6052,13 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>43.28</v>
+        <v>41.24</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -6067,13 +6067,13 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>43.74</v>
+        <v>41.92</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -6082,13 +6082,13 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>43.16</v>
+        <v>41.59</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -6097,13 +6097,13 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>43.22</v>
+        <v>42.03</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -6112,13 +6112,13 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>44.73</v>
+        <v>42.03</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -6127,13 +6127,13 @@
         </is>
       </c>
       <c r="C380" t="n">
-        <v>44.08</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -6142,13 +6142,13 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>44.43</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -6157,13 +6157,13 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>43.57</v>
+        <v>43.16</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -6172,13 +6172,13 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>43.08</v>
+        <v>43.22</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -6187,13 +6187,13 @@
         </is>
       </c>
       <c r="C384" t="n">
-        <v>43.05</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -6202,13 +6202,13 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>42.78</v>
+        <v>44.08</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -6217,13 +6217,13 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>43.53</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -6232,13 +6232,13 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>43.71</v>
+        <v>43.57</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -6247,13 +6247,13 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>43.14</v>
+        <v>43.08</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -6262,13 +6262,13 @@
         </is>
       </c>
       <c r="C389" t="n">
-        <v>42.09</v>
+        <v>43.05</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -6277,13 +6277,13 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>41.73</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -6292,13 +6292,13 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>41.43</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -6307,13 +6307,13 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>41.17</v>
+        <v>43.71</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -6322,13 +6322,13 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>40.69</v>
+        <v>43.14</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -6337,13 +6337,13 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>40.11</v>
+        <v>42.09</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -6352,13 +6352,13 @@
         </is>
       </c>
       <c r="C395" t="n">
-        <v>40.12</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -6367,13 +6367,13 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>40.75</v>
+        <v>41.43</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -6382,13 +6382,13 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>40.39</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -6397,13 +6397,13 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>40.6</v>
+        <v>40.69</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -6412,13 +6412,13 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>41.29</v>
+        <v>40.11</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -6427,13 +6427,13 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>40.49</v>
+        <v>40.12</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -6442,13 +6442,13 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>41.62</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -6457,13 +6457,13 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>40.98</v>
+        <v>40.39</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -6472,13 +6472,13 @@
         </is>
       </c>
       <c r="C403" t="n">
-        <v>41.5</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -6487,13 +6487,13 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>42.26</v>
+        <v>41.29</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -6502,13 +6502,13 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>42.24</v>
+        <v>40.49</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -6517,13 +6517,13 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>41.21</v>
+        <v>41.62</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -6532,13 +6532,13 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>40.93</v>
+        <v>40.98</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>40.83</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -6562,13 +6562,13 @@
         </is>
       </c>
       <c r="C409" t="n">
-        <v>40.51</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -6577,13 +6577,13 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>39.52</v>
+        <v>42.24</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -6592,13 +6592,13 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>40.05</v>
+        <v>41.21</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -6607,13 +6607,13 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>39.68</v>
+        <v>40.93</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -6622,13 +6622,13 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>39.76</v>
+        <v>40.83</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -6637,13 +6637,13 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>39.55</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -6652,13 +6652,13 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>39.29</v>
+        <v>39.52</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -6667,13 +6667,13 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>39.58</v>
+        <v>40.05</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -6682,13 +6682,13 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>39.89</v>
+        <v>39.68</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -6697,13 +6697,13 @@
         </is>
       </c>
       <c r="C418" t="n">
-        <v>40.84</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -6712,13 +6712,13 @@
         </is>
       </c>
       <c r="C419" t="n">
-        <v>40.75</v>
+        <v>39.55</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -6727,13 +6727,13 @@
         </is>
       </c>
       <c r="C420" t="n">
-        <v>40.68</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -6742,13 +6742,13 @@
         </is>
       </c>
       <c r="C421" t="n">
-        <v>40.51</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -6757,13 +6757,13 @@
         </is>
       </c>
       <c r="C422" t="n">
-        <v>40.16</v>
+        <v>39.89</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -6772,13 +6772,13 @@
         </is>
       </c>
       <c r="C423" t="n">
-        <v>40.25</v>
+        <v>40.84</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -6787,13 +6787,13 @@
         </is>
       </c>
       <c r="C424" t="n">
-        <v>40.91</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -6802,13 +6802,13 @@
         </is>
       </c>
       <c r="C425" t="n">
-        <v>41.18</v>
+        <v>40.68</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -6817,13 +6817,13 @@
         </is>
       </c>
       <c r="C426" t="n">
-        <v>41.72</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -6832,13 +6832,13 @@
         </is>
       </c>
       <c r="C427" t="n">
-        <v>41.2</v>
+        <v>40.16</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="C428" t="n">
-        <v>41.67</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -6862,13 +6862,13 @@
         </is>
       </c>
       <c r="C429" t="n">
-        <v>41.34</v>
+        <v>40.91</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -6877,13 +6877,13 @@
         </is>
       </c>
       <c r="C430" t="n">
-        <v>42.82</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -6892,13 +6892,13 @@
         </is>
       </c>
       <c r="C431" t="n">
-        <v>42.57</v>
+        <v>41.72</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -6907,13 +6907,13 @@
         </is>
       </c>
       <c r="C432" t="n">
-        <v>43.28</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -6922,13 +6922,13 @@
         </is>
       </c>
       <c r="C433" t="n">
-        <v>42.86</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -6937,13 +6937,13 @@
         </is>
       </c>
       <c r="C434" t="n">
-        <v>41.96</v>
+        <v>41.34</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -6952,13 +6952,13 @@
         </is>
       </c>
       <c r="C435" t="n">
-        <v>42.63</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -6967,13 +6967,13 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>42.6</v>
+        <v>42.57</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -6982,13 +6982,13 @@
         </is>
       </c>
       <c r="C437" t="n">
-        <v>43.39</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -6997,13 +6997,13 @@
         </is>
       </c>
       <c r="C438" t="n">
-        <v>43.49</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -7012,13 +7012,13 @@
         </is>
       </c>
       <c r="C439" t="n">
-        <v>44.6</v>
+        <v>41.96</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -7027,13 +7027,13 @@
         </is>
       </c>
       <c r="C440" t="n">
-        <v>45.01</v>
+        <v>42.63</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -7042,13 +7042,13 @@
         </is>
       </c>
       <c r="C441" t="n">
-        <v>44.73</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -7057,13 +7057,13 @@
         </is>
       </c>
       <c r="C442" t="n">
-        <v>45.87</v>
+        <v>43.39</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -7072,13 +7072,13 @@
         </is>
       </c>
       <c r="C443" t="n">
-        <v>46.97</v>
+        <v>43.49</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -7087,13 +7087,13 @@
         </is>
       </c>
       <c r="C444" t="n">
-        <v>47.02</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -7102,13 +7102,13 @@
         </is>
       </c>
       <c r="C445" t="n">
-        <v>46.75</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -7117,13 +7117,13 @@
         </is>
       </c>
       <c r="C446" t="n">
-        <v>45.79</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -7132,13 +7132,13 @@
         </is>
       </c>
       <c r="C447" t="n">
-        <v>44.84</v>
+        <v>45.87</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -7147,13 +7147,13 @@
         </is>
       </c>
       <c r="C448" t="n">
-        <v>43.13</v>
+        <v>46.97</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -7162,13 +7162,13 @@
         </is>
       </c>
       <c r="C449" t="n">
-        <v>42.97</v>
+        <v>47.02</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -7177,13 +7177,13 @@
         </is>
       </c>
       <c r="C450" t="n">
-        <v>43.37</v>
+        <v>46.75</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -7192,13 +7192,13 @@
         </is>
       </c>
       <c r="C451" t="n">
-        <v>42.71</v>
+        <v>45.79</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="C452" t="n">
-        <v>43.35</v>
+        <v>44.84</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -7222,13 +7222,13 @@
         </is>
       </c>
       <c r="C453" t="n">
-        <v>43.58</v>
+        <v>43.13</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -7237,13 +7237,13 @@
         </is>
       </c>
       <c r="C454" t="n">
-        <v>43.59</v>
+        <v>42.97</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="C455" t="n">
-        <v>44.01</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -7267,13 +7267,13 @@
         </is>
       </c>
       <c r="C456" t="n">
-        <v>43.56</v>
+        <v>42.71</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -7282,13 +7282,13 @@
         </is>
       </c>
       <c r="C457" t="n">
-        <v>43.53</v>
+        <v>43.35</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -7297,13 +7297,13 @@
         </is>
       </c>
       <c r="C458" t="n">
-        <v>43.76</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -7312,13 +7312,13 @@
         </is>
       </c>
       <c r="C459" t="n">
-        <v>43.87</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -7327,13 +7327,13 @@
         </is>
       </c>
       <c r="C460" t="n">
-        <v>43.76</v>
+        <v>44.01</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -7342,13 +7342,13 @@
         </is>
       </c>
       <c r="C461" t="n">
-        <v>43.98</v>
+        <v>43.56</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -7357,13 +7357,13 @@
         </is>
       </c>
       <c r="C462" t="n">
-        <v>44.29</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -7372,13 +7372,13 @@
         </is>
       </c>
       <c r="C463" t="n">
-        <v>44.83</v>
+        <v>43.76</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -7387,13 +7387,13 @@
         </is>
       </c>
       <c r="C464" t="n">
-        <v>43.88</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -7402,13 +7402,13 @@
         </is>
       </c>
       <c r="C465" t="n">
-        <v>44.2</v>
+        <v>43.76</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -7417,13 +7417,13 @@
         </is>
       </c>
       <c r="C466" t="n">
-        <v>44.63</v>
+        <v>43.98</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -7432,13 +7432,13 @@
         </is>
       </c>
       <c r="C467" t="n">
-        <v>45.81</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -7447,13 +7447,13 @@
         </is>
       </c>
       <c r="C468" t="n">
-        <v>45.93</v>
+        <v>44.83</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="C469" t="n">
-        <v>46.11</v>
+        <v>43.88</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -7477,13 +7477,13 @@
         </is>
       </c>
       <c r="C470" t="n">
-        <v>45.74</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -7492,13 +7492,13 @@
         </is>
       </c>
       <c r="C471" t="n">
-        <v>45.32</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -7507,13 +7507,13 @@
         </is>
       </c>
       <c r="C472" t="n">
-        <v>45.96</v>
+        <v>45.81</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -7522,13 +7522,13 @@
         </is>
       </c>
       <c r="C473" t="n">
-        <v>46.2</v>
+        <v>45.93</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -7537,13 +7537,13 @@
         </is>
       </c>
       <c r="C474" t="n">
-        <v>46.37</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -7552,13 +7552,13 @@
         </is>
       </c>
       <c r="C475" t="n">
-        <v>46.6</v>
+        <v>45.74</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -7567,13 +7567,13 @@
         </is>
       </c>
       <c r="C476" t="n">
-        <v>45.89</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -7582,13 +7582,13 @@
         </is>
       </c>
       <c r="C477" t="n">
-        <v>45.45</v>
+        <v>45.96</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -7597,13 +7597,13 @@
         </is>
       </c>
       <c r="C478" t="n">
-        <v>44.82</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -7612,13 +7612,13 @@
         </is>
       </c>
       <c r="C479" t="n">
-        <v>44.7</v>
+        <v>46.37</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -7627,13 +7627,13 @@
         </is>
       </c>
       <c r="C480" t="n">
-        <v>46.01</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -7642,13 +7642,13 @@
         </is>
       </c>
       <c r="C481" t="n">
-        <v>45.24</v>
+        <v>45.89</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -7657,13 +7657,13 @@
         </is>
       </c>
       <c r="C482" t="n">
-        <v>44.2</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -7672,13 +7672,13 @@
         </is>
       </c>
       <c r="C483" t="n">
-        <v>44.8</v>
+        <v>44.82</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -7687,13 +7687,13 @@
         </is>
       </c>
       <c r="C484" t="n">
-        <v>45.29</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -7702,13 +7702,13 @@
         </is>
       </c>
       <c r="C485" t="n">
-        <v>44.66</v>
+        <v>46.01</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -7717,13 +7717,13 @@
         </is>
       </c>
       <c r="C486" t="n">
-        <v>44.34</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -7732,13 +7732,13 @@
         </is>
       </c>
       <c r="C487" t="n">
-        <v>44.43</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -7747,13 +7747,13 @@
         </is>
       </c>
       <c r="C488" t="n">
-        <v>44.49</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -7762,13 +7762,13 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>44.32</v>
+        <v>45.29</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -7777,13 +7777,13 @@
         </is>
       </c>
       <c r="C490" t="n">
-        <v>45.01</v>
+        <v>44.66</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -7792,13 +7792,13 @@
         </is>
       </c>
       <c r="C491" t="n">
-        <v>45.94</v>
+        <v>44.34</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="C492" t="n">
-        <v>45.67</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -7822,13 +7822,13 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>45.58</v>
+        <v>44.49</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -7837,13 +7837,13 @@
         </is>
       </c>
       <c r="C494" t="n">
-        <v>45.95</v>
+        <v>44.32</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -7852,13 +7852,13 @@
         </is>
       </c>
       <c r="C495" t="n">
-        <v>45.8</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -7867,13 +7867,13 @@
         </is>
       </c>
       <c r="C496" t="n">
-        <v>45.14</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -7882,13 +7882,13 @@
         </is>
       </c>
       <c r="C497" t="n">
-        <v>44.97</v>
+        <v>45.67</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -7897,13 +7897,13 @@
         </is>
       </c>
       <c r="C498" t="n">
-        <v>45.19</v>
+        <v>45.58</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -7912,13 +7912,13 @@
         </is>
       </c>
       <c r="C499" t="n">
-        <v>45.34</v>
+        <v>45.95</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -7927,13 +7927,13 @@
         </is>
       </c>
       <c r="C500" t="n">
-        <v>45.6</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -7942,13 +7942,13 @@
         </is>
       </c>
       <c r="C501" t="n">
-        <v>45.97</v>
+        <v>45.14</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -7957,13 +7957,13 @@
         </is>
       </c>
       <c r="C502" t="n">
-        <v>45.91</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -7972,13 +7972,13 @@
         </is>
       </c>
       <c r="C503" t="n">
-        <v>46.95</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -7987,13 +7987,13 @@
         </is>
       </c>
       <c r="C504" t="n">
-        <v>46.91</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -8002,13 +8002,13 @@
         </is>
       </c>
       <c r="C505" t="n">
-        <v>47.23</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -8017,13 +8017,13 @@
         </is>
       </c>
       <c r="C506" t="n">
-        <v>47.84</v>
+        <v>45.97</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -8032,13 +8032,13 @@
         </is>
       </c>
       <c r="C507" t="n">
-        <v>47.38</v>
+        <v>45.91</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -8047,13 +8047,13 @@
         </is>
       </c>
       <c r="C508" t="n">
-        <v>48</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -8062,13 +8062,13 @@
         </is>
       </c>
       <c r="C509" t="n">
-        <v>47.67</v>
+        <v>46.91</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -8077,13 +8077,13 @@
         </is>
       </c>
       <c r="C510" t="n">
-        <v>47.12</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -8092,13 +8092,13 @@
         </is>
       </c>
       <c r="C511" t="n">
-        <v>47.14</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -8107,13 +8107,13 @@
         </is>
       </c>
       <c r="C512" t="n">
-        <v>46.67</v>
+        <v>47.38</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -8122,13 +8122,13 @@
         </is>
       </c>
       <c r="C513" t="n">
-        <v>47.46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -8137,13 +8137,13 @@
         </is>
       </c>
       <c r="C514" t="n">
-        <v>47.71</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -8152,13 +8152,13 @@
         </is>
       </c>
       <c r="C515" t="n">
-        <v>46.65</v>
+        <v>47.12</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -8167,13 +8167,13 @@
         </is>
       </c>
       <c r="C516" t="n">
-        <v>47.72</v>
+        <v>47.14</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -8182,13 +8182,13 @@
         </is>
       </c>
       <c r="C517" t="n">
-        <v>47.89</v>
+        <v>46.67</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -8197,13 +8197,13 @@
         </is>
       </c>
       <c r="C518" t="n">
-        <v>47.23</v>
+        <v>47.46</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -8212,13 +8212,13 @@
         </is>
       </c>
       <c r="C519" t="n">
-        <v>47.63</v>
+        <v>47.71</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -8227,13 +8227,13 @@
         </is>
       </c>
       <c r="C520" t="n">
-        <v>48.16</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -8242,13 +8242,13 @@
         </is>
       </c>
       <c r="C521" t="n">
-        <v>47.08</v>
+        <v>47.72</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -8257,13 +8257,13 @@
         </is>
       </c>
       <c r="C522" t="n">
-        <v>47.34</v>
+        <v>47.89</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -8272,13 +8272,13 @@
         </is>
       </c>
       <c r="C523" t="n">
-        <v>46.61</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="C524" t="n">
-        <v>45.84</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -8302,13 +8302,13 @@
         </is>
       </c>
       <c r="C525" t="n">
-        <v>45.28</v>
+        <v>48.16</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -8317,13 +8317,13 @@
         </is>
       </c>
       <c r="C526" t="n">
-        <v>45.23</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -8332,13 +8332,13 @@
         </is>
       </c>
       <c r="C527" t="n">
-        <v>44.51</v>
+        <v>47.34</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -8347,13 +8347,13 @@
         </is>
       </c>
       <c r="C528" t="n">
-        <v>44.37</v>
+        <v>46.61</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -8362,13 +8362,13 @@
         </is>
       </c>
       <c r="C529" t="n">
-        <v>44.55</v>
+        <v>45.84</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="C530" t="n">
-        <v>44.45</v>
+        <v>45.28</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -8392,13 +8392,13 @@
         </is>
       </c>
       <c r="C531" t="n">
-        <v>44.56</v>
+        <v>45.23</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -8407,13 +8407,13 @@
         </is>
       </c>
       <c r="C532" t="n">
-        <v>44.63</v>
+        <v>44.51</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -8422,13 +8422,13 @@
         </is>
       </c>
       <c r="C533" t="n">
-        <v>44.69</v>
+        <v>44.37</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>2024-02-26</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -8437,13 +8437,13 @@
         </is>
       </c>
       <c r="C534" t="n">
-        <v>44.2</v>
+        <v>44.55</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -8452,13 +8452,13 @@
         </is>
       </c>
       <c r="C535" t="n">
-        <v>43.78</v>
+        <v>44.45</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -8467,13 +8467,13 @@
         </is>
       </c>
       <c r="C536" t="n">
-        <v>43.99</v>
+        <v>44.56</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -8482,13 +8482,13 @@
         </is>
       </c>
       <c r="C537" t="n">
-        <v>44</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -8497,13 +8497,13 @@
         </is>
       </c>
       <c r="C538" t="n">
-        <v>44.35</v>
+        <v>44.69</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -8512,13 +8512,13 @@
         </is>
       </c>
       <c r="C539" t="n">
-        <v>44.52</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -8527,13 +8527,13 @@
         </is>
       </c>
       <c r="C540" t="n">
-        <v>44.68</v>
+        <v>43.78</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-22</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -8542,13 +8542,13 @@
         </is>
       </c>
       <c r="C541" t="n">
-        <v>45.07</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -8557,13 +8557,13 @@
         </is>
       </c>
       <c r="C542" t="n">
-        <v>45.62</v>
+        <v>44</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -8572,13 +8572,13 @@
         </is>
       </c>
       <c r="C543" t="n">
-        <v>45.33</v>
+        <v>44.35</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -8587,13 +8587,13 @@
         </is>
       </c>
       <c r="C544" t="n">
-        <v>45.64</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -8602,13 +8602,13 @@
         </is>
       </c>
       <c r="C545" t="n">
-        <v>45.59</v>
+        <v>44.68</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -8617,13 +8617,13 @@
         </is>
       </c>
       <c r="C546" t="n">
-        <v>44.61</v>
+        <v>45.07</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="C547" t="n">
-        <v>44.2</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -8647,13 +8647,13 @@
         </is>
       </c>
       <c r="C548" t="n">
-        <v>43.73</v>
+        <v>45.33</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-09</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -8662,13 +8662,13 @@
         </is>
       </c>
       <c r="C549" t="n">
-        <v>43.66</v>
+        <v>45.64</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -8677,13 +8677,13 @@
         </is>
       </c>
       <c r="C550" t="n">
-        <v>44.07</v>
+        <v>45.59</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -8692,13 +8692,13 @@
         </is>
       </c>
       <c r="C551" t="n">
-        <v>44.66</v>
+        <v>44.61</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="C552" t="n">
-        <v>44.75</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -8722,13 +8722,13 @@
         </is>
       </c>
       <c r="C553" t="n">
-        <v>44.73</v>
+        <v>43.73</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -8737,13 +8737,13 @@
         </is>
       </c>
       <c r="C554" t="n">
-        <v>45.37</v>
+        <v>43.66</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -8752,13 +8752,13 @@
         </is>
       </c>
       <c r="C555" t="n">
-        <v>45.34</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -8767,13 +8767,13 @@
         </is>
       </c>
       <c r="C556" t="n">
-        <v>45.57</v>
+        <v>44.66</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>2024-01-23</t>
+          <t>2024-01-30</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -8782,13 +8782,13 @@
         </is>
       </c>
       <c r="C557" t="n">
-        <v>45.97</v>
+        <v>44.75</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -8797,13 +8797,13 @@
         </is>
       </c>
       <c r="C558" t="n">
-        <v>45.94</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>2024-01-19</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -8812,13 +8812,13 @@
         </is>
       </c>
       <c r="C559" t="n">
-        <v>45.19</v>
+        <v>45.37</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -8827,13 +8827,13 @@
         </is>
       </c>
       <c r="C560" t="n">
-        <v>45.44</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -8842,13 +8842,13 @@
         </is>
       </c>
       <c r="C561" t="n">
-        <v>45.42</v>
+        <v>45.57</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-01-23</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -8857,13 +8857,13 @@
         </is>
       </c>
       <c r="C562" t="n">
-        <v>45.42</v>
+        <v>45.97</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>2024-01-22</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -8872,13 +8872,13 @@
         </is>
       </c>
       <c r="C563" t="n">
-        <v>46.13</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>2024-01-11</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -8887,13 +8887,13 @@
         </is>
       </c>
       <c r="C564" t="n">
-        <v>46.6</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -8902,13 +8902,13 @@
         </is>
       </c>
       <c r="C565" t="n">
-        <v>46.28</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -8917,13 +8917,13 @@
         </is>
       </c>
       <c r="C566" t="n">
-        <v>46.63</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>2024-01-08</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -8932,13 +8932,13 @@
         </is>
       </c>
       <c r="C567" t="n">
-        <v>45.95</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -8947,13 +8947,13 @@
         </is>
       </c>
       <c r="C568" t="n">
-        <v>45.99</v>
+        <v>46.13</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>2024-01-04</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -8962,13 +8962,13 @@
         </is>
       </c>
       <c r="C569" t="n">
-        <v>46.36</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>2024-01-03</t>
+          <t>2024-01-10</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -8977,13 +8977,13 @@
         </is>
       </c>
       <c r="C570" t="n">
-        <v>46.7</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -8992,13 +8992,13 @@
         </is>
       </c>
       <c r="C571" t="n">
-        <v>46.66</v>
+        <v>46.63</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>2023-12-29</t>
+          <t>2024-01-08</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -9007,13 +9007,13 @@
         </is>
       </c>
       <c r="C572" t="n">
-        <v>46.4</v>
+        <v>45.95</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>2023-12-28</t>
+          <t>2024-01-05</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -9022,13 +9022,13 @@
         </is>
       </c>
       <c r="C573" t="n">
-        <v>46.26</v>
+        <v>45.99</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>2023-12-27</t>
+          <t>2024-01-04</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -9037,13 +9037,13 @@
         </is>
       </c>
       <c r="C574" t="n">
-        <v>46.98</v>
+        <v>46.36</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>2023-12-26</t>
+          <t>2024-01-03</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -9052,13 +9052,13 @@
         </is>
       </c>
       <c r="C575" t="n">
-        <v>47.03</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2024-01-02</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -9067,13 +9067,13 @@
         </is>
       </c>
       <c r="C576" t="n">
-        <v>47.28</v>
+        <v>46.66</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2023-12-29</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -9082,13 +9082,13 @@
         </is>
       </c>
       <c r="C577" t="n">
-        <v>47.36</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2023-12-28</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -9097,13 +9097,13 @@
         </is>
       </c>
       <c r="C578" t="n">
-        <v>48.24</v>
+        <v>46.26</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-27</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -9112,13 +9112,13 @@
         </is>
       </c>
       <c r="C579" t="n">
-        <v>48.29</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-26</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -9127,13 +9127,13 @@
         </is>
       </c>
       <c r="C580" t="n">
-        <v>48.22</v>
+        <v>47.03</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2023-12-22</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -9142,21 +9142,96 @@
         </is>
       </c>
       <c r="C581" t="n">
-        <v>47.59</v>
+        <v>47.28</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
+          <t>2023-12-21</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C582" t="n">
+        <v>47.36</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C583" t="n">
+        <v>48.24</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C584" t="n">
+        <v>48.29</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C585" t="n">
+        <v>48.22</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2023-12-15</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C586" t="n">
+        <v>47.59</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
           <t>2023-12-14</t>
         </is>
       </c>
-      <c r="B582" t="inlineStr">
-        <is>
-          <t>BOK26</t>
-        </is>
-      </c>
-      <c r="C582" t="n">
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C587" t="n">
         <v>47.31</v>
       </c>
     </row>

--- a/data/lseg_excel/BOK26.xlsx
+++ b/data/lseg_excel/BOK26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C587"/>
+  <dimension ref="A1:C603"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>66.90000000000001</v>
+        <v>75.09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>66.44</v>
+        <v>76.51000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>66.5</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -502,13 +502,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>67.09</v>
+        <v>78.02</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>67.7</v>
+        <v>76.65000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>67.42</v>
+        <v>76.36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -547,13 +547,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>69.72</v>
+        <v>75.31</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -562,13 +562,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>69.95</v>
+        <v>73.38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>68.94</v>
+        <v>72.26000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>68.94</v>
+        <v>71.91</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>67.11</v>
+        <v>71.66</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>68.88</v>
+        <v>71.68000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -637,13 +637,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>68.47</v>
+        <v>72.14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -652,13 +652,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>67.41</v>
+        <v>69.63</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -667,13 +667,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>68.02</v>
+        <v>68.16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -682,13 +682,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>67.09999999999999</v>
+        <v>69.33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -697,13 +697,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>65.73</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -712,13 +712,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>65.58</v>
+        <v>66.44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>65.51000000000001</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -742,13 +742,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>65.41</v>
+        <v>67.09</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>65.53</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -772,13 +772,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>65.97</v>
+        <v>67.42</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>63.94</v>
+        <v>69.72</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -802,13 +802,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>67.44</v>
+        <v>69.95</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>67.42</v>
+        <v>68.94</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>67.16</v>
+        <v>68.94</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -847,13 +847,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>65.62</v>
+        <v>67.11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>66.09999999999999</v>
+        <v>68.88</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -877,13 +877,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>66.58</v>
+        <v>68.47</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -892,13 +892,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>65.7</v>
+        <v>67.41</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>63.59</v>
+        <v>68.02</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -922,13 +922,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>62.82</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -937,13 +937,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>62.74</v>
+        <v>65.73</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -952,13 +952,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>61.85</v>
+        <v>65.58</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>61.76</v>
+        <v>65.51000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>60.67</v>
+        <v>65.41</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>60.5</v>
+        <v>65.53</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>59.88</v>
+        <v>65.97</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1027,13 +1027,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>59.3</v>
+        <v>63.94</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1042,13 +1042,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>60.09</v>
+        <v>67.44</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>59.08</v>
+        <v>67.42</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>57.76</v>
+        <v>67.16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>57.47</v>
+        <v>65.62</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1102,13 +1102,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>57.91</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>57.5</v>
+        <v>66.58</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>57.74</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1147,13 +1147,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>57.17</v>
+        <v>63.59</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1162,13 +1162,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>55.84</v>
+        <v>62.82</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>56.17</v>
+        <v>62.74</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>56.18</v>
+        <v>61.85</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1207,13 +1207,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>55.03</v>
+        <v>61.76</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1222,13 +1222,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>53.74</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1237,13 +1237,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>54.06</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>54.58</v>
+        <v>59.88</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>54.85</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1282,13 +1282,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>54.95</v>
+        <v>60.09</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>54.42</v>
+        <v>59.08</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>54.52</v>
+        <v>57.76</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>54.33</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1342,13 +1342,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>54.54</v>
+        <v>57.91</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1357,13 +1357,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>53.11</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1372,13 +1372,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>53.15</v>
+        <v>57.74</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>53.47</v>
+        <v>57.17</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1402,13 +1402,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>51.5</v>
+        <v>55.84</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>51.69</v>
+        <v>56.17</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>50.77</v>
+        <v>56.18</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1447,13 +1447,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>50.2</v>
+        <v>55.03</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1462,13 +1462,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>49.97</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1477,13 +1477,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>49.84</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>49.95</v>
+        <v>54.58</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>50.41</v>
+        <v>54.85</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1522,13 +1522,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>49.83</v>
+        <v>54.95</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1537,13 +1537,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>49.09</v>
+        <v>54.42</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1552,13 +1552,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>49.94</v>
+        <v>54.52</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1567,13 +1567,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>49.8</v>
+        <v>54.33</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1582,13 +1582,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>49.73</v>
+        <v>54.54</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>50</v>
+        <v>53.11</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1612,13 +1612,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>49.28</v>
+        <v>53.15</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1627,13 +1627,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>49.58</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1642,13 +1642,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>48.92</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1657,13 +1657,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>49.1</v>
+        <v>51.69</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1672,13 +1672,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>49.53</v>
+        <v>50.77</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1687,13 +1687,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>49.4</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1702,13 +1702,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>50.45</v>
+        <v>49.97</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1717,13 +1717,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>51.03</v>
+        <v>49.84</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>51.68</v>
+        <v>49.95</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1747,13 +1747,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>51.96</v>
+        <v>50.41</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1762,13 +1762,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>51.88</v>
+        <v>49.83</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1777,13 +1777,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>52.04</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1792,13 +1792,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>52.54</v>
+        <v>49.94</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1807,13 +1807,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>52.63</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -1822,13 +1822,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>52.54</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>53.51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1852,13 +1852,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>53.16</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1867,13 +1867,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>52.84</v>
+        <v>49.58</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -1882,13 +1882,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>51.89</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1897,13 +1897,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>51.51</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>51.41</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -1927,13 +1927,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>51.47</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -1942,13 +1942,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>51.83</v>
+        <v>50.45</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -1957,13 +1957,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>52.3</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>53.35</v>
+        <v>51.68</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -1987,13 +1987,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>52.36</v>
+        <v>51.96</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2002,13 +2002,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>51.46</v>
+        <v>51.88</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>51.56</v>
+        <v>52.04</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2032,13 +2032,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>51.9</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2047,13 +2047,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>52.33</v>
+        <v>52.63</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2062,13 +2062,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>51.8</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>50.9</v>
+        <v>53.51</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2092,13 +2092,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>50.56</v>
+        <v>53.16</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2107,13 +2107,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>50.88</v>
+        <v>52.84</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2122,13 +2122,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>50.76</v>
+        <v>51.89</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2137,13 +2137,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>51.08</v>
+        <v>51.51</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2152,13 +2152,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>50</v>
+        <v>51.41</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2167,13 +2167,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>50.88</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2182,13 +2182,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>51.34</v>
+        <v>51.83</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2197,13 +2197,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>51.46</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2212,13 +2212,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>51.93</v>
+        <v>53.35</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2227,13 +2227,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>51.4</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2242,13 +2242,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>51.93</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2257,13 +2257,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>51.21</v>
+        <v>51.56</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2272,13 +2272,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>51.72</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>52.32</v>
+        <v>52.33</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2302,13 +2302,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>52.09</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2317,13 +2317,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>51.84</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2332,13 +2332,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>51.73</v>
+        <v>50.56</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>51.47</v>
+        <v>50.88</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2362,13 +2362,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>51.47</v>
+        <v>50.76</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>50.86</v>
+        <v>51.08</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -2392,13 +2392,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>51.84</v>
+        <v>50</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -2407,13 +2407,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>52.41</v>
+        <v>50.88</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -2422,13 +2422,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>51.89</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -2437,13 +2437,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>51.33</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -2452,13 +2452,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>51.02</v>
+        <v>51.93</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -2467,13 +2467,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>51.38</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -2482,13 +2482,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>51.34</v>
+        <v>51.93</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -2497,13 +2497,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>50.46</v>
+        <v>51.21</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -2512,13 +2512,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>50.74</v>
+        <v>51.72</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -2527,13 +2527,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>51.27</v>
+        <v>52.32</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>51.34</v>
+        <v>52.09</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -2557,13 +2557,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>50.92</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -2572,13 +2572,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>50.93</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -2587,13 +2587,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>50.7</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -2602,13 +2602,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>51.5</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -2617,13 +2617,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>52.03</v>
+        <v>50.86</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -2632,13 +2632,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>52.59</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>53.81</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -2662,13 +2662,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>52.98</v>
+        <v>51.89</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -2677,13 +2677,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>52.98</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -2692,13 +2692,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>52.41</v>
+        <v>51.02</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -2707,13 +2707,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>51.85</v>
+        <v>51.38</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -2722,13 +2722,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>51.41</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -2737,13 +2737,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>52.36</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -2752,13 +2752,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>52.02</v>
+        <v>50.74</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -2767,13 +2767,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>52.63</v>
+        <v>51.27</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -2782,13 +2782,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>52.54</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -2797,13 +2797,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>53.3</v>
+        <v>50.92</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -2812,13 +2812,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>52.79</v>
+        <v>50.93</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -2827,13 +2827,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>53.07</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -2842,13 +2842,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>53.82</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -2857,13 +2857,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>53.93</v>
+        <v>52.03</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -2872,13 +2872,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>55.12</v>
+        <v>52.59</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>55.41</v>
+        <v>53.81</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -2902,13 +2902,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>54.01</v>
+        <v>52.98</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>51.87</v>
+        <v>52.98</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -2932,13 +2932,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>52.23</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -2947,13 +2947,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>53.59</v>
+        <v>51.85</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -2962,13 +2962,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>53.31</v>
+        <v>51.41</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -2977,13 +2977,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>52.27</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -2992,13 +2992,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>53.3</v>
+        <v>52.02</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3007,13 +3007,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>53</v>
+        <v>52.63</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3022,13 +3022,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>52.87</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -3037,13 +3037,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>52.46</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -3052,13 +3052,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>53.33</v>
+        <v>52.79</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>53.53</v>
+        <v>53.07</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -3082,13 +3082,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>53.25</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3097,13 +3097,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>53.87</v>
+        <v>53.93</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -3112,13 +3112,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>53.61</v>
+        <v>55.12</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -3127,13 +3127,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>54.32</v>
+        <v>55.41</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -3142,13 +3142,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>55.55</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -3157,13 +3157,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>56.24</v>
+        <v>51.87</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -3172,13 +3172,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>55.61</v>
+        <v>52.23</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -3187,13 +3187,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>55.47</v>
+        <v>53.59</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -3202,13 +3202,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>55.8</v>
+        <v>53.31</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -3217,13 +3217,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>55.34</v>
+        <v>52.27</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -3232,13 +3232,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>54.93</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -3247,13 +3247,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>55.29</v>
+        <v>53</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -3262,13 +3262,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>55.02</v>
+        <v>52.87</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>55.59</v>
+        <v>52.46</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -3292,13 +3292,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>54.31</v>
+        <v>53.33</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -3307,13 +3307,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>54.1</v>
+        <v>53.53</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -3322,13 +3322,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>53.8</v>
+        <v>53.25</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -3337,13 +3337,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>53.47</v>
+        <v>53.87</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -3352,13 +3352,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>53.38</v>
+        <v>53.61</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -3367,13 +3367,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>53.17</v>
+        <v>54.32</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -3382,13 +3382,13 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>53.82</v>
+        <v>55.55</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>53.64</v>
+        <v>56.24</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -3412,13 +3412,13 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>54.46</v>
+        <v>55.61</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -3427,13 +3427,13 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>54.77</v>
+        <v>55.47</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -3442,13 +3442,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>53.48</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -3457,13 +3457,13 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>52.62</v>
+        <v>55.34</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -3472,13 +3472,13 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>52.52</v>
+        <v>54.93</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -3487,13 +3487,13 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>52.86</v>
+        <v>55.29</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -3502,13 +3502,13 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>52.43</v>
+        <v>55.02</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>52.69</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -3532,13 +3532,13 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>53.79</v>
+        <v>54.31</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -3547,13 +3547,13 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>55.04</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -3562,13 +3562,13 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>55.23</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -3577,13 +3577,13 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>55.16</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -3592,13 +3592,13 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>55.1</v>
+        <v>53.38</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -3607,13 +3607,13 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>51.65</v>
+        <v>53.17</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -3622,13 +3622,13 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>48.65</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -3637,13 +3637,13 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>48.94</v>
+        <v>53.64</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -3652,13 +3652,13 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>48.82</v>
+        <v>54.46</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>48.46</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -3682,13 +3682,13 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>48.62</v>
+        <v>53.48</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -3697,13 +3697,13 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>47.95</v>
+        <v>52.62</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -3712,13 +3712,13 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>47.8</v>
+        <v>52.52</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -3727,13 +3727,13 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>47.85</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -3742,13 +3742,13 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>47.49</v>
+        <v>52.43</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -3757,13 +3757,13 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>47.78</v>
+        <v>52.69</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -3772,13 +3772,13 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>49.05</v>
+        <v>53.79</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -3787,13 +3787,13 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>49.41</v>
+        <v>55.04</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>50.03</v>
+        <v>55.23</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -3817,13 +3817,13 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>49.88</v>
+        <v>55.16</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -3832,13 +3832,13 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>49.73</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -3847,13 +3847,13 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>50.23</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -3862,13 +3862,13 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>49.88</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -3877,13 +3877,13 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>49.78</v>
+        <v>48.94</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -3892,13 +3892,13 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>49.2</v>
+        <v>48.82</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -3907,13 +3907,13 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>48.9</v>
+        <v>48.46</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -3922,13 +3922,13 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>51.9</v>
+        <v>48.62</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -3937,13 +3937,13 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>51.46</v>
+        <v>47.95</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -3952,13 +3952,13 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>50.03</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -3967,13 +3967,13 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>48.66</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -3982,13 +3982,13 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>48.38</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -3997,13 +3997,13 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>47.52</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -4012,13 +4012,13 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>48.22</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -4027,13 +4027,13 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>48.33</v>
+        <v>49.41</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -4042,13 +4042,13 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>48.82</v>
+        <v>50.03</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -4057,13 +4057,13 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>48.95</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -4072,13 +4072,13 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>48.22</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -4087,13 +4087,13 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>48.75</v>
+        <v>50.23</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -4102,13 +4102,13 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>49.78</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -4117,13 +4117,13 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>49.23</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -4132,13 +4132,13 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>49.17</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -4147,13 +4147,13 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>47.85</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -4162,13 +4162,13 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>47.78</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -4177,13 +4177,13 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>47.83</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -4192,13 +4192,13 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>47.91</v>
+        <v>50.03</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -4207,13 +4207,13 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>47.73</v>
+        <v>48.66</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -4222,13 +4222,13 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>47.54</v>
+        <v>48.38</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -4237,13 +4237,13 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>46.72</v>
+        <v>47.52</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -4252,13 +4252,13 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>47.16</v>
+        <v>48.22</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -4267,13 +4267,13 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>46.15</v>
+        <v>48.33</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -4282,13 +4282,13 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>46.11</v>
+        <v>48.82</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -4297,13 +4297,13 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>44.82</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -4312,13 +4312,13 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>45.02</v>
+        <v>48.22</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -4327,13 +4327,13 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>45.96</v>
+        <v>48.75</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>47.35</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -4357,13 +4357,13 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>48.65</v>
+        <v>49.23</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -4372,13 +4372,13 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>47.87</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -4387,13 +4387,13 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>46</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -4402,13 +4402,13 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>46.11</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -4417,13 +4417,13 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>45.42</v>
+        <v>47.83</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -4432,13 +4432,13 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>44.2</v>
+        <v>47.91</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -4447,13 +4447,13 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>43.82</v>
+        <v>47.73</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -4462,13 +4462,13 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>43.48</v>
+        <v>47.54</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -4477,13 +4477,13 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>43.28</v>
+        <v>46.72</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -4492,13 +4492,13 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>43.7</v>
+        <v>47.16</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -4507,13 +4507,13 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>43.32</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -4522,13 +4522,13 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>43.28</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -4537,13 +4537,13 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>42.9</v>
+        <v>44.82</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -4552,13 +4552,13 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>42.51</v>
+        <v>45.02</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -4567,13 +4567,13 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>42.36</v>
+        <v>45.96</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -4582,13 +4582,13 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>42.65</v>
+        <v>47.35</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -4597,13 +4597,13 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>42.85</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -4612,13 +4612,13 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>43.04</v>
+        <v>47.87</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -4627,13 +4627,13 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>43.92</v>
+        <v>46</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -4642,13 +4642,13 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>43.52</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -4657,13 +4657,13 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>43.37</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -4672,13 +4672,13 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>43.24</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -4687,13 +4687,13 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>43.99</v>
+        <v>43.82</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -4702,13 +4702,13 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>44.52</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>45.66</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -4732,13 +4732,13 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>45.78</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -4747,13 +4747,13 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>46.1</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -4762,13 +4762,13 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>46.42</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -4777,13 +4777,13 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>47.21</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -4792,13 +4792,13 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>47.44</v>
+        <v>42.51</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -4807,13 +4807,13 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>46.5</v>
+        <v>42.36</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -4822,13 +4822,13 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>47.21</v>
+        <v>42.65</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -4837,13 +4837,13 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>46.08</v>
+        <v>42.85</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -4852,13 +4852,13 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>46.21</v>
+        <v>43.04</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -4867,13 +4867,13 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>45.72</v>
+        <v>43.92</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -4882,13 +4882,13 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>46.29</v>
+        <v>43.52</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -4897,13 +4897,13 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>45.9</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -4912,13 +4912,13 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>46.05</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -4927,13 +4927,13 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>45.73</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -4942,13 +4942,13 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>45.31</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -4957,13 +4957,13 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>45.75</v>
+        <v>45.66</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -4972,13 +4972,13 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>46.37</v>
+        <v>45.78</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -4987,13 +4987,13 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>45.77</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>45.1</v>
+        <v>46.42</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -5017,13 +5017,13 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>44.97</v>
+        <v>47.21</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>45.11</v>
+        <v>47.44</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -5047,13 +5047,13 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>44.88</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>45.06</v>
+        <v>47.21</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -5077,13 +5077,13 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>44.73</v>
+        <v>46.08</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -5092,13 +5092,13 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>44.3</v>
+        <v>46.21</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -5107,13 +5107,13 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>45.15</v>
+        <v>45.72</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -5122,13 +5122,13 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>45.27</v>
+        <v>46.29</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -5137,13 +5137,13 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>45.03</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -5152,13 +5152,13 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>45.99</v>
+        <v>46.05</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -5167,13 +5167,13 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>46.22</v>
+        <v>45.73</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -5182,13 +5182,13 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>46.06</v>
+        <v>45.31</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -5197,13 +5197,13 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>45.62</v>
+        <v>45.75</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -5212,13 +5212,13 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>43.48</v>
+        <v>46.37</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -5227,13 +5227,13 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>42.45</v>
+        <v>45.77</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -5242,13 +5242,13 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>42.17</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -5257,13 +5257,13 @@
         </is>
       </c>
       <c r="C322" t="n">
-        <v>41.34</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -5272,13 +5272,13 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>40.87</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -5287,13 +5287,13 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>41.09</v>
+        <v>44.88</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -5302,13 +5302,13 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>41.32</v>
+        <v>45.06</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -5317,13 +5317,13 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>41.19</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>40.94</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -5347,13 +5347,13 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>40.94</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2024-12-24</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>41.38</v>
+        <v>45.27</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -5377,13 +5377,13 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>41.62</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -5392,13 +5392,13 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>40.87</v>
+        <v>45.99</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -5407,13 +5407,13 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>41.15</v>
+        <v>46.22</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -5422,13 +5422,13 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>40.92</v>
+        <v>46.06</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -5437,13 +5437,13 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>41.73</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -5452,13 +5452,13 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>42.72</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -5467,13 +5467,13 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>43.49</v>
+        <v>42.45</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -5482,13 +5482,13 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>43.53</v>
+        <v>42.17</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -5497,13 +5497,13 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>43.26</v>
+        <v>41.34</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -5512,13 +5512,13 @@
         </is>
       </c>
       <c r="C339" t="n">
-        <v>43.46</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -5527,13 +5527,13 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>43.52</v>
+        <v>41.09</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -5542,13 +5542,13 @@
         </is>
       </c>
       <c r="C341" t="n">
-        <v>43.58</v>
+        <v>41.32</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -5557,13 +5557,13 @@
         </is>
       </c>
       <c r="C342" t="n">
-        <v>42.89</v>
+        <v>41.19</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -5572,13 +5572,13 @@
         </is>
       </c>
       <c r="C343" t="n">
-        <v>42.12</v>
+        <v>40.94</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -5587,13 +5587,13 @@
         </is>
       </c>
       <c r="C344" t="n">
-        <v>42.67</v>
+        <v>40.94</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -5602,13 +5602,13 @@
         </is>
       </c>
       <c r="C345" t="n">
-        <v>42.3</v>
+        <v>41.38</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -5617,13 +5617,13 @@
         </is>
       </c>
       <c r="C346" t="n">
-        <v>42.39</v>
+        <v>41.62</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>41.84</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -5647,13 +5647,13 @@
         </is>
       </c>
       <c r="C348" t="n">
-        <v>43.17</v>
+        <v>41.15</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -5662,13 +5662,13 @@
         </is>
       </c>
       <c r="C349" t="n">
-        <v>42.27</v>
+        <v>40.92</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -5677,13 +5677,13 @@
         </is>
       </c>
       <c r="C350" t="n">
-        <v>42.78</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -5692,13 +5692,13 @@
         </is>
       </c>
       <c r="C351" t="n">
-        <v>43.09</v>
+        <v>42.72</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -5707,13 +5707,13 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>43.95</v>
+        <v>43.49</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -5722,13 +5722,13 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>44.91</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -5737,13 +5737,13 @@
         </is>
       </c>
       <c r="C354" t="n">
-        <v>45.32</v>
+        <v>43.26</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -5752,13 +5752,13 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>45.24</v>
+        <v>43.46</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -5767,13 +5767,13 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>44.48</v>
+        <v>43.52</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -5782,13 +5782,13 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>45.38</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>46.24</v>
+        <v>42.89</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>47.78</v>
+        <v>42.12</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -5827,13 +5827,13 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>48.04</v>
+        <v>42.67</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -5842,13 +5842,13 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>47.49</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -5857,13 +5857,13 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>45.65</v>
+        <v>42.39</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -5872,13 +5872,13 @@
         </is>
       </c>
       <c r="C363" t="n">
-        <v>45.01</v>
+        <v>41.84</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -5887,13 +5887,13 @@
         </is>
       </c>
       <c r="C364" t="n">
-        <v>45.36</v>
+        <v>43.17</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -5902,13 +5902,13 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>45.49</v>
+        <v>42.27</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -5917,13 +5917,13 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>44.54</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -5932,13 +5932,13 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>43.62</v>
+        <v>43.09</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -5947,13 +5947,13 @@
         </is>
       </c>
       <c r="C368" t="n">
-        <v>42.78</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -5962,13 +5962,13 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>42.73</v>
+        <v>44.91</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -5977,13 +5977,13 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>43.65</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -5992,13 +5992,13 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>43.48</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -6007,13 +6007,13 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>42.77</v>
+        <v>44.48</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -6022,13 +6022,13 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>42.86</v>
+        <v>45.38</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -6037,13 +6037,13 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>41.8</v>
+        <v>46.24</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -6052,13 +6052,13 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>41.24</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -6067,13 +6067,13 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>41.92</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -6082,13 +6082,13 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>41.59</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -6097,13 +6097,13 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>42.03</v>
+        <v>45.65</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -6112,13 +6112,13 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>42.03</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -6127,13 +6127,13 @@
         </is>
       </c>
       <c r="C380" t="n">
-        <v>43.28</v>
+        <v>45.36</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -6142,13 +6142,13 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>43.74</v>
+        <v>45.49</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -6157,13 +6157,13 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>43.16</v>
+        <v>44.54</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -6172,13 +6172,13 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>43.22</v>
+        <v>43.62</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -6187,13 +6187,13 @@
         </is>
       </c>
       <c r="C384" t="n">
-        <v>44.73</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -6202,13 +6202,13 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>44.08</v>
+        <v>42.73</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -6217,13 +6217,13 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>44.43</v>
+        <v>43.65</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -6232,13 +6232,13 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>43.57</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -6247,13 +6247,13 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>43.08</v>
+        <v>42.77</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -6262,13 +6262,13 @@
         </is>
       </c>
       <c r="C389" t="n">
-        <v>43.05</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -6277,13 +6277,13 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>42.78</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -6292,13 +6292,13 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>43.53</v>
+        <v>41.24</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -6307,13 +6307,13 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>43.71</v>
+        <v>41.92</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -6322,13 +6322,13 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>43.14</v>
+        <v>41.59</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -6337,13 +6337,13 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>42.09</v>
+        <v>42.03</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -6352,13 +6352,13 @@
         </is>
       </c>
       <c r="C395" t="n">
-        <v>41.73</v>
+        <v>42.03</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -6367,13 +6367,13 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>41.43</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -6382,13 +6382,13 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>41.17</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -6397,13 +6397,13 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>40.69</v>
+        <v>43.16</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -6412,13 +6412,13 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>40.11</v>
+        <v>43.22</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -6427,13 +6427,13 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>40.12</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -6442,13 +6442,13 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>40.75</v>
+        <v>44.08</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -6457,13 +6457,13 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>40.39</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -6472,13 +6472,13 @@
         </is>
       </c>
       <c r="C403" t="n">
-        <v>40.6</v>
+        <v>43.57</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -6487,13 +6487,13 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>41.29</v>
+        <v>43.08</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -6502,13 +6502,13 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>40.49</v>
+        <v>43.05</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -6517,13 +6517,13 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>41.62</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -6532,13 +6532,13 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>40.98</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>41.5</v>
+        <v>43.71</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -6562,13 +6562,13 @@
         </is>
       </c>
       <c r="C409" t="n">
-        <v>42.26</v>
+        <v>43.14</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -6577,13 +6577,13 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>42.24</v>
+        <v>42.09</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -6592,13 +6592,13 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>41.21</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -6607,13 +6607,13 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>40.93</v>
+        <v>41.43</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -6622,13 +6622,13 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>40.83</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -6637,13 +6637,13 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>40.51</v>
+        <v>40.69</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -6652,13 +6652,13 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>39.52</v>
+        <v>40.11</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -6667,13 +6667,13 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>40.05</v>
+        <v>40.12</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -6682,13 +6682,13 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>39.68</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -6697,13 +6697,13 @@
         </is>
       </c>
       <c r="C418" t="n">
-        <v>39.76</v>
+        <v>40.39</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -6712,13 +6712,13 @@
         </is>
       </c>
       <c r="C419" t="n">
-        <v>39.55</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -6727,13 +6727,13 @@
         </is>
       </c>
       <c r="C420" t="n">
-        <v>39.29</v>
+        <v>41.29</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -6742,13 +6742,13 @@
         </is>
       </c>
       <c r="C421" t="n">
-        <v>39.58</v>
+        <v>40.49</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -6757,13 +6757,13 @@
         </is>
       </c>
       <c r="C422" t="n">
-        <v>39.89</v>
+        <v>41.62</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -6772,13 +6772,13 @@
         </is>
       </c>
       <c r="C423" t="n">
-        <v>40.84</v>
+        <v>40.98</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -6787,13 +6787,13 @@
         </is>
       </c>
       <c r="C424" t="n">
-        <v>40.75</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -6802,13 +6802,13 @@
         </is>
       </c>
       <c r="C425" t="n">
-        <v>40.68</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -6817,13 +6817,13 @@
         </is>
       </c>
       <c r="C426" t="n">
-        <v>40.51</v>
+        <v>42.24</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -6832,13 +6832,13 @@
         </is>
       </c>
       <c r="C427" t="n">
-        <v>40.16</v>
+        <v>41.21</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="C428" t="n">
-        <v>40.25</v>
+        <v>40.93</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -6862,13 +6862,13 @@
         </is>
       </c>
       <c r="C429" t="n">
-        <v>40.91</v>
+        <v>40.83</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -6877,13 +6877,13 @@
         </is>
       </c>
       <c r="C430" t="n">
-        <v>41.18</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -6892,13 +6892,13 @@
         </is>
       </c>
       <c r="C431" t="n">
-        <v>41.72</v>
+        <v>39.52</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -6907,13 +6907,13 @@
         </is>
       </c>
       <c r="C432" t="n">
-        <v>41.2</v>
+        <v>40.05</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -6922,13 +6922,13 @@
         </is>
       </c>
       <c r="C433" t="n">
-        <v>41.67</v>
+        <v>39.68</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -6937,13 +6937,13 @@
         </is>
       </c>
       <c r="C434" t="n">
-        <v>41.34</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -6952,13 +6952,13 @@
         </is>
       </c>
       <c r="C435" t="n">
-        <v>42.82</v>
+        <v>39.55</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -6967,13 +6967,13 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>42.57</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -6982,13 +6982,13 @@
         </is>
       </c>
       <c r="C437" t="n">
-        <v>43.28</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -6997,13 +6997,13 @@
         </is>
       </c>
       <c r="C438" t="n">
-        <v>42.86</v>
+        <v>39.89</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -7012,13 +7012,13 @@
         </is>
       </c>
       <c r="C439" t="n">
-        <v>41.96</v>
+        <v>40.84</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -7027,13 +7027,13 @@
         </is>
       </c>
       <c r="C440" t="n">
-        <v>42.63</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -7042,13 +7042,13 @@
         </is>
       </c>
       <c r="C441" t="n">
-        <v>42.6</v>
+        <v>40.68</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -7057,13 +7057,13 @@
         </is>
       </c>
       <c r="C442" t="n">
-        <v>43.39</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -7072,13 +7072,13 @@
         </is>
       </c>
       <c r="C443" t="n">
-        <v>43.49</v>
+        <v>40.16</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -7087,13 +7087,13 @@
         </is>
       </c>
       <c r="C444" t="n">
-        <v>44.6</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -7102,13 +7102,13 @@
         </is>
       </c>
       <c r="C445" t="n">
-        <v>45.01</v>
+        <v>40.91</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -7117,13 +7117,13 @@
         </is>
       </c>
       <c r="C446" t="n">
-        <v>44.73</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -7132,13 +7132,13 @@
         </is>
       </c>
       <c r="C447" t="n">
-        <v>45.87</v>
+        <v>41.72</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -7147,13 +7147,13 @@
         </is>
       </c>
       <c r="C448" t="n">
-        <v>46.97</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -7162,13 +7162,13 @@
         </is>
       </c>
       <c r="C449" t="n">
-        <v>47.02</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -7177,13 +7177,13 @@
         </is>
       </c>
       <c r="C450" t="n">
-        <v>46.75</v>
+        <v>41.34</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -7192,13 +7192,13 @@
         </is>
       </c>
       <c r="C451" t="n">
-        <v>45.79</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="C452" t="n">
-        <v>44.84</v>
+        <v>42.57</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -7222,13 +7222,13 @@
         </is>
       </c>
       <c r="C453" t="n">
-        <v>43.13</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -7237,13 +7237,13 @@
         </is>
       </c>
       <c r="C454" t="n">
-        <v>42.97</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="C455" t="n">
-        <v>43.37</v>
+        <v>41.96</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -7267,13 +7267,13 @@
         </is>
       </c>
       <c r="C456" t="n">
-        <v>42.71</v>
+        <v>42.63</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -7282,13 +7282,13 @@
         </is>
       </c>
       <c r="C457" t="n">
-        <v>43.35</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -7297,13 +7297,13 @@
         </is>
       </c>
       <c r="C458" t="n">
-        <v>43.58</v>
+        <v>43.39</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -7312,13 +7312,13 @@
         </is>
       </c>
       <c r="C459" t="n">
-        <v>43.59</v>
+        <v>43.49</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -7327,13 +7327,13 @@
         </is>
       </c>
       <c r="C460" t="n">
-        <v>44.01</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -7342,13 +7342,13 @@
         </is>
       </c>
       <c r="C461" t="n">
-        <v>43.56</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -7357,13 +7357,13 @@
         </is>
       </c>
       <c r="C462" t="n">
-        <v>43.53</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -7372,13 +7372,13 @@
         </is>
       </c>
       <c r="C463" t="n">
-        <v>43.76</v>
+        <v>45.87</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -7387,13 +7387,13 @@
         </is>
       </c>
       <c r="C464" t="n">
-        <v>43.87</v>
+        <v>46.97</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -7402,13 +7402,13 @@
         </is>
       </c>
       <c r="C465" t="n">
-        <v>43.76</v>
+        <v>47.02</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -7417,13 +7417,13 @@
         </is>
       </c>
       <c r="C466" t="n">
-        <v>43.98</v>
+        <v>46.75</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -7432,13 +7432,13 @@
         </is>
       </c>
       <c r="C467" t="n">
-        <v>44.29</v>
+        <v>45.79</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -7447,13 +7447,13 @@
         </is>
       </c>
       <c r="C468" t="n">
-        <v>44.83</v>
+        <v>44.84</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="C469" t="n">
-        <v>43.88</v>
+        <v>43.13</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -7477,13 +7477,13 @@
         </is>
       </c>
       <c r="C470" t="n">
-        <v>44.2</v>
+        <v>42.97</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -7492,13 +7492,13 @@
         </is>
       </c>
       <c r="C471" t="n">
-        <v>44.63</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -7507,13 +7507,13 @@
         </is>
       </c>
       <c r="C472" t="n">
-        <v>45.81</v>
+        <v>42.71</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -7522,13 +7522,13 @@
         </is>
       </c>
       <c r="C473" t="n">
-        <v>45.93</v>
+        <v>43.35</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -7537,13 +7537,13 @@
         </is>
       </c>
       <c r="C474" t="n">
-        <v>46.11</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -7552,13 +7552,13 @@
         </is>
       </c>
       <c r="C475" t="n">
-        <v>45.74</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -7567,13 +7567,13 @@
         </is>
       </c>
       <c r="C476" t="n">
-        <v>45.32</v>
+        <v>44.01</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -7582,13 +7582,13 @@
         </is>
       </c>
       <c r="C477" t="n">
-        <v>45.96</v>
+        <v>43.56</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -7597,13 +7597,13 @@
         </is>
       </c>
       <c r="C478" t="n">
-        <v>46.2</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -7612,13 +7612,13 @@
         </is>
       </c>
       <c r="C479" t="n">
-        <v>46.37</v>
+        <v>43.76</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -7627,13 +7627,13 @@
         </is>
       </c>
       <c r="C480" t="n">
-        <v>46.6</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -7642,13 +7642,13 @@
         </is>
       </c>
       <c r="C481" t="n">
-        <v>45.89</v>
+        <v>43.76</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -7657,13 +7657,13 @@
         </is>
       </c>
       <c r="C482" t="n">
-        <v>45.45</v>
+        <v>43.98</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -7672,13 +7672,13 @@
         </is>
       </c>
       <c r="C483" t="n">
-        <v>44.82</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -7687,13 +7687,13 @@
         </is>
       </c>
       <c r="C484" t="n">
-        <v>44.7</v>
+        <v>44.83</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -7702,13 +7702,13 @@
         </is>
       </c>
       <c r="C485" t="n">
-        <v>46.01</v>
+        <v>43.88</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -7717,13 +7717,13 @@
         </is>
       </c>
       <c r="C486" t="n">
-        <v>45.24</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -7732,13 +7732,13 @@
         </is>
       </c>
       <c r="C487" t="n">
-        <v>44.2</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -7747,13 +7747,13 @@
         </is>
       </c>
       <c r="C488" t="n">
-        <v>44.8</v>
+        <v>45.81</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -7762,13 +7762,13 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>45.29</v>
+        <v>45.93</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -7777,13 +7777,13 @@
         </is>
       </c>
       <c r="C490" t="n">
-        <v>44.66</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -7792,13 +7792,13 @@
         </is>
       </c>
       <c r="C491" t="n">
-        <v>44.34</v>
+        <v>45.74</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="C492" t="n">
-        <v>44.43</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -7822,13 +7822,13 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>44.49</v>
+        <v>45.96</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -7837,13 +7837,13 @@
         </is>
       </c>
       <c r="C494" t="n">
-        <v>44.32</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -7852,13 +7852,13 @@
         </is>
       </c>
       <c r="C495" t="n">
-        <v>45.01</v>
+        <v>46.37</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -7867,13 +7867,13 @@
         </is>
       </c>
       <c r="C496" t="n">
-        <v>45.94</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -7882,13 +7882,13 @@
         </is>
       </c>
       <c r="C497" t="n">
-        <v>45.67</v>
+        <v>45.89</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -7897,13 +7897,13 @@
         </is>
       </c>
       <c r="C498" t="n">
-        <v>45.58</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -7912,13 +7912,13 @@
         </is>
       </c>
       <c r="C499" t="n">
-        <v>45.95</v>
+        <v>44.82</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -7927,13 +7927,13 @@
         </is>
       </c>
       <c r="C500" t="n">
-        <v>45.8</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -7942,13 +7942,13 @@
         </is>
       </c>
       <c r="C501" t="n">
-        <v>45.14</v>
+        <v>46.01</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -7957,13 +7957,13 @@
         </is>
       </c>
       <c r="C502" t="n">
-        <v>44.97</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -7972,13 +7972,13 @@
         </is>
       </c>
       <c r="C503" t="n">
-        <v>45.19</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -7987,13 +7987,13 @@
         </is>
       </c>
       <c r="C504" t="n">
-        <v>45.34</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -8002,13 +8002,13 @@
         </is>
       </c>
       <c r="C505" t="n">
-        <v>45.6</v>
+        <v>45.29</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -8017,13 +8017,13 @@
         </is>
       </c>
       <c r="C506" t="n">
-        <v>45.97</v>
+        <v>44.66</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -8032,13 +8032,13 @@
         </is>
       </c>
       <c r="C507" t="n">
-        <v>45.91</v>
+        <v>44.34</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -8047,13 +8047,13 @@
         </is>
       </c>
       <c r="C508" t="n">
-        <v>46.95</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -8062,13 +8062,13 @@
         </is>
       </c>
       <c r="C509" t="n">
-        <v>46.91</v>
+        <v>44.49</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -8077,13 +8077,13 @@
         </is>
       </c>
       <c r="C510" t="n">
-        <v>47.23</v>
+        <v>44.32</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -8092,13 +8092,13 @@
         </is>
       </c>
       <c r="C511" t="n">
-        <v>47.84</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -8107,13 +8107,13 @@
         </is>
       </c>
       <c r="C512" t="n">
-        <v>47.38</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -8122,13 +8122,13 @@
         </is>
       </c>
       <c r="C513" t="n">
-        <v>48</v>
+        <v>45.67</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -8137,13 +8137,13 @@
         </is>
       </c>
       <c r="C514" t="n">
-        <v>47.67</v>
+        <v>45.58</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -8152,13 +8152,13 @@
         </is>
       </c>
       <c r="C515" t="n">
-        <v>47.12</v>
+        <v>45.95</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -8167,13 +8167,13 @@
         </is>
       </c>
       <c r="C516" t="n">
-        <v>47.14</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -8182,13 +8182,13 @@
         </is>
       </c>
       <c r="C517" t="n">
-        <v>46.67</v>
+        <v>45.14</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -8197,13 +8197,13 @@
         </is>
       </c>
       <c r="C518" t="n">
-        <v>47.46</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -8212,13 +8212,13 @@
         </is>
       </c>
       <c r="C519" t="n">
-        <v>47.71</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -8227,13 +8227,13 @@
         </is>
       </c>
       <c r="C520" t="n">
-        <v>46.65</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -8242,13 +8242,13 @@
         </is>
       </c>
       <c r="C521" t="n">
-        <v>47.72</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -8257,13 +8257,13 @@
         </is>
       </c>
       <c r="C522" t="n">
-        <v>47.89</v>
+        <v>45.97</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -8272,13 +8272,13 @@
         </is>
       </c>
       <c r="C523" t="n">
-        <v>47.23</v>
+        <v>45.91</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="C524" t="n">
-        <v>47.63</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -8302,13 +8302,13 @@
         </is>
       </c>
       <c r="C525" t="n">
-        <v>48.16</v>
+        <v>46.91</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -8317,13 +8317,13 @@
         </is>
       </c>
       <c r="C526" t="n">
-        <v>47.08</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -8332,13 +8332,13 @@
         </is>
       </c>
       <c r="C527" t="n">
-        <v>47.34</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -8347,13 +8347,13 @@
         </is>
       </c>
       <c r="C528" t="n">
-        <v>46.61</v>
+        <v>47.38</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -8362,13 +8362,13 @@
         </is>
       </c>
       <c r="C529" t="n">
-        <v>45.84</v>
+        <v>48</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="C530" t="n">
-        <v>45.28</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -8392,13 +8392,13 @@
         </is>
       </c>
       <c r="C531" t="n">
-        <v>45.23</v>
+        <v>47.12</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -8407,13 +8407,13 @@
         </is>
       </c>
       <c r="C532" t="n">
-        <v>44.51</v>
+        <v>47.14</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -8422,13 +8422,13 @@
         </is>
       </c>
       <c r="C533" t="n">
-        <v>44.37</v>
+        <v>46.67</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -8437,13 +8437,13 @@
         </is>
       </c>
       <c r="C534" t="n">
-        <v>44.55</v>
+        <v>47.46</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -8452,13 +8452,13 @@
         </is>
       </c>
       <c r="C535" t="n">
-        <v>44.45</v>
+        <v>47.71</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -8467,13 +8467,13 @@
         </is>
       </c>
       <c r="C536" t="n">
-        <v>44.56</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -8482,13 +8482,13 @@
         </is>
       </c>
       <c r="C537" t="n">
-        <v>44.63</v>
+        <v>47.72</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -8497,13 +8497,13 @@
         </is>
       </c>
       <c r="C538" t="n">
-        <v>44.69</v>
+        <v>47.89</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>2024-02-26</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -8512,13 +8512,13 @@
         </is>
       </c>
       <c r="C539" t="n">
-        <v>44.2</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -8527,13 +8527,13 @@
         </is>
       </c>
       <c r="C540" t="n">
-        <v>43.78</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -8542,13 +8542,13 @@
         </is>
       </c>
       <c r="C541" t="n">
-        <v>43.99</v>
+        <v>48.16</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -8557,13 +8557,13 @@
         </is>
       </c>
       <c r="C542" t="n">
-        <v>44</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -8572,13 +8572,13 @@
         </is>
       </c>
       <c r="C543" t="n">
-        <v>44.35</v>
+        <v>47.34</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -8587,13 +8587,13 @@
         </is>
       </c>
       <c r="C544" t="n">
-        <v>44.52</v>
+        <v>46.61</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -8602,13 +8602,13 @@
         </is>
       </c>
       <c r="C545" t="n">
-        <v>44.68</v>
+        <v>45.84</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -8617,13 +8617,13 @@
         </is>
       </c>
       <c r="C546" t="n">
-        <v>45.07</v>
+        <v>45.28</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="C547" t="n">
-        <v>45.62</v>
+        <v>45.23</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>2024-02-12</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -8647,13 +8647,13 @@
         </is>
       </c>
       <c r="C548" t="n">
-        <v>45.33</v>
+        <v>44.51</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -8662,13 +8662,13 @@
         </is>
       </c>
       <c r="C549" t="n">
-        <v>45.64</v>
+        <v>44.37</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -8677,13 +8677,13 @@
         </is>
       </c>
       <c r="C550" t="n">
-        <v>45.59</v>
+        <v>44.55</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -8692,13 +8692,13 @@
         </is>
       </c>
       <c r="C551" t="n">
-        <v>44.61</v>
+        <v>44.45</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="C552" t="n">
-        <v>44.2</v>
+        <v>44.56</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -8722,13 +8722,13 @@
         </is>
       </c>
       <c r="C553" t="n">
-        <v>43.73</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -8737,13 +8737,13 @@
         </is>
       </c>
       <c r="C554" t="n">
-        <v>43.66</v>
+        <v>44.69</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -8752,13 +8752,13 @@
         </is>
       </c>
       <c r="C555" t="n">
-        <v>44.07</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -8767,13 +8767,13 @@
         </is>
       </c>
       <c r="C556" t="n">
-        <v>44.66</v>
+        <v>43.78</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2024-02-22</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -8782,13 +8782,13 @@
         </is>
       </c>
       <c r="C557" t="n">
-        <v>44.75</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -8797,13 +8797,13 @@
         </is>
       </c>
       <c r="C558" t="n">
-        <v>44.73</v>
+        <v>44</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -8812,13 +8812,13 @@
         </is>
       </c>
       <c r="C559" t="n">
-        <v>45.37</v>
+        <v>44.35</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -8827,13 +8827,13 @@
         </is>
       </c>
       <c r="C560" t="n">
-        <v>45.34</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -8842,13 +8842,13 @@
         </is>
       </c>
       <c r="C561" t="n">
-        <v>45.57</v>
+        <v>44.68</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>2024-01-23</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -8857,13 +8857,13 @@
         </is>
       </c>
       <c r="C562" t="n">
-        <v>45.97</v>
+        <v>45.07</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -8872,13 +8872,13 @@
         </is>
       </c>
       <c r="C563" t="n">
-        <v>45.94</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>2024-01-19</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -8887,13 +8887,13 @@
         </is>
       </c>
       <c r="C564" t="n">
-        <v>45.19</v>
+        <v>45.33</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-09</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -8902,13 +8902,13 @@
         </is>
       </c>
       <c r="C565" t="n">
-        <v>45.44</v>
+        <v>45.64</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -8917,13 +8917,13 @@
         </is>
       </c>
       <c r="C566" t="n">
-        <v>45.42</v>
+        <v>45.59</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -8932,13 +8932,13 @@
         </is>
       </c>
       <c r="C567" t="n">
-        <v>45.42</v>
+        <v>44.61</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -8947,13 +8947,13 @@
         </is>
       </c>
       <c r="C568" t="n">
-        <v>46.13</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>2024-01-11</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -8962,13 +8962,13 @@
         </is>
       </c>
       <c r="C569" t="n">
-        <v>46.6</v>
+        <v>43.73</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -8977,13 +8977,13 @@
         </is>
       </c>
       <c r="C570" t="n">
-        <v>46.28</v>
+        <v>43.66</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -8992,13 +8992,13 @@
         </is>
       </c>
       <c r="C571" t="n">
-        <v>46.63</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>2024-01-08</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -9007,13 +9007,13 @@
         </is>
       </c>
       <c r="C572" t="n">
-        <v>45.95</v>
+        <v>44.66</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>2024-01-30</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -9022,13 +9022,13 @@
         </is>
       </c>
       <c r="C573" t="n">
-        <v>45.99</v>
+        <v>44.75</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>2024-01-04</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -9037,13 +9037,13 @@
         </is>
       </c>
       <c r="C574" t="n">
-        <v>46.36</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>2024-01-03</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -9052,13 +9052,13 @@
         </is>
       </c>
       <c r="C575" t="n">
-        <v>46.7</v>
+        <v>45.37</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -9067,13 +9067,13 @@
         </is>
       </c>
       <c r="C576" t="n">
-        <v>46.66</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>2023-12-29</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -9082,13 +9082,13 @@
         </is>
       </c>
       <c r="C577" t="n">
-        <v>46.4</v>
+        <v>45.57</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>2023-12-28</t>
+          <t>2024-01-23</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -9097,13 +9097,13 @@
         </is>
       </c>
       <c r="C578" t="n">
-        <v>46.26</v>
+        <v>45.97</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>2023-12-27</t>
+          <t>2024-01-22</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -9112,13 +9112,13 @@
         </is>
       </c>
       <c r="C579" t="n">
-        <v>46.98</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>2023-12-26</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -9127,13 +9127,13 @@
         </is>
       </c>
       <c r="C580" t="n">
-        <v>47.03</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -9142,13 +9142,13 @@
         </is>
       </c>
       <c r="C581" t="n">
-        <v>47.28</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -9157,13 +9157,13 @@
         </is>
       </c>
       <c r="C582" t="n">
-        <v>47.36</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -9172,13 +9172,13 @@
         </is>
       </c>
       <c r="C583" t="n">
-        <v>48.24</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -9187,13 +9187,13 @@
         </is>
       </c>
       <c r="C584" t="n">
-        <v>48.29</v>
+        <v>46.13</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -9202,13 +9202,13 @@
         </is>
       </c>
       <c r="C585" t="n">
-        <v>48.22</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2024-01-10</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -9217,21 +9217,261 @@
         </is>
       </c>
       <c r="C586" t="n">
-        <v>47.59</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
+          <t>2024-01-09</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C587" t="n">
+        <v>46.63</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C588" t="n">
+        <v>45.95</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2024-01-05</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C589" t="n">
+        <v>45.99</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2024-01-04</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C590" t="n">
+        <v>46.36</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2024-01-03</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C591" t="n">
+        <v>46.7</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2024-01-02</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C592" t="n">
+        <v>46.66</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2023-12-29</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C593" t="n">
+        <v>46.4</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2023-12-28</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C594" t="n">
+        <v>46.26</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2023-12-27</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C595" t="n">
+        <v>46.98</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2023-12-26</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C596" t="n">
+        <v>47.03</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2023-12-22</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C597" t="n">
+        <v>47.28</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2023-12-21</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C598" t="n">
+        <v>47.36</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C599" t="n">
+        <v>48.24</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C600" t="n">
+        <v>48.29</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C601" t="n">
+        <v>48.22</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2023-12-15</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C602" t="n">
+        <v>47.59</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
           <t>2023-12-14</t>
         </is>
       </c>
-      <c r="B587" t="inlineStr">
-        <is>
-          <t>BOK26</t>
-        </is>
-      </c>
-      <c r="C587" t="n">
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>BOK26</t>
+        </is>
+      </c>
+      <c r="C603" t="n">
         <v>47.31</v>
       </c>
     </row>
